--- a/data/12_defence_shipbuilding.xlsx
+++ b/data/12_defence_shipbuilding.xlsx
@@ -2,18 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defence Companies" sheetId="1" r:id="Ra831b9a213cf4ff9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="2" r:id="Ra483a8f224c0474a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Facilities" sheetId="3" r:id="R3899dbff72064c13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Capabilities" sheetId="4" r:id="R090536db2c4d4458"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="5" r:id="R1dc4d4e06d7f4ef6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Participants" sheetId="6" r:id="R728d38a351e649f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Vessels" sheetId="7" r:id="Rf06dca9f61984d77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="8" r:id="R8f0fce0601234f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales &amp; Delivery Routes" sheetId="9" r:id="R9b6626e7402b4dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announcements" sheetId="10" r:id="Rabe2f1162a0e49a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="R6acb24d6674340a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="12" r:id="R28fe87ea5ad1412c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defence Companies" sheetId="1" r:id="Rf0d7417cd8ed4252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="2" r:id="R183fffb32ef44619"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Facilities" sheetId="3" r:id="R0b8abc690aad4858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Capabilities" sheetId="4" r:id="Rb2f4fe22144a459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="5" r:id="Rf972820517014da5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Participants" sheetId="6" r:id="Rfcb857d3f9ce4d35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Vessels" sheetId="7" r:id="R1d7fc0d6c047498f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="8" r:id="R971065f2a6964a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales &amp; Delivery Routes" sheetId="9" r:id="Rbc701406891e4e11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announcements" sheetId="10" r:id="R183d0f6888e74177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="Rb10e389a00bc4705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="12" r:id="R1e27b49969284f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform Classes" sheetId="13" r:id="R4113781fa4d44614"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Status History" sheetId="14" r:id="R451c8a024b364631"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -48,7 +50,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -65,6 +67,11 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B1F33"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -73,7 +80,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -99,6 +106,12 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1186,6 +1199,240 @@
         <x:v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>ANN_AOPS_01</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>2025-08-21</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>RCN accepts sixth and final AOPS, HMCS Robert Hampton Gray</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Irving; Halifax Shipyard; RCN; Robert Hampton Gray</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>ANN_AOPS_02</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-04-29</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Canadian Coast Guard launches CCGS Donjek</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Launch</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>Irving; Halifax Shipyard; CCG; Donjek; Sermilik</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>ANN_UAE_01</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2021-05-18</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>ADSB awarded AED3.5bn contract for four FALAJ 3 vessels</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Contract</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>ADSB; UAE Navy; UAE Ministry of Defence; FALAJ3</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>https://edgegroup.ae/share/pdf/news/173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>ANN_UAE_02</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>2025-01-14</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>ADSB launches first FALAJ 3 vessel</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Launch</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>ADSB; UAE Navy; first FALAJ3</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>https://edgegroup.ae/news/adsb-launches-first-vessel-prestigious-falaj-3-programme</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>ANN_UAE_03</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2025-02-19</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>ALTAF commissioned as first FALAJ 3 missile boat</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Commissioning</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>ALTAF; ADSB; EDGE; UAE Navy</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>ANN_UAE_04</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2023-10-21</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Naval Group delivers Bani Yas to UAE Navy</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Bani Yas; Lorient; UAE Navy</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>ANN_UAE_05</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>2024-06-27</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Naval Group delivers Al Emarat to UAE Navy</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Al Emarat; Lorient; UAE Navy</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>ANN_UAE_06</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>2017-02-20</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>UAE commissions Al Hili, sixth Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Commissioning</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Al Hili; ADSB; UAE Navy</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>ANN_UAE_07</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>2013-01-08</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Fincantieri delivers Abu Dhabi corvette and Ghantut patrol vessel</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>COMP_FINCANTIERI</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>PROG_UAE_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Abu Dhabi; Ghantut; UAE Navy; Muggiano</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1488,6 +1735,244 @@
         <x:v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</x:v>
       </x:c>
       <x:c r="E17" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>SRC131_001</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>RCN AOPS fleet / six deliveries</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-navy.html</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>SRC131_002</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>AOPS project updates / delivery timeline</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>SRC131_003</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>CCGS Donjek launch / CCG AOPS status</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>SRC131_004</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>CCG AOPS programme budget / delivery</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>SRC131_005</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>EDGE / ADSB</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>FALAJ3 AED3.5bn / four-vessel contract</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>https://edgegroup.ae/share/pdf/news/173</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>SRC131_006</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>EDGE / ADSB</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>ALTAF commissioning / first-of-class</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>SRC131_007</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>EDGE / ADSB</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Baynunah programme / six corvettes</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>https://edgegroup.ae/adsb</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>SRC131_008</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>WAM</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Al Hili sixth Baynunah commissioned</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>SRC131_009</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Fincantieri</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Abu Dhabi / Falaj 2 UAE deliveries</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>SRC131_010</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Naval Group</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Bani Yas delivery</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>SRC131_011</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Naval Group</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Al Emarat delivery</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>SRC131_012</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Fincantieri</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Qarnen launch / Falaj 2 programme</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>SRC131_013</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Public fleet reference</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Baynunah class vessel names / pennants cross-check</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>SRC131_014</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>EDGE / MAESTRAL</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>UAE Coast Guard ten P51MR order</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
         <x:v>2026-09-09</x:v>
       </x:c>
     </x:row>
@@ -1512,7 +1997,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>P&amp;C Trade System Intelligence Model v1.27 — Defence &amp; Strategic Shipbuilding Stress Test</x:v>
+        <x:v>P&amp;C Trade System Intelligence Model v1.31 — Programme-to-Vessel Fleet Expansion</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -1602,10 +2087,10 @@
         <x:v>Programmes</x:v>
       </x:c>
       <x:c r="B8" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>Commercial + defence + coast guard + MRO can coexist on one company / yard</x:v>
+        <x:v>AOPS expanded into parent + RCN + CCG programme branches</x:v>
       </x:c>
       <x:c r="E8" t="str"/>
       <x:c r="F8" t="str"/>
@@ -1617,10 +2102,10 @@
         <x:v>Programme participants</x:v>
       </x:c>
       <x:c r="B9" t="n">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>Source conflicts remain separate records with evidence notes</x:v>
+        <x:v>UAE fleet expanded across Baynunah, FALAJ3, Bani Yas/Gowind, Falaj 2 and P51MR</x:v>
       </x:c>
       <x:c r="E9" t="str"/>
       <x:c r="F9" t="str"/>
@@ -1632,10 +2117,10 @@
         <x:v>Sample vessels</x:v>
       </x:c>
       <x:c r="B10" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>Tables are evidence; search/entity explorer is the primary UI</x:v>
+        <x:v>Named vessels are canonical where verified; unnamed ordered hulls remain explicit 'name pending' slots</x:v>
       </x:c>
       <x:c r="E10" t="str"/>
       <x:c r="F10" t="str"/>
@@ -1647,7 +2132,10 @@
         <x:v>Contracts</x:v>
       </x:c>
       <x:c r="B11" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Programme → contract → builder → yard → vessel → customer is searchable</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1655,7 +2143,10 @@
         <x:v>Sales / delivery routes</x:v>
       </x:c>
       <x:c r="B12" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Vessel status history preserves launch / delivery / commissioning milestones</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1663,13 +2154,633 @@
         <x:v>Announcements</x:v>
       </x:c>
       <x:c r="B13" t="n">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Platform Classes separates class from programme and individual vessel</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="20" t="str">
+        <x:v>Class ID</x:v>
+      </x:c>
+      <x:c r="B1" s="20" t="str">
+        <x:v>Class / Platform</x:v>
+      </x:c>
+      <x:c r="C1" s="20" t="str">
+        <x:v>Programme ID</x:v>
+      </x:c>
+      <x:c r="D1" s="20" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="E1" s="20" t="str">
+        <x:v>Length</x:v>
+      </x:c>
+      <x:c r="F1" s="20" t="str">
+        <x:v>Quantity</x:v>
+      </x:c>
+      <x:c r="G1" s="20" t="str">
+        <x:v>Primary Customer</x:v>
+      </x:c>
+      <x:c r="H1" s="20" t="str">
+        <x:v>Prime / Builder</x:v>
+      </x:c>
+      <x:c r="I1" s="20" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="J1" s="20" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>CLASS_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>Harry DeWolf class</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Arctic / offshore patrol vessel</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>103 m</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>Irving Shipbuilding</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>Six delivered</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>https://www.canada.ca/en/navy/corporate/fleet-units/surface/harry-dewolf-class/fact-sheet.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>CLASS_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>CCG AOPS variant</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Coast Guard offshore patrol / ice-capable</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>AOPS-derived</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>Irving Shipbuilding</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>Build / delivery</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>CLASS_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>FALAJ 3</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Missile boat / fast patrol vessel</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>62 m</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>ADSB</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>Programme active</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>CLASS_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Baynunah class</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>Corvette</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>71 m</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>ADSB / CMN</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>https://edgegroup.ae/adsb</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>CLASS_UAE_GOWIND</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Bani Yas / Gowind</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>Multi-mission corvette</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>~102 m</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>Naval Group</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>CLASS_UAE_FALAJ2</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Falaj 2</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>PROG_UAE_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Stealth patrol vessel</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>55 m</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Fincantieri</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>CLASS_UAE_P51</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>P51MR</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Offshore patrol vessel</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>51 m</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>MAESTRAL</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>Contracted</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="20" t="str">
+        <x:v>Status ID</x:v>
+      </x:c>
+      <x:c r="B1" s="20" t="str">
+        <x:v>Vessel ID</x:v>
+      </x:c>
+      <x:c r="C1" s="20" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="D1" s="20" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="E1" s="20" t="str">
+        <x:v>Milestone</x:v>
+      </x:c>
+      <x:c r="F1" s="20" t="str">
+        <x:v>Location</x:v>
+      </x:c>
+      <x:c r="G1" s="20" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>VSTAT_AOPS_01</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>VES_AOPS_01</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>2020-07-31</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>Delivery to RCN</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>Halifax</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>VSTAT_AOPS_02</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>VES_AOPS_02</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>2021-07-15</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>Delivery to RCN</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Halifax</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>VSTAT_AOPS_03</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>VES_AOPS_03</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>2022-09-02</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>Delivery to RCN</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>Halifax</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>VSTAT_AOPS_04</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>VES_AOPS_04</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>2023-08-31</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>Delivery to RCN</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>Halifax</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>VSTAT_AOPS_05</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>VES_AOPS_05</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>2024-08-29</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>Delivery to RCN</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>Halifax</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>VSTAT_AOPS_06</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>VES_AOPS_05</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>2025-06-13</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Commissioned</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Commissioned into RCN service</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/06/his-majestys-canadian-ship-frederick-rolette-commissioned-into-service.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>VSTAT_AOPS_07</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>VES_AOPS_06</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>2025-08-21</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>Sixth/final RCN AOPS accepted</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Halifax</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>VSTAT_AOPS_08</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>VES_AOPS_07</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>2026-04-29</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Launched</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>CCGS Donjek launched</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>Halifax</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>VSTAT_UAE_01</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>VES_UAE_F3_01</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>2025-01-14</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Launched</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>First FALAJ3 launched</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>https://edgegroup.ae/news/adsb-launches-first-vessel-prestigious-falaj-3-programme</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>VSTAT_UAE_02</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>VES_UAE_F3_01</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>2025-02-19</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Commissioned</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>ALTAF commissioned</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>VSTAT_UAE_03</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>VES_UAE_GOW_01</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>2023-10-21</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Bani Yas delivered</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>Lorient</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>VSTAT_UAE_04</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>VES_UAE_GOW_02</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>2024-06-27</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Al Emarat delivered</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Lorient</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>VSTAT_UAE_05</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>VES_UAE_BAY_06</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>2017-02-20</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Commissioned</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Al Hili commissioned</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -2209,6 +3320,64 @@
       </x:c>
       <x:c r="I18" s="8" t="str">
         <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>YARD_NAVAL_LORIENT</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Naval Group Lorient Shipyard</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Lorient</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Naval strategic newbuild</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Bani Yas-class Gowind corvettes; other surface combatants</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>YARD_CMN_CHERBOURG</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>COMP_CMN_NAVAL</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>CMN Cherbourg Shipyard</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Cherbourg</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Naval / patrol craft newbuild</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Lead Baynunah; BR71 / Combattante family</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>https://edgegroup.ae/news/edge-announces-launch-first-class-corvette-angolan-navy</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3240,7 +4409,7 @@
         <x:v>PROG_AOPS</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
-        <x:v>Arctic and Offshore Patrol Ships</x:v>
+        <x:v>Arctic and Offshore Patrol Ships — programme family</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
         <x:v>Navy / Coast Guard</x:v>
@@ -3252,20 +4421,20 @@
         <x:v>COMP_IRVING</x:v>
       </x:c>
       <x:c r="F5" s="8" t="str">
-        <x:v>8 variants</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G5" s="8" t="str">
-        <x:v>AOPS</x:v>
-      </x:c>
-      <x:c r="H5" s="8" t="str"/>
+        <x:v>Harry DeWolf-class / CCG AOPS variant</x:v>
+      </x:c>
+      <x:c r="H5" s="8"/>
       <x:c r="I5" s="8" t="str">
-        <x:v>Late build / delivery phase</x:v>
+        <x:v>RCN six delivered; CCG two in build/delivery phase</x:v>
       </x:c>
       <x:c r="J5" s="8" t="str">
         <x:v>Canada</x:v>
       </x:c>
       <x:c r="K5" s="8" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/corporate/reports-publications/departmental-plans/departmental-plan-2026-27/status-report-transformational-major-capital-projects.html</x:v>
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3633,6 +4802,177 @@
       </x:c>
       <x:c r="K16" s="8" t="str">
         <x:v>https://www.seaspan.com/seaspan-shipyards/repair-refit-and-maintenance/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>AOPS — Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Navy</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>C$4.98bn project budget / C$6.4bn awarded noted Sep 2025</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>Six delivered</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-navy.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>AOPS — Canadian Coast Guard variant</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Coast Guard</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>AOPS-derived Coast Guard patrol ship</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>C$2.1bn project budget</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>Donjek launched; Sermilik under construction</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>UAE FALAJ 3 Missile Boat Programme</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Navy</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>62 m FALAJ 3 missile boat</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>AED3.5bn</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>First vessel ALTAF commissioned; remaining vessels in programme</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>UAE</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>UAE Baynunah-class Corvette Programme</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Navy</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>71 m Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="H20"/>
+      <x:c r="I20" t="str">
+        <x:v>Six delivered / in service</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>France + UAE</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>https://edgegroup.ae/adsb</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>UAE Bani Yas / Gowind Corvette Programme</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Navy</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Gowind multi-mission corvette</x:v>
+      </x:c>
+      <x:c r="H21"/>
+      <x:c r="I21" t="str">
+        <x:v>Both delivered</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>France → UAE</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3928,6 +5268,202 @@
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>Victoria Shipyards</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>PROG_AOPS</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Prime contractor / builder</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Halifax Shipyard; eight AOPS family vessels</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Prime contractor / builder</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Six Harry DeWolf-class vessels</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>MIL_RCN</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Customer / operator</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Prime contractor / builder</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>Two Coast Guard variants</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>GOV_CCG</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Customer / operator</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Prime builder</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Four 62 m FALAJ3 missile boats</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>COMP_EDGE</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Parent / programme support</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>ADSB parent group</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>MIL_UAE_NAVY</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Customer / operator</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Prime contractor / builder</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Five of six vessels built in Abu Dhabi; programme delivery/support</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>COMP_CMN_NAVAL</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Design / lead-vessel builder</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Lead ship built in Cherbourg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>MIL_UAE_NAVY</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Customer / operator</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Prime / builder</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Two Gowind corvettes built at Lorient</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>MIL_UAE_NAVY</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Customer / operator</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>GOV_UAE_CG</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Customer / operator</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>UAE Coast Guard</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4184,10 +5720,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
-        <x:v>VES_DEF_008</x:v>
+        <x:v>VES_UAE_P51_01</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>P51MR OPV - sample hull</x:v>
+        <x:v>P51MR OPV 01 — name pending</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
         <x:v>PROG_UAE_P51MR</x:v>
@@ -4198,15 +5734,15 @@
       <x:c r="E9" s="8" t="str">
         <x:v>UAE Coast Guard</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="str"/>
+      <x:c r="F9" s="8"/>
       <x:c r="G9" s="8" t="str">
-        <x:v>Build programme</x:v>
+        <x:v>Contracted / name not confirmed</x:v>
       </x:c>
       <x:c r="H9" s="8" t="str">
         <x:v>UAE / Italy</x:v>
       </x:c>
       <x:c r="I9" s="8" t="str">
-        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2024/edge-group-and-fincantieri-formalise-maestral-shipbuilding-joint-venture-and-announce-400-million-euro-order-for-10-naval-vessels</x:v>
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4265,6 +5801,858 @@
       </x:c>
       <x:c r="I11" s="8" t="str">
         <x:v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>VES_AOPS_01</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>HMCS Harry DeWolf</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Delivered 2020 / operational</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>VES_AOPS_02</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>HMCS Margaret Brooke</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>Delivered 2021 / operational</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>VES_AOPS_03</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>HMCS Max Bernays</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Delivered 2022 / operational</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>VES_AOPS_04</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>HMCS William Hall</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Delivered 2023 / commissioned 2024</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>VES_AOPS_05</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>HMCS Frédérick Rolette</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Delivered 2024 / commissioned 2025</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/06/his-majestys-canadian-ship-frederick-rolette-commissioned-into-service.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>VES_AOPS_06</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>HMCS Robert Hampton Gray</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Delivered 21 Aug 2025; commissioning expected 2026</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Halifax → RCN / Esquimalt</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>VES_AOPS_07</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>CCGS Donjek</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>AOPS Coast Guard variant</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Launched 29 Apr 2026; delivery expected late 2026</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Halifax → CCG</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>VES_AOPS_08</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>CCGS Sermilik</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>AOPS Coast Guard variant</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Under construction; delivery expected 2027</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Halifax → CCG</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>VES_UAE_F3_01</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>ALTAF</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>FALAJ 3 62 m missile boat</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Commissioned 19 Feb 2025</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>VES_UAE_F3_02</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>FALAJ 3 Unit 2 — name pending</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>FALAJ 3 62 m missile boat</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Programme vessel / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>VES_UAE_F3_03</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>FALAJ 3 Unit 3 — name pending</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>FALAJ 3 62 m missile boat</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Programme vessel / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>VES_UAE_F3_04</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>FALAJ 3 Unit 4 — name pending</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>FALAJ 3 62 m missile boat</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Programme vessel / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>VES_UAE_BAY_01</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>Baynunah (P171)</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>YARD_CMN_CHERBOURG</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>France → UAE</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>VES_UAE_BAY_02</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Al Hesen (P172)</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>VES_UAE_BAY_03</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Al Dhafra (P173)</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>VES_UAE_BAY_04</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Mezyad (P174)</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>VES_UAE_BAY_05</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Al Jahili (P175)</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>VES_UAE_BAY_06</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Al Hili (P176)</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Commissioned 20 Feb 2017 / in service</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>VES_UAE_GOW_01</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Bani Yas</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Gowind multi-mission corvette</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>YARD_NAVAL_LORIENT</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Delivered 21 Oct 2023</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Lorient → UAE</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>VES_UAE_GOW_02</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Al Emarat</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>Gowind multi-mission corvette</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>YARD_NAVAL_LORIENT</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Delivered 27 Jun 2024</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Lorient → UAE</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>VES_UAE_F2_02</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Qarnen</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>PROG_UAE_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Falaj 2 patrol vessel</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>YARD_FIN_MUGGIANO</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Delivered / operational</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Italy → UAE</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>VES_UAE_P51_02</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>P51MR OPV 02 — name pending</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F33"/>
+      <x:c r="G33" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>VES_UAE_P51_03</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>P51MR OPV 03 — name pending</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F34"/>
+      <x:c r="G34" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>VES_UAE_P51_04</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>P51MR OPV 04 — name pending</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F35"/>
+      <x:c r="G35" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>VES_UAE_P51_05</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>P51MR OPV 05 — name pending</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F36"/>
+      <x:c r="G36" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>VES_UAE_P51_06</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>P51MR OPV 06 — name pending</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F37"/>
+      <x:c r="G37" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>VES_UAE_P51_07</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>P51MR OPV 07 — name pending</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F38"/>
+      <x:c r="G38" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>VES_UAE_P51_08</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>P51MR OPV 08 — name pending</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F39"/>
+      <x:c r="G39" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>VES_UAE_P51_09</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>P51MR OPV 09 — name pending</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F40"/>
+      <x:c r="G40" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>VES_UAE_P51_10</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>P51MR OPV 10 — name pending</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F41"/>
+      <x:c r="G41" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4540,6 +6928,132 @@
         <x:v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>CON_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>2014-12-23</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Government of Canada / RCN</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>C$6.4bn awarded noted Sep 2025</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>Construction of 6 RCN AOPS within 8-vessel shipbuilding contract family</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>Shipbuilding contract / amendments</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>Six RCN vessels delivered</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/corporate/transparency/briefing-materials/standing-committee-government-operations-estimates/2025-10-30.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>CON_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>2019-11-01</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Government of Canada / CCG</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>C$2.1bn project budget</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>2 adapted AOPS for Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>Design / build programme</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>Construction / delivery 2026-27</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>CON_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>2021-05-18</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>UAE Ministry of Defence / UAE Navy</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>AED3.5bn</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>4 FALAJ 3-class vessels</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>Shipbuilding contract</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>Active; first commissioned</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>https://edgegroup.ae/share/pdf/news/173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>CON_UAE_GOWIND</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>2019-03-25</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>United Arab Emirates / UAE Navy</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="F12"/>
+      <x:c r="G12" t="str">
+        <x:v>2 Gowind corvettes</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Export shipbuilding contract</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4785,6 +7299,134 @@
         <x:v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>SALE_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>DOMESTIC_BUILD</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>Halifax Shipyard → RCN</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-navy.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>SALE_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>DOMESTIC_BUILD</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>Halifax Shipyard → CCG</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>In build / delivery</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>SALE_UAE_F3</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>UAE</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>UAE</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>LOCAL_BUILD</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>ADSB Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>https://edgegroup.ae/news/adsb-launches-first-vessel-prestigious-falaj-3-programme</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>SALE_UAE_GOW</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>UAE</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>EXPORT_BUILD</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>Naval Group Lorient → UAE</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>Delivered</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/12_defence_shipbuilding.xlsx
+++ b/data/12_defence_shipbuilding.xlsx
@@ -2,20 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defence Companies" sheetId="1" r:id="Rf0d7417cd8ed4252"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="2" r:id="R183fffb32ef44619"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Facilities" sheetId="3" r:id="R0b8abc690aad4858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Capabilities" sheetId="4" r:id="Rb2f4fe22144a459c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="5" r:id="Rf972820517014da5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Participants" sheetId="6" r:id="Rfcb857d3f9ce4d35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Vessels" sheetId="7" r:id="R1d7fc0d6c047498f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="8" r:id="R971065f2a6964a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales &amp; Delivery Routes" sheetId="9" r:id="Rbc701406891e4e11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announcements" sheetId="10" r:id="R183d0f6888e74177"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="Rb10e389a00bc4705"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="12" r:id="R1e27b49969284f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform Classes" sheetId="13" r:id="R4113781fa4d44614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Status History" sheetId="14" r:id="R451c8a024b364631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defence Companies" sheetId="1" r:id="Rc5bf986753914697"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="2" r:id="R9093970298e84ddf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Facilities" sheetId="3" r:id="Rd017ec8067334c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Capabilities" sheetId="4" r:id="Rc425a36ae76d4b62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="5" r:id="R99392d7ebcbf48fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Participants" sheetId="6" r:id="R8f42584db1014144"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Vessels" sheetId="7" r:id="R53cc3979b37e40ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="8" r:id="R323227e176384a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales &amp; Delivery Routes" sheetId="9" r:id="Rcbcddd8a96094213"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announcements" sheetId="10" r:id="R7a0e8af8ec3044ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="R1cc1847f3f9045eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="12" r:id="R6cd3ea34420f4135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform Classes" sheetId="13" r:id="Rfdb619aacd934d94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Status History" sheetId="14" r:id="R076d1feee9cf436e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maritime Workforce" sheetId="15" r:id="Rdad202afbf6d4f61"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +27,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -49,8 +50,19 @@
       <x:color rgb="FF0B1F33"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF101820"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -72,15 +84,34 @@
         <x:fgColor rgb="FF0B1F33"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -114,11 +145,51 @@
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MaritimeWorkforceTable" displayName="MaritimeWorkforceTable" ref="A1:P7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="16">
+    <x:tableColumn id="1" name="Workforce Record ID"/>
+    <x:tableColumn id="2" name="Programme / Institution"/>
+    <x:tableColumn id="3" name="Record Type"/>
+    <x:tableColumn id="4" name="Country"/>
+    <x:tableColumn id="5" name="State / Territory"/>
+    <x:tableColumn id="6" name="Designation Year"/>
+    <x:tableColumn id="7" name="Institution Count"/>
+    <x:tableColumn id="8" name="Facility Count"/>
+    <x:tableColumn id="9" name="Annual Trainees"/>
+    <x:tableColumn id="10" name="Cohort Trainees"/>
+    <x:tableColumn id="11" name="Designation Term (Years)"/>
+    <x:tableColumn id="12" name="Capability / Role"/>
+    <x:tableColumn id="13" name="Status"/>
+    <x:tableColumn id="14" name="Source ID"/>
+    <x:tableColumn id="15" name="Source URL"/>
+    <x:tableColumn id="16" name="Notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1433,6 +1504,56 @@
         <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>ANN134_001</x:v>
+      </x:c>
+      <x:c r="B21" t="str"/>
+      <x:c r="C21" t="str">
+        <x:v>Seaspan awarded submarine maintenance contract extension by Babcock Canada through 2032</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>COMP_SEASPAN_ULC</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>PROG_SEA_VISSC</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Contract extension</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Babcock Canada; Royal Canadian Navy; Victoria-class submarines; Victoria Shipyards</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>ANN134_002</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Arctic LNG 2 seeks USD 1.02bn from Hanwha Ocean over terminated carrier contracts</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Arbitration / contract dispute</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>NOVATEK; Hanwha Ocean; Sovcomflot; MOL; Arc7 LNG carriers; sanctions</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1974,6 +2095,57 @@
       </x:c>
       <x:c r="E31" t="str">
         <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>SRC134_004</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Seaspan</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Seaspan awarded a Babcock Canada submarine-maintenance contract extension through 2032.</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>MARAD adds 16 maritime training institutions, taking the network to 48 institutions and 87 facilities.</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Arctic LNG 2 seeks USD 1.02 billion / KRW 1.37 trillion at SIAC over terminated Arc7 LNG-carrier contracts.</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>2026-09-10</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2785,6 +2957,343 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF1F4E78"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="38" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="42" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="52" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>Workforce Record ID</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>Programme / Institution</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>Record Type</x:v>
+      </x:c>
+      <x:c r="D1" s="24" t="str">
+        <x:v>Country</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>State / Territory</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>Designation Year</x:v>
+      </x:c>
+      <x:c r="G1" s="24" t="str">
+        <x:v>Institution Count</x:v>
+      </x:c>
+      <x:c r="H1" s="24" t="str">
+        <x:v>Facility Count</x:v>
+      </x:c>
+      <x:c r="I1" s="24" t="str">
+        <x:v>Annual Trainees</x:v>
+      </x:c>
+      <x:c r="J1" s="24" t="str">
+        <x:v>Cohort Trainees</x:v>
+      </x:c>
+      <x:c r="K1" s="24" t="str">
+        <x:v>Designation Term (Years)</x:v>
+      </x:c>
+      <x:c r="L1" s="24" t="str">
+        <x:v>Capability / Role</x:v>
+      </x:c>
+      <x:c r="M1" s="24" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="N1" s="24" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="O1" s="24" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+      <x:c r="P1" s="24" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="28" t="str">
+        <x:v>MWF134_001</x:v>
+      </x:c>
+      <x:c r="B2" s="28" t="str">
+        <x:v>MARAD Centers of Excellence for Domestic Maritime Workforce Training</x:v>
+      </x:c>
+      <x:c r="C2" s="28" t="str">
+        <x:v>Programme aggregate</x:v>
+      </x:c>
+      <x:c r="D2" s="28" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E2" s="28" t="str">
+        <x:v>Nationwide</x:v>
+      </x:c>
+      <x:c r="F2" s="28" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="G2" s="28" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H2" s="28" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="I2" s="28" t="n">
+        <x:v>58000</x:v>
+      </x:c>
+      <x:c r="J2" s="28" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="K2" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L2" s="28" t="str">
+        <x:v>Mariner, shipbuilding and maritime technical workforce training</x:v>
+      </x:c>
+      <x:c r="M2" s="28" t="str">
+        <x:v>Active / expanded</x:v>
+      </x:c>
+      <x:c r="N2" s="28" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="O2" s="28" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="P2" s="28" t="str">
+        <x:v>Sixteen new institutions; cohort trainees are approximate and refer to the newly added group.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="28" t="str">
+        <x:v>MWF134_002</x:v>
+      </x:c>
+      <x:c r="B3" s="28" t="str">
+        <x:v>University of Michigan Department of Naval Architecture and Marine Engineering</x:v>
+      </x:c>
+      <x:c r="C3" s="28" t="str">
+        <x:v>Designated institution</x:v>
+      </x:c>
+      <x:c r="D3" s="28" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E3" s="28" t="str">
+        <x:v>Michigan</x:v>
+      </x:c>
+      <x:c r="F3" s="28" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="G3" s="28" t="str"/>
+      <x:c r="H3" s="28" t="str"/>
+      <x:c r="I3" s="28" t="str"/>
+      <x:c r="J3" s="28" t="str"/>
+      <x:c r="K3" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L3" s="28" t="str">
+        <x:v>Naval architecture and marine engineering education</x:v>
+      </x:c>
+      <x:c r="M3" s="28" t="str">
+        <x:v>Designated</x:v>
+      </x:c>
+      <x:c r="N3" s="28" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="O3" s="28" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="P3" s="28" t="str">
+        <x:v>One of five named institutions captured from article.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="28" t="str">
+        <x:v>MWF134_003</x:v>
+      </x:c>
+      <x:c r="B4" s="28" t="str">
+        <x:v>Northwest Maritime Center</x:v>
+      </x:c>
+      <x:c r="C4" s="28" t="str">
+        <x:v>Designated institution</x:v>
+      </x:c>
+      <x:c r="D4" s="28" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E4" s="28" t="str">
+        <x:v>Washington</x:v>
+      </x:c>
+      <x:c r="F4" s="28" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="G4" s="28" t="str"/>
+      <x:c r="H4" s="28" t="str"/>
+      <x:c r="I4" s="28" t="str"/>
+      <x:c r="J4" s="28" t="str"/>
+      <x:c r="K4" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L4" s="28" t="str">
+        <x:v>Maritime workforce training</x:v>
+      </x:c>
+      <x:c r="M4" s="28" t="str">
+        <x:v>Designated</x:v>
+      </x:c>
+      <x:c r="N4" s="28" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="O4" s="28" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="P4" s="28" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="28" t="str">
+        <x:v>MWF134_004</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="str">
+        <x:v>Chapman School of Seamanship</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="str">
+        <x:v>Designated institution</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="str">
+        <x:v>Florida</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="str"/>
+      <x:c r="H5" s="28" t="str"/>
+      <x:c r="I5" s="28" t="str"/>
+      <x:c r="J5" s="28" t="str"/>
+      <x:c r="K5" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L5" s="28" t="str">
+        <x:v>Seamanship and mariner training</x:v>
+      </x:c>
+      <x:c r="M5" s="28" t="str">
+        <x:v>Designated</x:v>
+      </x:c>
+      <x:c r="N5" s="28" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="O5" s="28" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="P5" s="28" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="28" t="str">
+        <x:v>MWF134_005</x:v>
+      </x:c>
+      <x:c r="B6" s="28" t="str">
+        <x:v>Bunker Hill Community College</x:v>
+      </x:c>
+      <x:c r="C6" s="28" t="str">
+        <x:v>Designated institution</x:v>
+      </x:c>
+      <x:c r="D6" s="28" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E6" s="28" t="str">
+        <x:v>Massachusetts</x:v>
+      </x:c>
+      <x:c r="F6" s="28" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="G6" s="28" t="str"/>
+      <x:c r="H6" s="28" t="str"/>
+      <x:c r="I6" s="28" t="str"/>
+      <x:c r="J6" s="28" t="str"/>
+      <x:c r="K6" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L6" s="28" t="str">
+        <x:v>Maritime workforce training</x:v>
+      </x:c>
+      <x:c r="M6" s="28" t="str">
+        <x:v>Designated</x:v>
+      </x:c>
+      <x:c r="N6" s="28" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="O6" s="28" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="P6" s="28" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="28" t="str">
+        <x:v>MWF134_006</x:v>
+      </x:c>
+      <x:c r="B7" s="28" t="str">
+        <x:v>Webb Institute</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="str">
+        <x:v>Designated institution</x:v>
+      </x:c>
+      <x:c r="D7" s="28" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E7" s="28" t="str">
+        <x:v>New York</x:v>
+      </x:c>
+      <x:c r="F7" s="28" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="G7" s="28" t="str"/>
+      <x:c r="H7" s="28" t="str"/>
+      <x:c r="I7" s="28" t="str"/>
+      <x:c r="J7" s="28" t="str"/>
+      <x:c r="K7" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L7" s="28" t="str">
+        <x:v>Naval architecture and marine engineering education</x:v>
+      </x:c>
+      <x:c r="M7" s="28" t="str">
+        <x:v>Designated</x:v>
+      </x:c>
+      <x:c r="N7" s="28" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="O7" s="28" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="P7" s="28" t="str">
+        <x:v>Only five of sixteen newly designated institutions are named in the article; full roster pending primary MARAD verification.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ad9b5899314090"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -4975,6 +5484,39 @@
         <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Arctic LNG 2 Arc7 LNG Carrier Programme</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Energy project</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Arctic LNG 2 LLC</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>COMP_HANWHA_OCEAN</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Arc7 icebreaking LNG carriers</x:v>
+      </x:c>
+      <x:c r="H22" t="str"/>
+      <x:c r="I22" t="str">
+        <x:v>Mixed / disputed; three Sovcomflot orders canceled</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>South Korea → Russian Arctic</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5464,6 +6006,62 @@
       </x:c>
       <x:c r="D34" t="str">
         <x:v>UAE Coast Guard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Project customer / claimant</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>LNG export fleet requirement</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>COMP_HANWHA_OCEAN</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Shipbuilder / respondent</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Six-carrier programme</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>COMP_SOVCOMFLOT</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Buyer / operator exposure</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>Three orders reported canceled due to sanctions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>COMP_MOL</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Buyer / operator exposure</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Three MOL-linked ships reported in programme</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7054,6 +7652,68 @@
         <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>CON134_001</x:v>
+      </x:c>
+      <x:c r="B13" t="str"/>
+      <x:c r="C13" t="str">
+        <x:v>PROG_SEA_VISSC</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Babcock Canada / Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>COMP_SEASPAN_ULC</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Undisclosed</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>Submarine maintenance support extension through 2032</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>Contract extension</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>Official headline verified; announcement date and detailed scope not captured</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>CON134_002</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Arctic LNG 2 LLC</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>COMP_HANWHA_OCEAN</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>USD 1.02bn claim / KRW 1.37tn</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Damages claim over terminated Arc7 LNG-carrier shipbuilding contracts</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>International arbitration</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>Pending at Singapore International Arbitration Centre</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/12_defence_shipbuilding.xlsx
+++ b/data/12_defence_shipbuilding.xlsx
@@ -2,21 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defence Companies" sheetId="1" r:id="Rc5bf986753914697"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="2" r:id="R9093970298e84ddf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Facilities" sheetId="3" r:id="Rd017ec8067334c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Capabilities" sheetId="4" r:id="Rc425a36ae76d4b62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="5" r:id="R99392d7ebcbf48fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Participants" sheetId="6" r:id="R8f42584db1014144"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Vessels" sheetId="7" r:id="R53cc3979b37e40ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="8" r:id="R323227e176384a6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales &amp; Delivery Routes" sheetId="9" r:id="Rcbcddd8a96094213"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announcements" sheetId="10" r:id="R7a0e8af8ec3044ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="R1cc1847f3f9045eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="12" r:id="R6cd3ea34420f4135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform Classes" sheetId="13" r:id="Rfdb619aacd934d94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Status History" sheetId="14" r:id="R076d1feee9cf436e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maritime Workforce" sheetId="15" r:id="Rdad202afbf6d4f61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defence Companies" sheetId="1" r:id="R54ae9faf2b474006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="2" r:id="R2d29bbaea92c4241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Facilities" sheetId="3" r:id="Rfd7ef2fd7c284ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Capabilities" sheetId="4" r:id="Rd6d4bf98e0c14643"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="5" r:id="R80ec610710cd40b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Participants" sheetId="6" r:id="R6ba5817d465e4249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Vessels" sheetId="7" r:id="Re334253c9a2a4e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="8" r:id="R6f2cc80169fc4111"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales &amp; Delivery Routes" sheetId="9" r:id="R0e5d6e20c6ce4859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announcements" sheetId="10" r:id="R6a36be628caa4e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="Rffc8e124f6354546"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="12" r:id="Rcaee9e4085c145cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform Classes" sheetId="13" r:id="R38a546632d4445b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Status History" sheetId="14" r:id="Rbbfc6926670445c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -50,19 +49,8 @@
       <x:color rgb="FF0B1F33"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF101820"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -84,34 +72,15 @@
         <x:fgColor rgb="FF0B1F33"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF17365D"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="2">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD9E2F3"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD9E2F3"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD9E2F3"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD9E2F3"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -145,51 +114,11 @@
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MaritimeWorkforceTable" displayName="MaritimeWorkforceTable" ref="A1:P7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="16">
-    <x:tableColumn id="1" name="Workforce Record ID"/>
-    <x:tableColumn id="2" name="Programme / Institution"/>
-    <x:tableColumn id="3" name="Record Type"/>
-    <x:tableColumn id="4" name="Country"/>
-    <x:tableColumn id="5" name="State / Territory"/>
-    <x:tableColumn id="6" name="Designation Year"/>
-    <x:tableColumn id="7" name="Institution Count"/>
-    <x:tableColumn id="8" name="Facility Count"/>
-    <x:tableColumn id="9" name="Annual Trainees"/>
-    <x:tableColumn id="10" name="Cohort Trainees"/>
-    <x:tableColumn id="11" name="Designation Term (Years)"/>
-    <x:tableColumn id="12" name="Capability / Role"/>
-    <x:tableColumn id="13" name="Status"/>
-    <x:tableColumn id="14" name="Source ID"/>
-    <x:tableColumn id="15" name="Source URL"/>
-    <x:tableColumn id="16" name="Notes"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1504,56 +1433,6 @@
         <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>ANN134_001</x:v>
-      </x:c>
-      <x:c r="B21" t="str"/>
-      <x:c r="C21" t="str">
-        <x:v>Seaspan awarded submarine maintenance contract extension by Babcock Canada through 2032</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>COMP_SEASPAN_ULC</x:v>
-      </x:c>
-      <x:c r="E21" t="str">
-        <x:v>PROG_SEA_VISSC</x:v>
-      </x:c>
-      <x:c r="F21" t="str">
-        <x:v>Contract extension</x:v>
-      </x:c>
-      <x:c r="G21" t="str">
-        <x:v>Babcock Canada; Royal Canadian Navy; Victoria-class submarines; Victoria Shipyards</x:v>
-      </x:c>
-      <x:c r="H21" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>ANN134_002</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>Arctic LNG 2 seeks USD 1.02bn from Hanwha Ocean over terminated carrier contracts</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
-        <x:v>Arbitration / contract dispute</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>NOVATEK; Hanwha Ocean; Sovcomflot; MOL; Arc7 LNG carriers; sanctions</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2095,57 +1974,6 @@
       </x:c>
       <x:c r="E31" t="str">
         <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="str">
-        <x:v>SRC134_004</x:v>
-      </x:c>
-      <x:c r="B32" t="str">
-        <x:v>Seaspan</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>Seaspan awarded a Babcock Canada submarine-maintenance contract extension through 2032.</x:v>
-      </x:c>
-      <x:c r="D32" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
-      </x:c>
-      <x:c r="E32" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="B33" t="str">
-        <x:v>gCaptain</x:v>
-      </x:c>
-      <x:c r="C33" t="str">
-        <x:v>MARAD adds 16 maritime training institutions, taking the network to 48 institutions and 87 facilities.</x:v>
-      </x:c>
-      <x:c r="D33" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
-      </x:c>
-      <x:c r="E33" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-      <x:c r="B34" t="str">
-        <x:v>Reuters</x:v>
-      </x:c>
-      <x:c r="C34" t="str">
-        <x:v>Arctic LNG 2 seeks USD 1.02 billion / KRW 1.37 trillion at SIAC over terminated Arc7 LNG-carrier contracts.</x:v>
-      </x:c>
-      <x:c r="D34" t="str">
-        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
-      </x:c>
-      <x:c r="E34" t="str">
-        <x:v>2026-09-10</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2957,343 +2785,6 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF1F4E78"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="38" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="42" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="52" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="24" t="str">
-        <x:v>Workforce Record ID</x:v>
-      </x:c>
-      <x:c r="B1" s="24" t="str">
-        <x:v>Programme / Institution</x:v>
-      </x:c>
-      <x:c r="C1" s="24" t="str">
-        <x:v>Record Type</x:v>
-      </x:c>
-      <x:c r="D1" s="24" t="str">
-        <x:v>Country</x:v>
-      </x:c>
-      <x:c r="E1" s="24" t="str">
-        <x:v>State / Territory</x:v>
-      </x:c>
-      <x:c r="F1" s="24" t="str">
-        <x:v>Designation Year</x:v>
-      </x:c>
-      <x:c r="G1" s="24" t="str">
-        <x:v>Institution Count</x:v>
-      </x:c>
-      <x:c r="H1" s="24" t="str">
-        <x:v>Facility Count</x:v>
-      </x:c>
-      <x:c r="I1" s="24" t="str">
-        <x:v>Annual Trainees</x:v>
-      </x:c>
-      <x:c r="J1" s="24" t="str">
-        <x:v>Cohort Trainees</x:v>
-      </x:c>
-      <x:c r="K1" s="24" t="str">
-        <x:v>Designation Term (Years)</x:v>
-      </x:c>
-      <x:c r="L1" s="24" t="str">
-        <x:v>Capability / Role</x:v>
-      </x:c>
-      <x:c r="M1" s="24" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="N1" s="24" t="str">
-        <x:v>Source ID</x:v>
-      </x:c>
-      <x:c r="O1" s="24" t="str">
-        <x:v>Source URL</x:v>
-      </x:c>
-      <x:c r="P1" s="24" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="28" t="str">
-        <x:v>MWF134_001</x:v>
-      </x:c>
-      <x:c r="B2" s="28" t="str">
-        <x:v>MARAD Centers of Excellence for Domestic Maritime Workforce Training</x:v>
-      </x:c>
-      <x:c r="C2" s="28" t="str">
-        <x:v>Programme aggregate</x:v>
-      </x:c>
-      <x:c r="D2" s="28" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E2" s="28" t="str">
-        <x:v>Nationwide</x:v>
-      </x:c>
-      <x:c r="F2" s="28" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="G2" s="28" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H2" s="28" t="n">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="I2" s="28" t="n">
-        <x:v>58000</x:v>
-      </x:c>
-      <x:c r="J2" s="28" t="n">
-        <x:v>20000</x:v>
-      </x:c>
-      <x:c r="K2" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L2" s="28" t="str">
-        <x:v>Mariner, shipbuilding and maritime technical workforce training</x:v>
-      </x:c>
-      <x:c r="M2" s="28" t="str">
-        <x:v>Active / expanded</x:v>
-      </x:c>
-      <x:c r="N2" s="28" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="O2" s="28" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
-      </x:c>
-      <x:c r="P2" s="28" t="str">
-        <x:v>Sixteen new institutions; cohort trainees are approximate and refer to the newly added group.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="28" t="str">
-        <x:v>MWF134_002</x:v>
-      </x:c>
-      <x:c r="B3" s="28" t="str">
-        <x:v>University of Michigan Department of Naval Architecture and Marine Engineering</x:v>
-      </x:c>
-      <x:c r="C3" s="28" t="str">
-        <x:v>Designated institution</x:v>
-      </x:c>
-      <x:c r="D3" s="28" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E3" s="28" t="str">
-        <x:v>Michigan</x:v>
-      </x:c>
-      <x:c r="F3" s="28" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="G3" s="28" t="str"/>
-      <x:c r="H3" s="28" t="str"/>
-      <x:c r="I3" s="28" t="str"/>
-      <x:c r="J3" s="28" t="str"/>
-      <x:c r="K3" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L3" s="28" t="str">
-        <x:v>Naval architecture and marine engineering education</x:v>
-      </x:c>
-      <x:c r="M3" s="28" t="str">
-        <x:v>Designated</x:v>
-      </x:c>
-      <x:c r="N3" s="28" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="O3" s="28" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
-      </x:c>
-      <x:c r="P3" s="28" t="str">
-        <x:v>One of five named institutions captured from article.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="28" t="str">
-        <x:v>MWF134_003</x:v>
-      </x:c>
-      <x:c r="B4" s="28" t="str">
-        <x:v>Northwest Maritime Center</x:v>
-      </x:c>
-      <x:c r="C4" s="28" t="str">
-        <x:v>Designated institution</x:v>
-      </x:c>
-      <x:c r="D4" s="28" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E4" s="28" t="str">
-        <x:v>Washington</x:v>
-      </x:c>
-      <x:c r="F4" s="28" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="G4" s="28" t="str"/>
-      <x:c r="H4" s="28" t="str"/>
-      <x:c r="I4" s="28" t="str"/>
-      <x:c r="J4" s="28" t="str"/>
-      <x:c r="K4" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L4" s="28" t="str">
-        <x:v>Maritime workforce training</x:v>
-      </x:c>
-      <x:c r="M4" s="28" t="str">
-        <x:v>Designated</x:v>
-      </x:c>
-      <x:c r="N4" s="28" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="O4" s="28" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
-      </x:c>
-      <x:c r="P4" s="28" t="str"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="28" t="str">
-        <x:v>MWF134_004</x:v>
-      </x:c>
-      <x:c r="B5" s="28" t="str">
-        <x:v>Chapman School of Seamanship</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="str">
-        <x:v>Designated institution</x:v>
-      </x:c>
-      <x:c r="D5" s="28" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E5" s="28" t="str">
-        <x:v>Florida</x:v>
-      </x:c>
-      <x:c r="F5" s="28" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="G5" s="28" t="str"/>
-      <x:c r="H5" s="28" t="str"/>
-      <x:c r="I5" s="28" t="str"/>
-      <x:c r="J5" s="28" t="str"/>
-      <x:c r="K5" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L5" s="28" t="str">
-        <x:v>Seamanship and mariner training</x:v>
-      </x:c>
-      <x:c r="M5" s="28" t="str">
-        <x:v>Designated</x:v>
-      </x:c>
-      <x:c r="N5" s="28" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="O5" s="28" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
-      </x:c>
-      <x:c r="P5" s="28" t="str"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="28" t="str">
-        <x:v>MWF134_005</x:v>
-      </x:c>
-      <x:c r="B6" s="28" t="str">
-        <x:v>Bunker Hill Community College</x:v>
-      </x:c>
-      <x:c r="C6" s="28" t="str">
-        <x:v>Designated institution</x:v>
-      </x:c>
-      <x:c r="D6" s="28" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E6" s="28" t="str">
-        <x:v>Massachusetts</x:v>
-      </x:c>
-      <x:c r="F6" s="28" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="G6" s="28" t="str"/>
-      <x:c r="H6" s="28" t="str"/>
-      <x:c r="I6" s="28" t="str"/>
-      <x:c r="J6" s="28" t="str"/>
-      <x:c r="K6" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L6" s="28" t="str">
-        <x:v>Maritime workforce training</x:v>
-      </x:c>
-      <x:c r="M6" s="28" t="str">
-        <x:v>Designated</x:v>
-      </x:c>
-      <x:c r="N6" s="28" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="O6" s="28" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
-      </x:c>
-      <x:c r="P6" s="28" t="str"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="28" t="str">
-        <x:v>MWF134_006</x:v>
-      </x:c>
-      <x:c r="B7" s="28" t="str">
-        <x:v>Webb Institute</x:v>
-      </x:c>
-      <x:c r="C7" s="28" t="str">
-        <x:v>Designated institution</x:v>
-      </x:c>
-      <x:c r="D7" s="28" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="E7" s="28" t="str">
-        <x:v>New York</x:v>
-      </x:c>
-      <x:c r="F7" s="28" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="G7" s="28" t="str"/>
-      <x:c r="H7" s="28" t="str"/>
-      <x:c r="I7" s="28" t="str"/>
-      <x:c r="J7" s="28" t="str"/>
-      <x:c r="K7" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L7" s="28" t="str">
-        <x:v>Naval architecture and marine engineering education</x:v>
-      </x:c>
-      <x:c r="M7" s="28" t="str">
-        <x:v>Designated</x:v>
-      </x:c>
-      <x:c r="N7" s="28" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="O7" s="28" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
-      </x:c>
-      <x:c r="P7" s="28" t="str">
-        <x:v>Only five of sixteen newly designated institutions are named in the article; full roster pending primary MARAD verification.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ad9b5899314090"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -3887,6 +3378,35 @@
       </x:c>
       <x:c r="I20" t="str">
         <x:v>https://edgegroup.ae/news/edge-announces-launch-first-class-corvette-angolan-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="8" t="str">
+        <x:v>YARD_QINGDAO_BEIHAI</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="str">
+        <x:v>COMP_CSSC</x:v>
+      </x:c>
+      <x:c r="C21" s="8" t="str">
+        <x:v>Qingdao Beihai Shipbuilding</x:v>
+      </x:c>
+      <x:c r="D21" s="8" t="str">
+        <x:v>Qingdao, Shandong</x:v>
+      </x:c>
+      <x:c r="E21" s="8" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="F21" s="8" t="str">
+        <x:v>Commercial shipbuilding / repair</x:v>
+      </x:c>
+      <x:c r="G21" s="8" t="str">
+        <x:v>Bulk-carrier construction and commercial ship repair</x:v>
+      </x:c>
+      <x:c r="H21" s="8" t="str">
+        <x:v>Active / incident recovery</x:v>
+      </x:c>
+      <x:c r="I21" s="8" t="str">
+        <x:v>https://www.reuters.com/world/asia-pacific/fire-cargo-vessel-china-shipyard-causes-major-casualties-state-media-reports-2026-09-10/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5484,39 +5004,6 @@
         <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>Arctic LNG 2 Arc7 LNG Carrier Programme</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>Energy project</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>Arctic LNG 2 LLC</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>COMP_HANWHA_OCEAN</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>Arc7 icebreaking LNG carriers</x:v>
-      </x:c>
-      <x:c r="H22" t="str"/>
-      <x:c r="I22" t="str">
-        <x:v>Mixed / disputed; three Sovcomflot orders canceled</x:v>
-      </x:c>
-      <x:c r="J22" t="str">
-        <x:v>South Korea → Russian Arctic</x:v>
-      </x:c>
-      <x:c r="K22" t="str">
-        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6006,62 +5493,6 @@
       </x:c>
       <x:c r="D34" t="str">
         <x:v>UAE Coast Guard</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" t="str">
-        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
-      </x:c>
-      <x:c r="B35" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="C35" t="str">
-        <x:v>Project customer / claimant</x:v>
-      </x:c>
-      <x:c r="D35" t="str">
-        <x:v>LNG export fleet requirement</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" t="str">
-        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
-      </x:c>
-      <x:c r="B36" t="str">
-        <x:v>COMP_HANWHA_OCEAN</x:v>
-      </x:c>
-      <x:c r="C36" t="str">
-        <x:v>Shipbuilder / respondent</x:v>
-      </x:c>
-      <x:c r="D36" t="str">
-        <x:v>Six-carrier programme</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="str">
-        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
-      </x:c>
-      <x:c r="B37" t="str">
-        <x:v>COMP_SOVCOMFLOT</x:v>
-      </x:c>
-      <x:c r="C37" t="str">
-        <x:v>Buyer / operator exposure</x:v>
-      </x:c>
-      <x:c r="D37" t="str">
-        <x:v>Three orders reported canceled due to sanctions</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="str">
-        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
-      </x:c>
-      <x:c r="B38" t="str">
-        <x:v>COMP_MOL</x:v>
-      </x:c>
-      <x:c r="C38" t="str">
-        <x:v>Buyer / operator exposure</x:v>
-      </x:c>
-      <x:c r="D38" t="str">
-        <x:v>Three MOL-linked ships reported in programme</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7652,68 +7083,6 @@
         <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>CON134_001</x:v>
-      </x:c>
-      <x:c r="B13" t="str"/>
-      <x:c r="C13" t="str">
-        <x:v>PROG_SEA_VISSC</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>Babcock Canada / Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>COMP_SEASPAN_ULC</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>Undisclosed</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>Submarine maintenance support extension through 2032</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>Contract extension</x:v>
-      </x:c>
-      <x:c r="I13" t="str">
-        <x:v>Official headline verified; announcement date and detailed scope not captured</x:v>
-      </x:c>
-      <x:c r="J13" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>CON134_002</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>Arctic LNG 2 LLC</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>COMP_HANWHA_OCEAN</x:v>
-      </x:c>
-      <x:c r="F14" t="str">
-        <x:v>USD 1.02bn claim / KRW 1.37tn</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
-        <x:v>Damages claim over terminated Arc7 LNG-carrier shipbuilding contracts</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>International arbitration</x:v>
-      </x:c>
-      <x:c r="I14" t="str">
-        <x:v>Pending at Singapore International Arbitration Centre</x:v>
-      </x:c>
-      <x:c r="J14" t="str">
-        <x:v>https://www.reuters.com/business/energy/russias-arctic-lng-2-seeks-1-billion-damages-south-koreas-hanwha-2026-09-08/</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/12_defence_shipbuilding.xlsx
+++ b/data/12_defence_shipbuilding.xlsx
@@ -904,1081 +904,1157 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Announcement ID</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>Headline</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="str">
-        <x:v>Primary Entity ID</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="str">
-        <x:v>Programme ID</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="str">
-        <x:v>Event Type</x:v>
-      </x:c>
-      <x:c r="G1" s="4" t="str">
-        <x:v>Linked Entities / Topics</x:v>
-      </x:c>
-      <x:c r="H1" s="4" t="str">
-        <x:v>Source URL</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="8" t="str">
-        <x:v>ANN_001</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="str">
-        <x:v>2024-05-20</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="str">
-        <x:v>MAESTRAL formalised and €400m UAE Coast Guard order announced</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="str">
-        <x:v>COMP_MAESTRAL</x:v>
-      </x:c>
-      <x:c r="E2" s="8" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="F2" s="8" t="str">
-        <x:v>JV / contract</x:v>
-      </x:c>
-      <x:c r="G2" s="8" t="str">
-        <x:v>EDGE; Fincantieri; UAE Coast Guard; P51MR</x:v>
-      </x:c>
-      <x:c r="H2" s="8" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="8" t="str">
-        <x:v>ANN_002</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="str">
-        <x:v>2026-02-03</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="str">
-        <x:v>ADSB launches first Al-Dorra-class 62m vessel for Kuwait</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="str">
-        <x:v>COMP_ADSB</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="str">
-        <x:v>PROG_ADSB_ALDORRA</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="str">
-        <x:v>Launch / export</x:v>
-      </x:c>
-      <x:c r="G3" s="8" t="str">
-        <x:v>ADSB; EDGE; Kuwait; Abu Dhabi shipyard</x:v>
-      </x:c>
-      <x:c r="H3" s="8" t="str">
-        <x:v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="8" t="str">
-        <x:v>ANN_003</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>2025-03-08</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
-        <x:v>Canada awards River-class destroyer implementation contract</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="str">
-        <x:v>COMP_IRVING</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="str">
-        <x:v>PROG_RCD</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="str">
-        <x:v>Contract</x:v>
-      </x:c>
-      <x:c r="G4" s="8" t="str">
-        <x:v>Irving; Halifax Shipyard; RCN; Lockheed Martin Canada; BAE Systems</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/03/government-of-canada-announces-contract-award-for-the-construction-of-the-river-class-destroyers-for-the-royal-canadian-navy.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="8" t="str">
-        <x:v>ANN_004</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>2026-05-26</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
-        <x:v>Seaspan reports one year of polar icebreaker progress</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="str">
-        <x:v>COMP_SEASPAN_ULC</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="str">
-        <x:v>PROG_SEA_POLAR</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="str">
-        <x:v>Construction milestone</x:v>
-      </x:c>
-      <x:c r="G5" s="8" t="str">
-        <x:v>Vancouver Shipyards; Victoria Shipyards; Ark Road; CCG</x:v>
-      </x:c>
-      <x:c r="H5" s="8" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-celebrates-one-year-of-progress-on-the-heavy-polar-icebreaker/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="8" t="str">
-        <x:v>ANN_005</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>2026-01-07</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
-        <x:v>Seaspan signs ASC agreements with Bollinger and Rauma</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="str">
-        <x:v>COMP_SEASPAN_ULC</x:v>
-      </x:c>
-      <x:c r="E6" s="8" t="str">
-        <x:v>PROG_US_ASC_BOLL</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="str">
-        <x:v>Design / build partnership</x:v>
-      </x:c>
-      <x:c r="G6" s="8" t="str">
-        <x:v>Seaspan; Bollinger; Rauma; Aker Arctic; USCG</x:v>
-      </x:c>
-      <x:c r="H6" s="8" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-inks-deal-with-bollinger-rauma-for-u-s-coast-guard-asc-program/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="8" t="str">
-        <x:v>ANN_006</x:v>
-      </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>2026-08-24</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
-        <x:v>Davie awarded six Program Icebreakers</x:v>
-      </x:c>
-      <x:c r="D7" s="8" t="str">
-        <x:v>COMP_DAVIE</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="str">
-        <x:v>PROG_DAV_PIB</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str">
-        <x:v>Contract</x:v>
-      </x:c>
-      <x:c r="G7" s="8" t="str">
-        <x:v>Davie; Inocea; Lévis; Canadian Coast Guard</x:v>
-      </x:c>
-      <x:c r="H7" s="8" t="str">
-        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="8" t="str">
-        <x:v>ANN_007</x:v>
-      </x:c>
-      <x:c r="B8" s="8" t="str">
-        <x:v>2026-05-13</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="str">
-        <x:v>Davie Defense states USCG ASC contract finalized</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="str">
-        <x:v>COMP_DAVIE_DEFENSE</x:v>
-      </x:c>
-      <x:c r="E8" s="8" t="str">
-        <x:v>PROG_US_ASC_DAV</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="str">
-        <x:v>Contract</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="str">
-        <x:v>Davie Defense; USCG; Galveston / Port Arthur</x:v>
-      </x:c>
-      <x:c r="H8" s="8" t="str">
-        <x:v>https://www.daviedefense.com/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="8" t="str">
-        <x:v>ANN_008</x:v>
-      </x:c>
-      <x:c r="B9" s="8" t="str">
-        <x:v>2026-03-16</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="str">
-        <x:v>Damen announces three Stan Patrol 5009s for Dutch Caribbean Coast Guard</x:v>
-      </x:c>
-      <x:c r="D9" s="8" t="str">
-        <x:v>COMP_DAMEN</x:v>
-      </x:c>
-      <x:c r="E9" s="8" t="str">
-        <x:v>PROG_DUTCH_CG</x:v>
-      </x:c>
-      <x:c r="F9" s="8" t="str">
-        <x:v>Contract</x:v>
-      </x:c>
-      <x:c r="G9" s="8" t="str">
-        <x:v>Damen; Antalya; Netherlands MoD; Dutch Caribbean Coast Guard</x:v>
-      </x:c>
-      <x:c r="H9" s="8" t="str">
-        <x:v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="8" t="str">
-        <x:v>ANN_009</x:v>
-      </x:c>
-      <x:c r="B10" s="8" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="str">
-        <x:v>SimFer begins Morebaya port commissioning</x:v>
-      </x:c>
-      <x:c r="D10" s="8" t="str">
-        <x:v>COMP_SIMFER</x:v>
-      </x:c>
-      <x:c r="E10" s="8" t="str"/>
-      <x:c r="F10" s="8" t="str">
-        <x:v>Port / rail commissioning</x:v>
-      </x:c>
-      <x:c r="G10" s="8" t="str">
-        <x:v>SimFer; Morebaya; rail spur; WCS port; Guinea; Rio Tinto; CIOH</x:v>
-      </x:c>
-      <x:c r="H10" s="8" t="str">
-        <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="8" t="str">
-        <x:v>ANN_010</x:v>
-      </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
-        <x:v>APM Terminals enters exclusive negotiations over Badagry deepsea port</x:v>
-      </x:c>
-      <x:c r="D11" s="8" t="str">
-        <x:v>COMP_BADAGRY_PORT_DEV</x:v>
-      </x:c>
-      <x:c r="E11" s="8" t="str"/>
-      <x:c r="F11" s="8" t="str">
-        <x:v>Port development</x:v>
-      </x:c>
-      <x:c r="G11" s="8" t="str">
-        <x:v>APM Terminals; Badagry; Nigeria; Apapa; Onne</x:v>
-      </x:c>
-      <x:c r="H11" s="8" t="str">
-        <x:v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>ANN_AOPS_01</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>2025-08-21</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>RCN accepts sixth and final AOPS, HMCS Robert Hampton Gray</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>COMP_IRVING</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>PROG_AOPS_RCN</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>Delivery</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>Irving; Halifax Shipyard; RCN; Robert Hampton Gray</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>ANN_AOPS_02</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>2026-04-29</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>Canadian Coast Guard launches CCGS Donjek</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>COMP_IRVING</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>PROG_AOPS_CCG</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>Launch</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>Irving; Halifax Shipyard; CCG; Donjek; Sermilik</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>ANN_UAE_01</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>2021-05-18</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>ADSB awarded AED3.5bn contract for four FALAJ 3 vessels</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>COMP_ADSB</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>PROG_UAE_FALAJ3</x:v>
-      </x:c>
-      <x:c r="F14" t="str">
-        <x:v>Contract</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
-        <x:v>ADSB; UAE Navy; UAE Ministry of Defence; FALAJ3</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>https://edgegroup.ae/share/pdf/news/173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>ANN_UAE_02</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>2025-01-14</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>ADSB launches first FALAJ 3 vessel</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>COMP_ADSB</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
-        <x:v>PROG_UAE_FALAJ3</x:v>
-      </x:c>
-      <x:c r="F15" t="str">
-        <x:v>Launch</x:v>
-      </x:c>
-      <x:c r="G15" t="str">
-        <x:v>ADSB; UAE Navy; first FALAJ3</x:v>
-      </x:c>
-      <x:c r="H15" t="str">
-        <x:v>https://edgegroup.ae/news/adsb-launches-first-vessel-prestigious-falaj-3-programme</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>ANN_UAE_03</x:v>
-      </x:c>
-      <x:c r="B16" t="str">
-        <x:v>2025-02-19</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>ALTAF commissioned as first FALAJ 3 missile boat</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>COMP_ADSB</x:v>
-      </x:c>
-      <x:c r="E16" t="str">
-        <x:v>PROG_UAE_FALAJ3</x:v>
-      </x:c>
-      <x:c r="F16" t="str">
-        <x:v>Commissioning</x:v>
-      </x:c>
-      <x:c r="G16" t="str">
-        <x:v>ALTAF; ADSB; EDGE; UAE Navy</x:v>
-      </x:c>
-      <x:c r="H16" t="str">
-        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>ANN_UAE_04</x:v>
-      </x:c>
-      <x:c r="B17" t="str">
-        <x:v>2023-10-21</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>Naval Group delivers Bani Yas to UAE Navy</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>COMP_NAVAL_GROUP</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
-        <x:v>PROG_UAE_BANIYAS</x:v>
-      </x:c>
-      <x:c r="F17" t="str">
-        <x:v>Delivery</x:v>
-      </x:c>
-      <x:c r="G17" t="str">
-        <x:v>Bani Yas; Lorient; UAE Navy</x:v>
-      </x:c>
-      <x:c r="H17" t="str">
-        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>ANN_UAE_05</x:v>
-      </x:c>
-      <x:c r="B18" t="str">
-        <x:v>2024-06-27</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>Naval Group delivers Al Emarat to UAE Navy</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>COMP_NAVAL_GROUP</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
-        <x:v>PROG_UAE_BANIYAS</x:v>
-      </x:c>
-      <x:c r="F18" t="str">
-        <x:v>Delivery</x:v>
-      </x:c>
-      <x:c r="G18" t="str">
-        <x:v>Al Emarat; Lorient; UAE Navy</x:v>
-      </x:c>
-      <x:c r="H18" t="str">
-        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>ANN_UAE_06</x:v>
-      </x:c>
-      <x:c r="B19" t="str">
-        <x:v>2017-02-20</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>UAE commissions Al Hili, sixth Baynunah-class corvette</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>COMP_ADSB</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
-        <x:v>PROG_UAE_BAYNUNAH</x:v>
-      </x:c>
-      <x:c r="F19" t="str">
-        <x:v>Commissioning</x:v>
-      </x:c>
-      <x:c r="G19" t="str">
-        <x:v>Al Hili; ADSB; UAE Navy</x:v>
-      </x:c>
-      <x:c r="H19" t="str">
-        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
-        <x:v>ANN_UAE_07</x:v>
-      </x:c>
-      <x:c r="B20" t="str">
-        <x:v>2013-01-08</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>Fincantieri delivers Abu Dhabi corvette and Ghantut patrol vessel</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>COMP_FINCANTIERI</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
-        <x:v>PROG_UAE_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="F20" t="str">
-        <x:v>Delivery</x:v>
-      </x:c>
-      <x:c r="G20" t="str">
-        <x:v>Abu Dhabi; Ghantut; UAE Navy; Muggiano</x:v>
-      </x:c>
-      <x:c r="H20" t="str">
-        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="str">
+        <v>Announcement ID</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C1" s="4" t="str">
+        <v>Headline</v>
+      </c>
+      <c r="D1" s="4" t="str">
+        <v>Primary Entity ID</v>
+      </c>
+      <c r="E1" s="4" t="str">
+        <v>Programme ID</v>
+      </c>
+      <c r="F1" s="4" t="str">
+        <v>Event Type</v>
+      </c>
+      <c r="G1" s="4" t="str">
+        <v>Linked Entities / Topics</v>
+      </c>
+      <c r="H1" s="4" t="str">
+        <v>Source URL</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="str">
+        <v>ANN_001</v>
+      </c>
+      <c r="B2" s="8" t="str">
+        <v>2024-05-20</v>
+      </c>
+      <c r="C2" s="8" t="str">
+        <v>MAESTRAL formalised and €400m UAE Coast Guard order announced</v>
+      </c>
+      <c r="D2" s="8" t="str">
+        <v>COMP_MAESTRAL</v>
+      </c>
+      <c r="E2" s="8" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="F2" s="8" t="str">
+        <v>JV / contract</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <v>EDGE; Fincantieri; UAE Coast Guard; P51MR</v>
+      </c>
+      <c r="H2" s="8" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="str">
+        <v>ANN_002</v>
+      </c>
+      <c r="B3" s="8" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="C3" s="8" t="str">
+        <v>ADSB launches first Al-Dorra-class 62m vessel for Kuwait</v>
+      </c>
+      <c r="D3" s="8" t="str">
+        <v>COMP_ADSB</v>
+      </c>
+      <c r="E3" s="8" t="str">
+        <v>PROG_ADSB_ALDORRA</v>
+      </c>
+      <c r="F3" s="8" t="str">
+        <v>Launch / export</v>
+      </c>
+      <c r="G3" s="8" t="str">
+        <v>ADSB; EDGE; Kuwait; Abu Dhabi shipyard</v>
+      </c>
+      <c r="H3" s="8" t="str">
+        <v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="str">
+        <v>ANN_003</v>
+      </c>
+      <c r="B4" s="8" t="str">
+        <v>2025-03-08</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <v>Canada awards River-class destroyer implementation contract</v>
+      </c>
+      <c r="D4" s="8" t="str">
+        <v>COMP_IRVING</v>
+      </c>
+      <c r="E4" s="8" t="str">
+        <v>PROG_RCD</v>
+      </c>
+      <c r="F4" s="8" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="G4" s="8" t="str">
+        <v>Irving; Halifax Shipyard; RCN; Lockheed Martin Canada; BAE Systems</v>
+      </c>
+      <c r="H4" s="8" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/news/2025/03/government-of-canada-announces-contract-award-for-the-construction-of-the-river-class-destroyers-for-the-royal-canadian-navy.html</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="str">
+        <v>ANN_004</v>
+      </c>
+      <c r="B5" s="8" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <v>Seaspan reports one year of polar icebreaker progress</v>
+      </c>
+      <c r="D5" s="8" t="str">
+        <v>COMP_SEASPAN_ULC</v>
+      </c>
+      <c r="E5" s="8" t="str">
+        <v>PROG_SEA_POLAR</v>
+      </c>
+      <c r="F5" s="8" t="str">
+        <v>Construction milestone</v>
+      </c>
+      <c r="G5" s="8" t="str">
+        <v>Vancouver Shipyards; Victoria Shipyards; Ark Road; CCG</v>
+      </c>
+      <c r="H5" s="8" t="str">
+        <v>https://www.seaspan.com/press-release/seaspan-celebrates-one-year-of-progress-on-the-heavy-polar-icebreaker/</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="str">
+        <v>ANN_005</v>
+      </c>
+      <c r="B6" s="8" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <v>Seaspan signs ASC agreements with Bollinger and Rauma</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <v>COMP_SEASPAN_ULC</v>
+      </c>
+      <c r="E6" s="8" t="str">
+        <v>PROG_US_ASC_BOLL</v>
+      </c>
+      <c r="F6" s="8" t="str">
+        <v>Design / build partnership</v>
+      </c>
+      <c r="G6" s="8" t="str">
+        <v>Seaspan; Bollinger; Rauma; Aker Arctic; USCG</v>
+      </c>
+      <c r="H6" s="8" t="str">
+        <v>https://www.seaspan.com/press-release/seaspan-inks-deal-with-bollinger-rauma-for-u-s-coast-guard-asc-program/</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="str">
+        <v>ANN_006</v>
+      </c>
+      <c r="B7" s="8" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <v>Davie awarded six Program Icebreakers</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <v>COMP_DAVIE</v>
+      </c>
+      <c r="E7" s="8" t="str">
+        <v>PROG_DAV_PIB</v>
+      </c>
+      <c r="F7" s="8" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="G7" s="8" t="str">
+        <v>Davie; Inocea; Lévis; Canadian Coast Guard</v>
+      </c>
+      <c r="H7" s="8" t="str">
+        <v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="str">
+        <v>ANN_007</v>
+      </c>
+      <c r="B8" s="8" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <v>Davie Defense states USCG ASC contract finalized</v>
+      </c>
+      <c r="D8" s="8" t="str">
+        <v>COMP_DAVIE_DEFENSE</v>
+      </c>
+      <c r="E8" s="8" t="str">
+        <v>PROG_US_ASC_DAV</v>
+      </c>
+      <c r="F8" s="8" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="G8" s="8" t="str">
+        <v>Davie Defense; USCG; Galveston / Port Arthur</v>
+      </c>
+      <c r="H8" s="8" t="str">
+        <v>https://www.daviedefense.com/</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="str">
+        <v>ANN_008</v>
+      </c>
+      <c r="B9" s="8" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <v>Damen announces three Stan Patrol 5009s for Dutch Caribbean Coast Guard</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <v>COMP_DAMEN</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <v>PROG_DUTCH_CG</v>
+      </c>
+      <c r="F9" s="8" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="G9" s="8" t="str">
+        <v>Damen; Antalya; Netherlands MoD; Dutch Caribbean Coast Guard</v>
+      </c>
+      <c r="H9" s="8" t="str">
+        <v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="str">
+        <v>ANN_009</v>
+      </c>
+      <c r="B10" s="8" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <v>SimFer begins Morebaya port commissioning</v>
+      </c>
+      <c r="D10" s="8" t="str">
+        <v>COMP_SIMFER</v>
+      </c>
+      <c r="E10" s="8" t="str"/>
+      <c r="F10" s="8" t="str">
+        <v>Port / rail commissioning</v>
+      </c>
+      <c r="G10" s="8" t="str">
+        <v>SimFer; Morebaya; rail spur; WCS port; Guinea; Rio Tinto; CIOH</v>
+      </c>
+      <c r="H10" s="8" t="str">
+        <v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="str">
+        <v>ANN_010</v>
+      </c>
+      <c r="B11" s="8" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <v>APM Terminals enters exclusive negotiations over Badagry deepsea port</v>
+      </c>
+      <c r="D11" s="8" t="str">
+        <v>COMP_BADAGRY_PORT_DEV</v>
+      </c>
+      <c r="E11" s="8" t="str"/>
+      <c r="F11" s="8" t="str">
+        <v>Port development</v>
+      </c>
+      <c r="G11" s="8" t="str">
+        <v>APM Terminals; Badagry; Nigeria; Apapa; Onne</v>
+      </c>
+      <c r="H11" s="8" t="str">
+        <v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ANN_AOPS_01</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2025-08-21</v>
+      </c>
+      <c r="C12" t="str">
+        <v>RCN accepts sixth and final AOPS, HMCS Robert Hampton Gray</v>
+      </c>
+      <c r="D12" t="str">
+        <v>COMP_IRVING</v>
+      </c>
+      <c r="E12" t="str">
+        <v>PROG_AOPS_RCN</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Delivery</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Irving; Halifax Shipyard; RCN; Robert Hampton Gray</v>
+      </c>
+      <c r="H12" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>ANN_AOPS_02</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Canadian Coast Guard launches CCGS Donjek</v>
+      </c>
+      <c r="D13" t="str">
+        <v>COMP_IRVING</v>
+      </c>
+      <c r="E13" t="str">
+        <v>PROG_AOPS_CCG</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Launch</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Irving; Halifax Shipyard; CCG; Donjek; Sermilik</v>
+      </c>
+      <c r="H13" t="str">
+        <v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>ANN_UAE_01</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2021-05-18</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ADSB awarded AED3.5bn contract for four FALAJ 3 vessels</v>
+      </c>
+      <c r="D14" t="str">
+        <v>COMP_ADSB</v>
+      </c>
+      <c r="E14" t="str">
+        <v>PROG_UAE_FALAJ3</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="G14" t="str">
+        <v>ADSB; UAE Navy; UAE Ministry of Defence; FALAJ3</v>
+      </c>
+      <c r="H14" t="str">
+        <v>https://edgegroup.ae/share/pdf/news/173</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>ANN_UAE_02</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-01-14</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ADSB launches first FALAJ 3 vessel</v>
+      </c>
+      <c r="D15" t="str">
+        <v>COMP_ADSB</v>
+      </c>
+      <c r="E15" t="str">
+        <v>PROG_UAE_FALAJ3</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Launch</v>
+      </c>
+      <c r="G15" t="str">
+        <v>ADSB; UAE Navy; first FALAJ3</v>
+      </c>
+      <c r="H15" t="str">
+        <v>https://edgegroup.ae/news/adsb-launches-first-vessel-prestigious-falaj-3-programme</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>ANN_UAE_03</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2025-02-19</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ALTAF commissioned as first FALAJ 3 missile boat</v>
+      </c>
+      <c r="D16" t="str">
+        <v>COMP_ADSB</v>
+      </c>
+      <c r="E16" t="str">
+        <v>PROG_UAE_FALAJ3</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Commissioning</v>
+      </c>
+      <c r="G16" t="str">
+        <v>ALTAF; ADSB; EDGE; UAE Navy</v>
+      </c>
+      <c r="H16" t="str">
+        <v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>ANN_UAE_04</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2023-10-21</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Naval Group delivers Bani Yas to UAE Navy</v>
+      </c>
+      <c r="D17" t="str">
+        <v>COMP_NAVAL_GROUP</v>
+      </c>
+      <c r="E17" t="str">
+        <v>PROG_UAE_BANIYAS</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Delivery</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Bani Yas; Lorient; UAE Navy</v>
+      </c>
+      <c r="H17" t="str">
+        <v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ANN_UAE_05</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2024-06-27</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Naval Group delivers Al Emarat to UAE Navy</v>
+      </c>
+      <c r="D18" t="str">
+        <v>COMP_NAVAL_GROUP</v>
+      </c>
+      <c r="E18" t="str">
+        <v>PROG_UAE_BANIYAS</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Delivery</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Al Emarat; Lorient; UAE Navy</v>
+      </c>
+      <c r="H18" t="str">
+        <v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ANN_UAE_06</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2017-02-20</v>
+      </c>
+      <c r="C19" t="str">
+        <v>UAE commissions Al Hili, sixth Baynunah-class corvette</v>
+      </c>
+      <c r="D19" t="str">
+        <v>COMP_ADSB</v>
+      </c>
+      <c r="E19" t="str">
+        <v>PROG_UAE_BAYNUNAH</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Commissioning</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Al Hili; ADSB; UAE Navy</v>
+      </c>
+      <c r="H19" t="str">
+        <v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>ANN_UAE_07</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2013-01-08</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Fincantieri delivers Abu Dhabi corvette and Ghantut patrol vessel</v>
+      </c>
+      <c r="D20" t="str">
+        <v>COMP_FINCANTIERI</v>
+      </c>
+      <c r="E20" t="str">
+        <v>PROG_UAE_ABUDHABI</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Delivery</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Abu Dhabi; Ghantut; UAE Navy; Muggiano</v>
+      </c>
+      <c r="H20" t="str">
+        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ANN260911_MI01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Indian Navy launches advanced Ocean Research Vessel ORV Sagar Manthan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VESSEL_SAGAR_MANTHAN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Launch</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Yard 3041; Rishi Bankim Shipyard; Indian Navy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Source ID</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>Publisher</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>Supports</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="str">
-        <x:v>URL</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="str">
-        <x:v>Checked As Of</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="8" t="str">
-        <x:v>SRC127_001</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="str">
-        <x:v>EDGE Group</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="str">
-        <x:v>MAESTRAL JV / UAE Coast Guard order</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-      <x:c r="E2" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="8" t="str">
-        <x:v>SRC127_002</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="str">
-        <x:v>EDGE Group</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="str">
-        <x:v>ADSB / Al-Dorra launch</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="str">
-        <x:v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="8" t="str">
-        <x:v>SRC127_003</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>Government of Canada</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
-        <x:v>River-class Destroyer</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="str">
-        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/river-class-destroyer.html</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="8" t="str">
-        <x:v>SRC127_004</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>Government of Canada</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
-        <x:v>AOPS</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/corporate/reports-publications/departmental-plans/departmental-plan-2026-27/status-report-transformational-major-capital-projects.html</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="8" t="str">
-        <x:v>SRC127_005</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>Seaspan</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
-        <x:v>Shipyards / roles</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="str">
-        <x:v>https://www.seaspan.com/seaspan-shipyards/</x:v>
-      </x:c>
-      <x:c r="E6" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="8" t="str">
-        <x:v>SRC127_006</x:v>
-      </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>Seaspan</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
-        <x:v>ASC partnership</x:v>
-      </x:c>
-      <x:c r="D7" s="8" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-inks-deal-with-bollinger-rauma-for-u-s-coast-guard-asc-program/</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="8" t="str">
-        <x:v>SRC127_007</x:v>
-      </x:c>
-      <x:c r="B8" s="8" t="str">
-        <x:v>Davie</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="str">
-        <x:v>Six Program Icebreakers</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="str">
-        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
-      </x:c>
-      <x:c r="E8" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="8" t="str">
-        <x:v>SRC127_008</x:v>
-      </x:c>
-      <x:c r="B9" s="8" t="str">
-        <x:v>Davie Defense</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="str">
-        <x:v>US facilities / ASC announcements</x:v>
-      </x:c>
-      <x:c r="D9" s="8" t="str">
-        <x:v>https://www.daviedefense.com/</x:v>
-      </x:c>
-      <x:c r="E9" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="8" t="str">
-        <x:v>SRC127_009</x:v>
-      </x:c>
-      <x:c r="B10" s="8" t="str">
-        <x:v>Bollinger</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="str">
-        <x:v>Yard network / Houma / Gulfport</x:v>
-      </x:c>
-      <x:c r="D10" s="8" t="str">
-        <x:v>https://www.bollingershipyards.com/locations/</x:v>
-      </x:c>
-      <x:c r="E10" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="8" t="str">
-        <x:v>SRC127_010</x:v>
-      </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>RMC</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
-        <x:v>Rauma capabilities</x:v>
-      </x:c>
-      <x:c r="D11" s="8" t="str">
-        <x:v>https://rmcfinland.fi/capabilities/</x:v>
-      </x:c>
-      <x:c r="E11" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="8" t="str">
-        <x:v>SRC127_011</x:v>
-      </x:c>
-      <x:c r="B12" s="8" t="str">
-        <x:v>Damen</x:v>
-      </x:c>
-      <x:c r="C12" s="8" t="str">
-        <x:v>Dutch Caribbean Coast Guard / Antalya</x:v>
-      </x:c>
-      <x:c r="D12" s="8" t="str">
-        <x:v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</x:v>
-      </x:c>
-      <x:c r="E12" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="8" t="str">
-        <x:v>SRC127_012</x:v>
-      </x:c>
-      <x:c r="B13" s="8" t="str">
-        <x:v>Fincantieri</x:v>
-      </x:c>
-      <x:c r="C13" s="8" t="str">
-        <x:v>UAE Navy Muggiano deliveries</x:v>
-      </x:c>
-      <x:c r="D13" s="8" t="str">
-        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
-      </x:c>
-      <x:c r="E13" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="8" t="str">
-        <x:v>SRC127_013</x:v>
-      </x:c>
-      <x:c r="B14" s="8" t="str">
-        <x:v>RMK Marine</x:v>
-      </x:c>
-      <x:c r="C14" s="8" t="str">
-        <x:v>Dual-use profile</x:v>
-      </x:c>
-      <x:c r="D14" s="8" t="str">
-        <x:v>https://www.rmkmarine.com.tr/Default.aspx</x:v>
-      </x:c>
-      <x:c r="E14" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="8" t="str">
-        <x:v>SRC127_014</x:v>
-      </x:c>
-      <x:c r="B15" s="8" t="str">
-        <x:v>Sefine</x:v>
-      </x:c>
-      <x:c r="C15" s="8" t="str">
-        <x:v>Commercial / government / repair profile</x:v>
-      </x:c>
-      <x:c r="D15" s="8" t="str">
-        <x:v>https://www.sefine.com.tr/</x:v>
-      </x:c>
-      <x:c r="E15" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="8" t="str">
-        <x:v>SRC127_015</x:v>
-      </x:c>
-      <x:c r="B16" s="8" t="str">
-        <x:v>SimFer</x:v>
-      </x:c>
-      <x:c r="C16" s="8" t="str">
-        <x:v>Morebaya commissioning</x:v>
-      </x:c>
-      <x:c r="D16" s="8" t="str">
-        <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</x:v>
-      </x:c>
-      <x:c r="E16" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="8" t="str">
-        <x:v>SRC127_016</x:v>
-      </x:c>
-      <x:c r="B17" s="8" t="str">
-        <x:v>Splash247</x:v>
-      </x:c>
-      <x:c r="C17" s="8" t="str">
-        <x:v>Badagry negotiations</x:v>
-      </x:c>
-      <x:c r="D17" s="8" t="str">
-        <x:v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</x:v>
-      </x:c>
-      <x:c r="E17" s="8" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>SRC131_001</x:v>
-      </x:c>
-      <x:c r="B18" t="str">
-        <x:v>Government of Canada</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>RCN AOPS fleet / six deliveries</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-navy.html</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>SRC131_002</x:v>
-      </x:c>
-      <x:c r="B19" t="str">
-        <x:v>Government of Canada</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>AOPS project updates / delivery timeline</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
-        <x:v>SRC131_003</x:v>
-      </x:c>
-      <x:c r="B20" t="str">
-        <x:v>Canadian Coast Guard</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>CCGS Donjek launch / CCG AOPS status</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>SRC131_004</x:v>
-      </x:c>
-      <x:c r="B21" t="str">
-        <x:v>Government of Canada</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>CCG AOPS programme budget / delivery</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
-      </x:c>
-      <x:c r="E21" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>SRC131_005</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>EDGE / ADSB</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>FALAJ3 AED3.5bn / four-vessel contract</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>https://edgegroup.ae/share/pdf/news/173</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>SRC131_006</x:v>
-      </x:c>
-      <x:c r="B23" t="str">
-        <x:v>EDGE / ADSB</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>ALTAF commissioning / first-of-class</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
-      </x:c>
-      <x:c r="E23" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>SRC131_007</x:v>
-      </x:c>
-      <x:c r="B24" t="str">
-        <x:v>EDGE / ADSB</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>Baynunah programme / six corvettes</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>https://edgegroup.ae/adsb</x:v>
-      </x:c>
-      <x:c r="E24" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>SRC131_008</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>WAM</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>Al Hili sixth Baynunah commissioned</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
-      </x:c>
-      <x:c r="E25" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>SRC131_009</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>Fincantieri</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>Abu Dhabi / Falaj 2 UAE deliveries</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>SRC131_010</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>Naval Group</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>Bani Yas delivery</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
-      </x:c>
-      <x:c r="E27" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" t="str">
-        <x:v>SRC131_011</x:v>
-      </x:c>
-      <x:c r="B28" t="str">
-        <x:v>Naval Group</x:v>
-      </x:c>
-      <x:c r="C28" t="str">
-        <x:v>Al Emarat delivery</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
-        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
-      </x:c>
-      <x:c r="E28" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" t="str">
-        <x:v>SRC131_012</x:v>
-      </x:c>
-      <x:c r="B29" t="str">
-        <x:v>Fincantieri</x:v>
-      </x:c>
-      <x:c r="C29" t="str">
-        <x:v>Qarnen launch / Falaj 2 programme</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
-        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</x:v>
-      </x:c>
-      <x:c r="E29" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" t="str">
-        <x:v>SRC131_013</x:v>
-      </x:c>
-      <x:c r="B30" t="str">
-        <x:v>Public fleet reference</x:v>
-      </x:c>
-      <x:c r="C30" t="str">
-        <x:v>Baynunah class vessel names / pennants cross-check</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
-        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
-      </x:c>
-      <x:c r="E30" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="str">
-        <x:v>SRC131_014</x:v>
-      </x:c>
-      <x:c r="B31" t="str">
-        <x:v>EDGE / MAESTRAL</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>UAE Coast Guard ten P51MR order</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-      <x:c r="E31" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="str">
+        <v>Source ID</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>Publisher</v>
+      </c>
+      <c r="C1" s="4" t="str">
+        <v>Supports</v>
+      </c>
+      <c r="D1" s="4" t="str">
+        <v>URL</v>
+      </c>
+      <c r="E1" s="4" t="str">
+        <v>Checked As Of</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="str">
+        <v>SRC127_001</v>
+      </c>
+      <c r="B2" s="8" t="str">
+        <v>EDGE Group</v>
+      </c>
+      <c r="C2" s="8" t="str">
+        <v>MAESTRAL JV / UAE Coast Guard order</v>
+      </c>
+      <c r="D2" s="8" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+      <c r="E2" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="str">
+        <v>SRC127_002</v>
+      </c>
+      <c r="B3" s="8" t="str">
+        <v>EDGE Group</v>
+      </c>
+      <c r="C3" s="8" t="str">
+        <v>ADSB / Al-Dorra launch</v>
+      </c>
+      <c r="D3" s="8" t="str">
+        <v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</v>
+      </c>
+      <c r="E3" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="str">
+        <v>SRC127_003</v>
+      </c>
+      <c r="B4" s="8" t="str">
+        <v>Government of Canada</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <v>River-class Destroyer</v>
+      </c>
+      <c r="D4" s="8" t="str">
+        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/river-class-destroyer.html</v>
+      </c>
+      <c r="E4" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="str">
+        <v>SRC127_004</v>
+      </c>
+      <c r="B5" s="8" t="str">
+        <v>Government of Canada</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <v>AOPS</v>
+      </c>
+      <c r="D5" s="8" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/corporate/reports-publications/departmental-plans/departmental-plan-2026-27/status-report-transformational-major-capital-projects.html</v>
+      </c>
+      <c r="E5" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="str">
+        <v>SRC127_005</v>
+      </c>
+      <c r="B6" s="8" t="str">
+        <v>Seaspan</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <v>Shipyards / roles</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <v>https://www.seaspan.com/seaspan-shipyards/</v>
+      </c>
+      <c r="E6" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="str">
+        <v>SRC127_006</v>
+      </c>
+      <c r="B7" s="8" t="str">
+        <v>Seaspan</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <v>ASC partnership</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <v>https://www.seaspan.com/press-release/seaspan-inks-deal-with-bollinger-rauma-for-u-s-coast-guard-asc-program/</v>
+      </c>
+      <c r="E7" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="str">
+        <v>SRC127_007</v>
+      </c>
+      <c r="B8" s="8" t="str">
+        <v>Davie</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <v>Six Program Icebreakers</v>
+      </c>
+      <c r="D8" s="8" t="str">
+        <v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</v>
+      </c>
+      <c r="E8" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="str">
+        <v>SRC127_008</v>
+      </c>
+      <c r="B9" s="8" t="str">
+        <v>Davie Defense</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <v>US facilities / ASC announcements</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <v>https://www.daviedefense.com/</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="str">
+        <v>SRC127_009</v>
+      </c>
+      <c r="B10" s="8" t="str">
+        <v>Bollinger</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <v>Yard network / Houma / Gulfport</v>
+      </c>
+      <c r="D10" s="8" t="str">
+        <v>https://www.bollingershipyards.com/locations/</v>
+      </c>
+      <c r="E10" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="str">
+        <v>SRC127_010</v>
+      </c>
+      <c r="B11" s="8" t="str">
+        <v>RMC</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <v>Rauma capabilities</v>
+      </c>
+      <c r="D11" s="8" t="str">
+        <v>https://rmcfinland.fi/capabilities/</v>
+      </c>
+      <c r="E11" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="str">
+        <v>SRC127_011</v>
+      </c>
+      <c r="B12" s="8" t="str">
+        <v>Damen</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <v>Dutch Caribbean Coast Guard / Antalya</v>
+      </c>
+      <c r="D12" s="8" t="str">
+        <v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</v>
+      </c>
+      <c r="E12" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="str">
+        <v>SRC127_012</v>
+      </c>
+      <c r="B13" s="8" t="str">
+        <v>Fincantieri</v>
+      </c>
+      <c r="C13" s="8" t="str">
+        <v>UAE Navy Muggiano deliveries</v>
+      </c>
+      <c r="D13" s="8" t="str">
+        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
+      </c>
+      <c r="E13" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="str">
+        <v>SRC127_013</v>
+      </c>
+      <c r="B14" s="8" t="str">
+        <v>RMK Marine</v>
+      </c>
+      <c r="C14" s="8" t="str">
+        <v>Dual-use profile</v>
+      </c>
+      <c r="D14" s="8" t="str">
+        <v>https://www.rmkmarine.com.tr/Default.aspx</v>
+      </c>
+      <c r="E14" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="str">
+        <v>SRC127_014</v>
+      </c>
+      <c r="B15" s="8" t="str">
+        <v>Sefine</v>
+      </c>
+      <c r="C15" s="8" t="str">
+        <v>Commercial / government / repair profile</v>
+      </c>
+      <c r="D15" s="8" t="str">
+        <v>https://www.sefine.com.tr/</v>
+      </c>
+      <c r="E15" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="str">
+        <v>SRC127_015</v>
+      </c>
+      <c r="B16" s="8" t="str">
+        <v>SimFer</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <v>Morebaya commissioning</v>
+      </c>
+      <c r="D16" s="8" t="str">
+        <v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</v>
+      </c>
+      <c r="E16" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="str">
+        <v>SRC127_016</v>
+      </c>
+      <c r="B17" s="8" t="str">
+        <v>Splash247</v>
+      </c>
+      <c r="C17" s="8" t="str">
+        <v>Badagry negotiations</v>
+      </c>
+      <c r="D17" s="8" t="str">
+        <v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</v>
+      </c>
+      <c r="E17" s="8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SRC131_001</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Government of Canada</v>
+      </c>
+      <c r="C18" t="str">
+        <v>RCN AOPS fleet / six deliveries</v>
+      </c>
+      <c r="D18" t="str">
+        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-navy.html</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SRC131_002</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Government of Canada</v>
+      </c>
+      <c r="C19" t="str">
+        <v>AOPS project updates / delivery timeline</v>
+      </c>
+      <c r="D19" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SRC131_003</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Canadian Coast Guard</v>
+      </c>
+      <c r="C20" t="str">
+        <v>CCGS Donjek launch / CCG AOPS status</v>
+      </c>
+      <c r="D20" t="str">
+        <v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SRC131_004</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Government of Canada</v>
+      </c>
+      <c r="C21" t="str">
+        <v>CCG AOPS programme budget / delivery</v>
+      </c>
+      <c r="D21" t="str">
+        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SRC131_005</v>
+      </c>
+      <c r="B22" t="str">
+        <v>EDGE / ADSB</v>
+      </c>
+      <c r="C22" t="str">
+        <v>FALAJ3 AED3.5bn / four-vessel contract</v>
+      </c>
+      <c r="D22" t="str">
+        <v>https://edgegroup.ae/share/pdf/news/173</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SRC131_006</v>
+      </c>
+      <c r="B23" t="str">
+        <v>EDGE / ADSB</v>
+      </c>
+      <c r="C23" t="str">
+        <v>ALTAF commissioning / first-of-class</v>
+      </c>
+      <c r="D23" t="str">
+        <v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SRC131_007</v>
+      </c>
+      <c r="B24" t="str">
+        <v>EDGE / ADSB</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Baynunah programme / six corvettes</v>
+      </c>
+      <c r="D24" t="str">
+        <v>https://edgegroup.ae/adsb</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SRC131_008</v>
+      </c>
+      <c r="B25" t="str">
+        <v>WAM</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Al Hili sixth Baynunah commissioned</v>
+      </c>
+      <c r="D25" t="str">
+        <v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SRC131_009</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Fincantieri</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Abu Dhabi / Falaj 2 UAE deliveries</v>
+      </c>
+      <c r="D26" t="str">
+        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SRC131_010</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Naval Group</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Bani Yas delivery</v>
+      </c>
+      <c r="D27" t="str">
+        <v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SRC131_011</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Naval Group</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Al Emarat delivery</v>
+      </c>
+      <c r="D28" t="str">
+        <v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SRC131_012</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Fincantieri</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Qarnen launch / Falaj 2 programme</v>
+      </c>
+      <c r="D29" t="str">
+        <v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SRC131_013</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Public fleet reference</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Baynunah class vessel names / pennants cross-check</v>
+      </c>
+      <c r="D30" t="str">
+        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SRC131_014</v>
+      </c>
+      <c r="B31" t="str">
+        <v>EDGE / MAESTRAL</v>
+      </c>
+      <c r="C31" t="str">
+        <v>UAE Coast Guard ten P51MR order</v>
+      </c>
+      <c r="D31" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SRC260911_MI01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Marine Insight</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Admiral Essen attack report in Novorossiysk</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SRC260911_MI15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Marine Insight</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ORV Sagar Manthan launch at Rishi Bankim Shipyard</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5501,1192 +5577,1256 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>Vessel ID</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="str">
-        <x:v>Programme ID</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="str">
-        <x:v>Class / Type</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="str">
-        <x:v>Customer / Operator</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="str">
-        <x:v>Build Yard ID</x:v>
-      </x:c>
-      <x:c r="G1" s="4" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="H1" s="4" t="str">
-        <x:v>Build / Delivery Route</x:v>
-      </x:c>
-      <x:c r="I1" s="4" t="str">
-        <x:v>Source URL</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="8" t="str">
-        <x:v>VES_DEF_001</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="str">
-        <x:v>HMCS Fraser</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="str">
-        <x:v>PROG_RCD</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="str">
-        <x:v>River-class Destroyer</x:v>
-      </x:c>
-      <x:c r="E2" s="8" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F2" s="8" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G2" s="8" t="str">
-        <x:v>Full-rate production</x:v>
-      </x:c>
-      <x:c r="H2" s="8" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="I2" s="8" t="str">
-        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/river-class-destroyer.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="8" t="str">
-        <x:v>VES_DEF_002</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="str">
-        <x:v>Joint Support Ship 1</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="str">
-        <x:v>PROG_SEA_JSS</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="str">
-        <x:v>Joint Support Ship</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="str">
-        <x:v>YARD_SEA_VAN</x:v>
-      </x:c>
-      <x:c r="G3" s="8" t="str">
-        <x:v>Under construction</x:v>
-      </x:c>
-      <x:c r="H3" s="8" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="I3" s="8" t="str">
-        <x:v>https://www.seaspan.com/seaspan-shipyards/shipbuilding/joint-support-ships/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="8" t="str">
-        <x:v>VES_DEF_003</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>Joint Support Ship 2</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
-        <x:v>PROG_SEA_JSS</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="str">
-        <x:v>Joint Support Ship</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="str">
-        <x:v>YARD_SEA_VAN</x:v>
-      </x:c>
-      <x:c r="G4" s="8" t="str">
-        <x:v>Under construction</x:v>
-      </x:c>
-      <x:c r="H4" s="8" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="I4" s="8" t="str">
-        <x:v>https://www.seaspan.com/seaspan-shipyards/shipbuilding/joint-support-ships/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="8" t="str">
-        <x:v>VES_DEF_004</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>Seaspan Heavy Polar Icebreaker</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
-        <x:v>PROG_SEA_POLAR</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="str">
-        <x:v>Heavy polar icebreaker</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="str">
-        <x:v>Canadian Coast Guard</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="str">
-        <x:v>YARD_SEA_VAN</x:v>
-      </x:c>
-      <x:c r="G5" s="8" t="str">
-        <x:v>Under construction</x:v>
-      </x:c>
-      <x:c r="H5" s="8" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="I5" s="8" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-celebrates-one-year-of-progress-on-the-heavy-polar-icebreaker/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="8" t="str">
-        <x:v>VES_DEF_005</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>Polar Max</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
-        <x:v>PROG_DAV_POLARMAX</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="str">
-        <x:v>Heavy polar icebreaker</x:v>
-      </x:c>
-      <x:c r="E6" s="8" t="str">
-        <x:v>Canadian Coast Guard</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="str">
-        <x:v>YARD_DAVIE_LEVIS</x:v>
-      </x:c>
-      <x:c r="G6" s="8" t="str">
-        <x:v>Under construction</x:v>
-      </x:c>
-      <x:c r="H6" s="8" t="str">
-        <x:v>Finland + Canada</x:v>
-      </x:c>
-      <x:c r="I6" s="8" t="str">
-        <x:v>https://www.davie.ca/en/news/20260331-davie-begins-construction-of-polarmax-en/</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="8" t="str">
-        <x:v>VES_DEF_006</x:v>
-      </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>Abu Dhabi</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
-        <x:v>PROG_UAE_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="D7" s="8" t="str">
-        <x:v>Abu Dhabi-class corvette</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str">
-        <x:v>YARD_FIN_MUGGIANO</x:v>
-      </x:c>
-      <x:c r="G7" s="8" t="str">
-        <x:v>Delivered 2013</x:v>
-      </x:c>
-      <x:c r="H7" s="8" t="str">
-        <x:v>Italy → UAE</x:v>
-      </x:c>
-      <x:c r="I7" s="8" t="str">
-        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="8" t="str">
-        <x:v>VES_DEF_007</x:v>
-      </x:c>
-      <x:c r="B8" s="8" t="str">
-        <x:v>Ghantut</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="str">
-        <x:v>PROG_UAE_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="str">
-        <x:v>Falaj 2 patrol vessel</x:v>
-      </x:c>
-      <x:c r="E8" s="8" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="str">
-        <x:v>YARD_FIN_MUGGIANO</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="str">
-        <x:v>Delivered 2013</x:v>
-      </x:c>
-      <x:c r="H8" s="8" t="str">
-        <x:v>Italy → UAE</x:v>
-      </x:c>
-      <x:c r="I8" s="8" t="str">
-        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="8" t="str">
-        <x:v>VES_UAE_P51_01</x:v>
-      </x:c>
-      <x:c r="B9" s="8" t="str">
-        <x:v>P51MR OPV 01 — name pending</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D9" s="8" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E9" s="8" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F9" s="8"/>
-      <x:c r="G9" s="8" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H9" s="8" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I9" s="8" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="8" t="str">
-        <x:v>VES_DEF_009</x:v>
-      </x:c>
-      <x:c r="B10" s="8" t="str">
-        <x:v>Al-Dorra class - first vessel</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="str">
-        <x:v>PROG_ADSB_ALDORRA</x:v>
-      </x:c>
-      <x:c r="D10" s="8" t="str">
-        <x:v>62 m vessel</x:v>
-      </x:c>
-      <x:c r="E10" s="8" t="str">
-        <x:v>Kuwait Naval Forces</x:v>
-      </x:c>
-      <x:c r="F10" s="8" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G10" s="8" t="str">
-        <x:v>Launched Feb 2026</x:v>
-      </x:c>
-      <x:c r="H10" s="8" t="str">
-        <x:v>UAE → Kuwait</x:v>
-      </x:c>
-      <x:c r="I10" s="8" t="str">
-        <x:v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="8" t="str">
-        <x:v>VES_DEF_010</x:v>
-      </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>Stan Patrol 5009 - sample hull</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
-        <x:v>PROG_DUTCH_CG</x:v>
-      </x:c>
-      <x:c r="D11" s="8" t="str">
-        <x:v>Stan Patrol 5009</x:v>
-      </x:c>
-      <x:c r="E11" s="8" t="str">
-        <x:v>Dutch Caribbean Coast Guard</x:v>
-      </x:c>
-      <x:c r="F11" s="8" t="str">
-        <x:v>YARD_DAMEN_ANTALYA</x:v>
-      </x:c>
-      <x:c r="G11" s="8" t="str">
-        <x:v>Contracted</x:v>
-      </x:c>
-      <x:c r="H11" s="8" t="str">
-        <x:v>Turkey → Caribbean</x:v>
-      </x:c>
-      <x:c r="I11" s="8" t="str">
-        <x:v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>VES_AOPS_01</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>HMCS Harry DeWolf</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>PROG_AOPS_RCN</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>Harry DeWolf-class AOPV</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>Delivered 2020 / operational</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>Halifax → RCN</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>VES_AOPS_02</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>HMCS Margaret Brooke</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>PROG_AOPS_RCN</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>Harry DeWolf-class AOPV</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>Delivered 2021 / operational</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>Halifax → RCN</x:v>
-      </x:c>
-      <x:c r="I13" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>VES_AOPS_03</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>HMCS Max Bernays</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>PROG_AOPS_RCN</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>Harry DeWolf-class AOPV</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F14" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
-        <x:v>Delivered 2022 / operational</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>Halifax → RCN</x:v>
-      </x:c>
-      <x:c r="I14" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>VES_AOPS_04</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>HMCS William Hall</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>PROG_AOPS_RCN</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>Harry DeWolf-class AOPV</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F15" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G15" t="str">
-        <x:v>Delivered 2023 / commissioned 2024</x:v>
-      </x:c>
-      <x:c r="H15" t="str">
-        <x:v>Halifax → RCN</x:v>
-      </x:c>
-      <x:c r="I15" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>VES_AOPS_05</x:v>
-      </x:c>
-      <x:c r="B16" t="str">
-        <x:v>HMCS Frédérick Rolette</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>PROG_AOPS_RCN</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>Harry DeWolf-class AOPV</x:v>
-      </x:c>
-      <x:c r="E16" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F16" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G16" t="str">
-        <x:v>Delivered 2024 / commissioned 2025</x:v>
-      </x:c>
-      <x:c r="H16" t="str">
-        <x:v>Halifax → RCN</x:v>
-      </x:c>
-      <x:c r="I16" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/06/his-majestys-canadian-ship-frederick-rolette-commissioned-into-service.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>VES_AOPS_06</x:v>
-      </x:c>
-      <x:c r="B17" t="str">
-        <x:v>HMCS Robert Hampton Gray</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>PROG_AOPS_RCN</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>Harry DeWolf-class AOPV</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
-        <x:v>Royal Canadian Navy</x:v>
-      </x:c>
-      <x:c r="F17" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G17" t="str">
-        <x:v>Delivered 21 Aug 2025; commissioning expected 2026</x:v>
-      </x:c>
-      <x:c r="H17" t="str">
-        <x:v>Halifax → RCN / Esquimalt</x:v>
-      </x:c>
-      <x:c r="I17" t="str">
-        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>VES_AOPS_07</x:v>
-      </x:c>
-      <x:c r="B18" t="str">
-        <x:v>CCGS Donjek</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>PROG_AOPS_CCG</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>AOPS Coast Guard variant</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
-        <x:v>Canadian Coast Guard</x:v>
-      </x:c>
-      <x:c r="F18" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G18" t="str">
-        <x:v>Launched 29 Apr 2026; delivery expected late 2026</x:v>
-      </x:c>
-      <x:c r="H18" t="str">
-        <x:v>Halifax → CCG</x:v>
-      </x:c>
-      <x:c r="I18" t="str">
-        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>VES_AOPS_08</x:v>
-      </x:c>
-      <x:c r="B19" t="str">
-        <x:v>CCGS Sermilik</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>PROG_AOPS_CCG</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>AOPS Coast Guard variant</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
-        <x:v>Canadian Coast Guard</x:v>
-      </x:c>
-      <x:c r="F19" t="str">
-        <x:v>YARD_IRV_HALIFAX</x:v>
-      </x:c>
-      <x:c r="G19" t="str">
-        <x:v>Under construction; delivery expected 2027</x:v>
-      </x:c>
-      <x:c r="H19" t="str">
-        <x:v>Halifax → CCG</x:v>
-      </x:c>
-      <x:c r="I19" t="str">
-        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
-        <x:v>VES_UAE_F3_01</x:v>
-      </x:c>
-      <x:c r="B20" t="str">
-        <x:v>ALTAF</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>PROG_UAE_FALAJ3</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>FALAJ 3 62 m missile boat</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F20" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G20" t="str">
-        <x:v>Commissioned 19 Feb 2025</x:v>
-      </x:c>
-      <x:c r="H20" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I20" t="str">
-        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>VES_UAE_F3_02</x:v>
-      </x:c>
-      <x:c r="B21" t="str">
-        <x:v>FALAJ 3 Unit 2 — name pending</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>PROG_UAE_FALAJ3</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>FALAJ 3 62 m missile boat</x:v>
-      </x:c>
-      <x:c r="E21" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F21" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G21" t="str">
-        <x:v>Programme vessel / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H21" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I21" t="str">
-        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>VES_UAE_F3_03</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>FALAJ 3 Unit 3 — name pending</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>PROG_UAE_FALAJ3</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>FALAJ 3 62 m missile boat</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>Programme vessel / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I22" t="str">
-        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>VES_UAE_F3_04</x:v>
-      </x:c>
-      <x:c r="B23" t="str">
-        <x:v>FALAJ 3 Unit 4 — name pending</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>PROG_UAE_FALAJ3</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>FALAJ 3 62 m missile boat</x:v>
-      </x:c>
-      <x:c r="E23" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F23" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G23" t="str">
-        <x:v>Programme vessel / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H23" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I23" t="str">
-        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>VES_UAE_BAY_01</x:v>
-      </x:c>
-      <x:c r="B24" t="str">
-        <x:v>Baynunah (P171)</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>PROG_UAE_BAYNUNAH</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>Baynunah-class corvette</x:v>
-      </x:c>
-      <x:c r="E24" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F24" t="str">
-        <x:v>YARD_CMN_CHERBOURG</x:v>
-      </x:c>
-      <x:c r="G24" t="str">
-        <x:v>In service</x:v>
-      </x:c>
-      <x:c r="H24" t="str">
-        <x:v>France → UAE</x:v>
-      </x:c>
-      <x:c r="I24" t="str">
-        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>VES_UAE_BAY_02</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>Al Hesen (P172)</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>PROG_UAE_BAYNUNAH</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>Baynunah-class corvette</x:v>
-      </x:c>
-      <x:c r="E25" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F25" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G25" t="str">
-        <x:v>In service</x:v>
-      </x:c>
-      <x:c r="H25" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I25" t="str">
-        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>VES_UAE_BAY_03</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>Al Dhafra (P173)</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>PROG_UAE_BAYNUNAH</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>Baynunah-class corvette</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F26" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G26" t="str">
-        <x:v>In service</x:v>
-      </x:c>
-      <x:c r="H26" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I26" t="str">
-        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>VES_UAE_BAY_04</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>Mezyad (P174)</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>PROG_UAE_BAYNUNAH</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>Baynunah-class corvette</x:v>
-      </x:c>
-      <x:c r="E27" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F27" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G27" t="str">
-        <x:v>In service</x:v>
-      </x:c>
-      <x:c r="H27" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I27" t="str">
-        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" t="str">
-        <x:v>VES_UAE_BAY_05</x:v>
-      </x:c>
-      <x:c r="B28" t="str">
-        <x:v>Al Jahili (P175)</x:v>
-      </x:c>
-      <x:c r="C28" t="str">
-        <x:v>PROG_UAE_BAYNUNAH</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
-        <x:v>Baynunah-class corvette</x:v>
-      </x:c>
-      <x:c r="E28" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F28" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G28" t="str">
-        <x:v>In service</x:v>
-      </x:c>
-      <x:c r="H28" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I28" t="str">
-        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" t="str">
-        <x:v>VES_UAE_BAY_06</x:v>
-      </x:c>
-      <x:c r="B29" t="str">
-        <x:v>Al Hili (P176)</x:v>
-      </x:c>
-      <x:c r="C29" t="str">
-        <x:v>PROG_UAE_BAYNUNAH</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
-        <x:v>Baynunah-class corvette</x:v>
-      </x:c>
-      <x:c r="E29" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F29" t="str">
-        <x:v>YARD_ADSB_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="G29" t="str">
-        <x:v>Commissioned 20 Feb 2017 / in service</x:v>
-      </x:c>
-      <x:c r="H29" t="str">
-        <x:v>Abu Dhabi → UAE Navy</x:v>
-      </x:c>
-      <x:c r="I29" t="str">
-        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" t="str">
-        <x:v>VES_UAE_GOW_01</x:v>
-      </x:c>
-      <x:c r="B30" t="str">
-        <x:v>Bani Yas</x:v>
-      </x:c>
-      <x:c r="C30" t="str">
-        <x:v>PROG_UAE_BANIYAS</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
-        <x:v>Gowind multi-mission corvette</x:v>
-      </x:c>
-      <x:c r="E30" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F30" t="str">
-        <x:v>YARD_NAVAL_LORIENT</x:v>
-      </x:c>
-      <x:c r="G30" t="str">
-        <x:v>Delivered 21 Oct 2023</x:v>
-      </x:c>
-      <x:c r="H30" t="str">
-        <x:v>Lorient → UAE</x:v>
-      </x:c>
-      <x:c r="I30" t="str">
-        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="str">
-        <x:v>VES_UAE_GOW_02</x:v>
-      </x:c>
-      <x:c r="B31" t="str">
-        <x:v>Al Emarat</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>PROG_UAE_BANIYAS</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>Gowind multi-mission corvette</x:v>
-      </x:c>
-      <x:c r="E31" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F31" t="str">
-        <x:v>YARD_NAVAL_LORIENT</x:v>
-      </x:c>
-      <x:c r="G31" t="str">
-        <x:v>Delivered 27 Jun 2024</x:v>
-      </x:c>
-      <x:c r="H31" t="str">
-        <x:v>Lorient → UAE</x:v>
-      </x:c>
-      <x:c r="I31" t="str">
-        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="str">
-        <x:v>VES_UAE_F2_02</x:v>
-      </x:c>
-      <x:c r="B32" t="str">
-        <x:v>Qarnen</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>PROG_UAE_ABUDHABI</x:v>
-      </x:c>
-      <x:c r="D32" t="str">
-        <x:v>Falaj 2 patrol vessel</x:v>
-      </x:c>
-      <x:c r="E32" t="str">
-        <x:v>UAE Navy</x:v>
-      </x:c>
-      <x:c r="F32" t="str">
-        <x:v>YARD_FIN_MUGGIANO</x:v>
-      </x:c>
-      <x:c r="G32" t="str">
-        <x:v>Delivered / operational</x:v>
-      </x:c>
-      <x:c r="H32" t="str">
-        <x:v>Italy → UAE</x:v>
-      </x:c>
-      <x:c r="I32" t="str">
-        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="str">
-        <x:v>VES_UAE_P51_02</x:v>
-      </x:c>
-      <x:c r="B33" t="str">
-        <x:v>P51MR OPV 02 — name pending</x:v>
-      </x:c>
-      <x:c r="C33" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D33" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E33" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F33"/>
-      <x:c r="G33" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H33" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I33" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="str">
-        <x:v>VES_UAE_P51_03</x:v>
-      </x:c>
-      <x:c r="B34" t="str">
-        <x:v>P51MR OPV 03 — name pending</x:v>
-      </x:c>
-      <x:c r="C34" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D34" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E34" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F34"/>
-      <x:c r="G34" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H34" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I34" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" t="str">
-        <x:v>VES_UAE_P51_04</x:v>
-      </x:c>
-      <x:c r="B35" t="str">
-        <x:v>P51MR OPV 04 — name pending</x:v>
-      </x:c>
-      <x:c r="C35" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D35" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E35" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F35"/>
-      <x:c r="G35" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H35" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I35" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" t="str">
-        <x:v>VES_UAE_P51_05</x:v>
-      </x:c>
-      <x:c r="B36" t="str">
-        <x:v>P51MR OPV 05 — name pending</x:v>
-      </x:c>
-      <x:c r="C36" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D36" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E36" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F36"/>
-      <x:c r="G36" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H36" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I36" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="str">
-        <x:v>VES_UAE_P51_06</x:v>
-      </x:c>
-      <x:c r="B37" t="str">
-        <x:v>P51MR OPV 06 — name pending</x:v>
-      </x:c>
-      <x:c r="C37" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D37" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E37" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F37"/>
-      <x:c r="G37" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H37" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I37" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="str">
-        <x:v>VES_UAE_P51_07</x:v>
-      </x:c>
-      <x:c r="B38" t="str">
-        <x:v>P51MR OPV 07 — name pending</x:v>
-      </x:c>
-      <x:c r="C38" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D38" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E38" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F38"/>
-      <x:c r="G38" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H38" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I38" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" t="str">
-        <x:v>VES_UAE_P51_08</x:v>
-      </x:c>
-      <x:c r="B39" t="str">
-        <x:v>P51MR OPV 08 — name pending</x:v>
-      </x:c>
-      <x:c r="C39" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D39" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E39" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F39"/>
-      <x:c r="G39" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H39" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I39" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" t="str">
-        <x:v>VES_UAE_P51_09</x:v>
-      </x:c>
-      <x:c r="B40" t="str">
-        <x:v>P51MR OPV 09 — name pending</x:v>
-      </x:c>
-      <x:c r="C40" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D40" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E40" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F40"/>
-      <x:c r="G40" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H40" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I40" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" t="str">
-        <x:v>VES_UAE_P51_10</x:v>
-      </x:c>
-      <x:c r="B41" t="str">
-        <x:v>P51MR OPV 10 — name pending</x:v>
-      </x:c>
-      <x:c r="C41" t="str">
-        <x:v>PROG_UAE_P51MR</x:v>
-      </x:c>
-      <x:c r="D41" t="str">
-        <x:v>51 m OPV</x:v>
-      </x:c>
-      <x:c r="E41" t="str">
-        <x:v>UAE Coast Guard</x:v>
-      </x:c>
-      <x:c r="F41"/>
-      <x:c r="G41" t="str">
-        <x:v>Contracted / name not confirmed</x:v>
-      </x:c>
-      <x:c r="H41" t="str">
-        <x:v>UAE / Italy</x:v>
-      </x:c>
-      <x:c r="I41" t="str">
-        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="str">
+        <v>Vessel ID</v>
+      </c>
+      <c r="B1" s="4" t="str">
+        <v>Vessel</v>
+      </c>
+      <c r="C1" s="4" t="str">
+        <v>Programme ID</v>
+      </c>
+      <c r="D1" s="4" t="str">
+        <v>Class / Type</v>
+      </c>
+      <c r="E1" s="4" t="str">
+        <v>Customer / Operator</v>
+      </c>
+      <c r="F1" s="4" t="str">
+        <v>Build Yard ID</v>
+      </c>
+      <c r="G1" s="4" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" s="4" t="str">
+        <v>Build / Delivery Route</v>
+      </c>
+      <c r="I1" s="4" t="str">
+        <v>Source URL</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="str">
+        <v>VES_DEF_001</v>
+      </c>
+      <c r="B2" s="8" t="str">
+        <v>HMCS Fraser</v>
+      </c>
+      <c r="C2" s="8" t="str">
+        <v>PROG_RCD</v>
+      </c>
+      <c r="D2" s="8" t="str">
+        <v>River-class Destroyer</v>
+      </c>
+      <c r="E2" s="8" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F2" s="8" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <v>Full-rate production</v>
+      </c>
+      <c r="H2" s="8" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="I2" s="8" t="str">
+        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/river-class-destroyer.html</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="str">
+        <v>VES_DEF_002</v>
+      </c>
+      <c r="B3" s="8" t="str">
+        <v>Joint Support Ship 1</v>
+      </c>
+      <c r="C3" s="8" t="str">
+        <v>PROG_SEA_JSS</v>
+      </c>
+      <c r="D3" s="8" t="str">
+        <v>Joint Support Ship</v>
+      </c>
+      <c r="E3" s="8" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F3" s="8" t="str">
+        <v>YARD_SEA_VAN</v>
+      </c>
+      <c r="G3" s="8" t="str">
+        <v>Under construction</v>
+      </c>
+      <c r="H3" s="8" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="I3" s="8" t="str">
+        <v>https://www.seaspan.com/seaspan-shipyards/shipbuilding/joint-support-ships/</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="str">
+        <v>VES_DEF_003</v>
+      </c>
+      <c r="B4" s="8" t="str">
+        <v>Joint Support Ship 2</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <v>PROG_SEA_JSS</v>
+      </c>
+      <c r="D4" s="8" t="str">
+        <v>Joint Support Ship</v>
+      </c>
+      <c r="E4" s="8" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F4" s="8" t="str">
+        <v>YARD_SEA_VAN</v>
+      </c>
+      <c r="G4" s="8" t="str">
+        <v>Under construction</v>
+      </c>
+      <c r="H4" s="8" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="I4" s="8" t="str">
+        <v>https://www.seaspan.com/seaspan-shipyards/shipbuilding/joint-support-ships/</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="str">
+        <v>VES_DEF_004</v>
+      </c>
+      <c r="B5" s="8" t="str">
+        <v>Seaspan Heavy Polar Icebreaker</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <v>PROG_SEA_POLAR</v>
+      </c>
+      <c r="D5" s="8" t="str">
+        <v>Heavy polar icebreaker</v>
+      </c>
+      <c r="E5" s="8" t="str">
+        <v>Canadian Coast Guard</v>
+      </c>
+      <c r="F5" s="8" t="str">
+        <v>YARD_SEA_VAN</v>
+      </c>
+      <c r="G5" s="8" t="str">
+        <v>Under construction</v>
+      </c>
+      <c r="H5" s="8" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="I5" s="8" t="str">
+        <v>https://www.seaspan.com/press-release/seaspan-celebrates-one-year-of-progress-on-the-heavy-polar-icebreaker/</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="str">
+        <v>VES_DEF_005</v>
+      </c>
+      <c r="B6" s="8" t="str">
+        <v>Polar Max</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <v>PROG_DAV_POLARMAX</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <v>Heavy polar icebreaker</v>
+      </c>
+      <c r="E6" s="8" t="str">
+        <v>Canadian Coast Guard</v>
+      </c>
+      <c r="F6" s="8" t="str">
+        <v>YARD_DAVIE_LEVIS</v>
+      </c>
+      <c r="G6" s="8" t="str">
+        <v>Under construction</v>
+      </c>
+      <c r="H6" s="8" t="str">
+        <v>Finland + Canada</v>
+      </c>
+      <c r="I6" s="8" t="str">
+        <v>https://www.davie.ca/en/news/20260331-davie-begins-construction-of-polarmax-en/</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="str">
+        <v>VES_DEF_006</v>
+      </c>
+      <c r="B7" s="8" t="str">
+        <v>Abu Dhabi</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <v>PROG_UAE_ABUDHABI</v>
+      </c>
+      <c r="D7" s="8" t="str">
+        <v>Abu Dhabi-class corvette</v>
+      </c>
+      <c r="E7" s="8" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F7" s="8" t="str">
+        <v>YARD_FIN_MUGGIANO</v>
+      </c>
+      <c r="G7" s="8" t="str">
+        <v>Delivered 2013</v>
+      </c>
+      <c r="H7" s="8" t="str">
+        <v>Italy → UAE</v>
+      </c>
+      <c r="I7" s="8" t="str">
+        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="str">
+        <v>VES_DEF_007</v>
+      </c>
+      <c r="B8" s="8" t="str">
+        <v>Ghantut</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <v>PROG_UAE_ABUDHABI</v>
+      </c>
+      <c r="D8" s="8" t="str">
+        <v>Falaj 2 patrol vessel</v>
+      </c>
+      <c r="E8" s="8" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F8" s="8" t="str">
+        <v>YARD_FIN_MUGGIANO</v>
+      </c>
+      <c r="G8" s="8" t="str">
+        <v>Delivered 2013</v>
+      </c>
+      <c r="H8" s="8" t="str">
+        <v>Italy → UAE</v>
+      </c>
+      <c r="I8" s="8" t="str">
+        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="str">
+        <v>VES_UAE_P51_01</v>
+      </c>
+      <c r="B9" s="8" t="str">
+        <v>P51MR OPV 01 — name pending</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E9" s="8" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H9" s="8" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I9" s="8" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="str">
+        <v>VES_DEF_009</v>
+      </c>
+      <c r="B10" s="8" t="str">
+        <v>Al-Dorra class - first vessel</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <v>PROG_ADSB_ALDORRA</v>
+      </c>
+      <c r="D10" s="8" t="str">
+        <v>62 m vessel</v>
+      </c>
+      <c r="E10" s="8" t="str">
+        <v>Kuwait Naval Forces</v>
+      </c>
+      <c r="F10" s="8" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G10" s="8" t="str">
+        <v>Launched Feb 2026</v>
+      </c>
+      <c r="H10" s="8" t="str">
+        <v>UAE → Kuwait</v>
+      </c>
+      <c r="I10" s="8" t="str">
+        <v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="str">
+        <v>VES_DEF_010</v>
+      </c>
+      <c r="B11" s="8" t="str">
+        <v>Stan Patrol 5009 - sample hull</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <v>PROG_DUTCH_CG</v>
+      </c>
+      <c r="D11" s="8" t="str">
+        <v>Stan Patrol 5009</v>
+      </c>
+      <c r="E11" s="8" t="str">
+        <v>Dutch Caribbean Coast Guard</v>
+      </c>
+      <c r="F11" s="8" t="str">
+        <v>YARD_DAMEN_ANTALYA</v>
+      </c>
+      <c r="G11" s="8" t="str">
+        <v>Contracted</v>
+      </c>
+      <c r="H11" s="8" t="str">
+        <v>Turkey → Caribbean</v>
+      </c>
+      <c r="I11" s="8" t="str">
+        <v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>VES_AOPS_01</v>
+      </c>
+      <c r="B12" t="str">
+        <v>HMCS Harry DeWolf</v>
+      </c>
+      <c r="C12" t="str">
+        <v>PROG_AOPS_RCN</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Harry DeWolf-class AOPV</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F12" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Delivered 2020 / operational</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Halifax → RCN</v>
+      </c>
+      <c r="I12" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>VES_AOPS_02</v>
+      </c>
+      <c r="B13" t="str">
+        <v>HMCS Margaret Brooke</v>
+      </c>
+      <c r="C13" t="str">
+        <v>PROG_AOPS_RCN</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Harry DeWolf-class AOPV</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F13" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Delivered 2021 / operational</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Halifax → RCN</v>
+      </c>
+      <c r="I13" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>VES_AOPS_03</v>
+      </c>
+      <c r="B14" t="str">
+        <v>HMCS Max Bernays</v>
+      </c>
+      <c r="C14" t="str">
+        <v>PROG_AOPS_RCN</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Harry DeWolf-class AOPV</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F14" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Delivered 2022 / operational</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Halifax → RCN</v>
+      </c>
+      <c r="I14" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>VES_AOPS_04</v>
+      </c>
+      <c r="B15" t="str">
+        <v>HMCS William Hall</v>
+      </c>
+      <c r="C15" t="str">
+        <v>PROG_AOPS_RCN</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Harry DeWolf-class AOPV</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F15" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Delivered 2023 / commissioned 2024</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Halifax → RCN</v>
+      </c>
+      <c r="I15" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>VES_AOPS_05</v>
+      </c>
+      <c r="B16" t="str">
+        <v>HMCS Frédérick Rolette</v>
+      </c>
+      <c r="C16" t="str">
+        <v>PROG_AOPS_RCN</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Harry DeWolf-class AOPV</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F16" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Delivered 2024 / commissioned 2025</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Halifax → RCN</v>
+      </c>
+      <c r="I16" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/news/2025/06/his-majestys-canadian-ship-frederick-rolette-commissioned-into-service.html</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>VES_AOPS_06</v>
+      </c>
+      <c r="B17" t="str">
+        <v>HMCS Robert Hampton Gray</v>
+      </c>
+      <c r="C17" t="str">
+        <v>PROG_AOPS_RCN</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Harry DeWolf-class AOPV</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Royal Canadian Navy</v>
+      </c>
+      <c r="F17" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Delivered 21 Aug 2025; commissioning expected 2026</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Halifax → RCN / Esquimalt</v>
+      </c>
+      <c r="I17" t="str">
+        <v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>VES_AOPS_07</v>
+      </c>
+      <c r="B18" t="str">
+        <v>CCGS Donjek</v>
+      </c>
+      <c r="C18" t="str">
+        <v>PROG_AOPS_CCG</v>
+      </c>
+      <c r="D18" t="str">
+        <v>AOPS Coast Guard variant</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Canadian Coast Guard</v>
+      </c>
+      <c r="F18" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Launched 29 Apr 2026; delivery expected late 2026</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Halifax → CCG</v>
+      </c>
+      <c r="I18" t="str">
+        <v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>VES_AOPS_08</v>
+      </c>
+      <c r="B19" t="str">
+        <v>CCGS Sermilik</v>
+      </c>
+      <c r="C19" t="str">
+        <v>PROG_AOPS_CCG</v>
+      </c>
+      <c r="D19" t="str">
+        <v>AOPS Coast Guard variant</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Canadian Coast Guard</v>
+      </c>
+      <c r="F19" t="str">
+        <v>YARD_IRV_HALIFAX</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Under construction; delivery expected 2027</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Halifax → CCG</v>
+      </c>
+      <c r="I19" t="str">
+        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>VES_UAE_F3_01</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ALTAF</v>
+      </c>
+      <c r="C20" t="str">
+        <v>PROG_UAE_FALAJ3</v>
+      </c>
+      <c r="D20" t="str">
+        <v>FALAJ 3 62 m missile boat</v>
+      </c>
+      <c r="E20" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F20" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Commissioned 19 Feb 2025</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I20" t="str">
+        <v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>VES_UAE_F3_02</v>
+      </c>
+      <c r="B21" t="str">
+        <v>FALAJ 3 Unit 2 — name pending</v>
+      </c>
+      <c r="C21" t="str">
+        <v>PROG_UAE_FALAJ3</v>
+      </c>
+      <c r="D21" t="str">
+        <v>FALAJ 3 62 m missile boat</v>
+      </c>
+      <c r="E21" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F21" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Programme vessel / name not confirmed</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I21" t="str">
+        <v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>VES_UAE_F3_03</v>
+      </c>
+      <c r="B22" t="str">
+        <v>FALAJ 3 Unit 3 — name pending</v>
+      </c>
+      <c r="C22" t="str">
+        <v>PROG_UAE_FALAJ3</v>
+      </c>
+      <c r="D22" t="str">
+        <v>FALAJ 3 62 m missile boat</v>
+      </c>
+      <c r="E22" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F22" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Programme vessel / name not confirmed</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I22" t="str">
+        <v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>VES_UAE_F3_04</v>
+      </c>
+      <c r="B23" t="str">
+        <v>FALAJ 3 Unit 4 — name pending</v>
+      </c>
+      <c r="C23" t="str">
+        <v>PROG_UAE_FALAJ3</v>
+      </c>
+      <c r="D23" t="str">
+        <v>FALAJ 3 62 m missile boat</v>
+      </c>
+      <c r="E23" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F23" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Programme vessel / name not confirmed</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I23" t="str">
+        <v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>VES_UAE_BAY_01</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Baynunah (P171)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>PROG_UAE_BAYNUNAH</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Baynunah-class corvette</v>
+      </c>
+      <c r="E24" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F24" t="str">
+        <v>YARD_CMN_CHERBOURG</v>
+      </c>
+      <c r="G24" t="str">
+        <v>In service</v>
+      </c>
+      <c r="H24" t="str">
+        <v>France → UAE</v>
+      </c>
+      <c r="I24" t="str">
+        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>VES_UAE_BAY_02</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Al Hesen (P172)</v>
+      </c>
+      <c r="C25" t="str">
+        <v>PROG_UAE_BAYNUNAH</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Baynunah-class corvette</v>
+      </c>
+      <c r="E25" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F25" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G25" t="str">
+        <v>In service</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I25" t="str">
+        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>VES_UAE_BAY_03</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Al Dhafra (P173)</v>
+      </c>
+      <c r="C26" t="str">
+        <v>PROG_UAE_BAYNUNAH</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Baynunah-class corvette</v>
+      </c>
+      <c r="E26" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F26" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G26" t="str">
+        <v>In service</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I26" t="str">
+        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>VES_UAE_BAY_04</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Mezyad (P174)</v>
+      </c>
+      <c r="C27" t="str">
+        <v>PROG_UAE_BAYNUNAH</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Baynunah-class corvette</v>
+      </c>
+      <c r="E27" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F27" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G27" t="str">
+        <v>In service</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I27" t="str">
+        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>VES_UAE_BAY_05</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Al Jahili (P175)</v>
+      </c>
+      <c r="C28" t="str">
+        <v>PROG_UAE_BAYNUNAH</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Baynunah-class corvette</v>
+      </c>
+      <c r="E28" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F28" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G28" t="str">
+        <v>In service</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I28" t="str">
+        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>VES_UAE_BAY_06</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Al Hili (P176)</v>
+      </c>
+      <c r="C29" t="str">
+        <v>PROG_UAE_BAYNUNAH</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Baynunah-class corvette</v>
+      </c>
+      <c r="E29" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F29" t="str">
+        <v>YARD_ADSB_ABUDHABI</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Commissioned 20 Feb 2017 / in service</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Abu Dhabi → UAE Navy</v>
+      </c>
+      <c r="I29" t="str">
+        <v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>VES_UAE_GOW_01</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Bani Yas</v>
+      </c>
+      <c r="C30" t="str">
+        <v>PROG_UAE_BANIYAS</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Gowind multi-mission corvette</v>
+      </c>
+      <c r="E30" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F30" t="str">
+        <v>YARD_NAVAL_LORIENT</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Delivered 21 Oct 2023</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Lorient → UAE</v>
+      </c>
+      <c r="I30" t="str">
+        <v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>VES_UAE_GOW_02</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Al Emarat</v>
+      </c>
+      <c r="C31" t="str">
+        <v>PROG_UAE_BANIYAS</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Gowind multi-mission corvette</v>
+      </c>
+      <c r="E31" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F31" t="str">
+        <v>YARD_NAVAL_LORIENT</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Delivered 27 Jun 2024</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Lorient → UAE</v>
+      </c>
+      <c r="I31" t="str">
+        <v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>VES_UAE_F2_02</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Qarnen</v>
+      </c>
+      <c r="C32" t="str">
+        <v>PROG_UAE_ABUDHABI</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Falaj 2 patrol vessel</v>
+      </c>
+      <c r="E32" t="str">
+        <v>UAE Navy</v>
+      </c>
+      <c r="F32" t="str">
+        <v>YARD_FIN_MUGGIANO</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Delivered / operational</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Italy → UAE</v>
+      </c>
+      <c r="I32" t="str">
+        <v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>VES_UAE_P51_02</v>
+      </c>
+      <c r="B33" t="str">
+        <v>P51MR OPV 02 — name pending</v>
+      </c>
+      <c r="C33" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D33" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E33" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F33"/>
+      <c r="G33" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H33" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I33" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>VES_UAE_P51_03</v>
+      </c>
+      <c r="B34" t="str">
+        <v>P51MR OPV 03 — name pending</v>
+      </c>
+      <c r="C34" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D34" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E34" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F34"/>
+      <c r="G34" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H34" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I34" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>VES_UAE_P51_04</v>
+      </c>
+      <c r="B35" t="str">
+        <v>P51MR OPV 04 — name pending</v>
+      </c>
+      <c r="C35" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D35" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E35" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F35"/>
+      <c r="G35" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H35" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I35" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>VES_UAE_P51_05</v>
+      </c>
+      <c r="B36" t="str">
+        <v>P51MR OPV 05 — name pending</v>
+      </c>
+      <c r="C36" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D36" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E36" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F36"/>
+      <c r="G36" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H36" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I36" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>VES_UAE_P51_06</v>
+      </c>
+      <c r="B37" t="str">
+        <v>P51MR OPV 06 — name pending</v>
+      </c>
+      <c r="C37" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D37" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E37" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F37"/>
+      <c r="G37" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H37" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I37" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>VES_UAE_P51_07</v>
+      </c>
+      <c r="B38" t="str">
+        <v>P51MR OPV 07 — name pending</v>
+      </c>
+      <c r="C38" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D38" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E38" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F38"/>
+      <c r="G38" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H38" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I38" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>VES_UAE_P51_08</v>
+      </c>
+      <c r="B39" t="str">
+        <v>P51MR OPV 08 — name pending</v>
+      </c>
+      <c r="C39" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D39" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E39" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F39"/>
+      <c r="G39" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H39" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I39" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>VES_UAE_P51_09</v>
+      </c>
+      <c r="B40" t="str">
+        <v>P51MR OPV 09 — name pending</v>
+      </c>
+      <c r="C40" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D40" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E40" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F40"/>
+      <c r="G40" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H40" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I40" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>VES_UAE_P51_10</v>
+      </c>
+      <c r="B41" t="str">
+        <v>P51MR OPV 10 — name pending</v>
+      </c>
+      <c r="C41" t="str">
+        <v>PROG_UAE_P51MR</v>
+      </c>
+      <c r="D41" t="str">
+        <v>51 m OPV</v>
+      </c>
+      <c r="E41" t="str">
+        <v>UAE Coast Guard</v>
+      </c>
+      <c r="F41"/>
+      <c r="G41" t="str">
+        <v>Contracted / name not confirmed</v>
+      </c>
+      <c r="H41" t="str">
+        <v>UAE / Italy</v>
+      </c>
+      <c r="I41" t="str">
+        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DEF_VES_ADMIRAL_ESSEN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Admiral Essen</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Missile carrier / naval vessel</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Russian Black Sea Fleet</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Reported attacked</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Novorossiysk / Black Sea</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VESSEL_SAGAR_MANTHAN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ORV Sagar Manthan</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ocean Research Vessel (Yard 3041)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Indian Navy</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Rishi Bankim Shipyard / India</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/12_defence_shipbuilding.xlsx
+++ b/data/12_defence_shipbuilding.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defence Companies" sheetId="1" r:id="R54ae9faf2b474006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="2" r:id="R2d29bbaea92c4241"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Facilities" sheetId="3" r:id="Rfd7ef2fd7c284ad3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Capabilities" sheetId="4" r:id="Rd6d4bf98e0c14643"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="5" r:id="R80ec610710cd40b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Participants" sheetId="6" r:id="R6ba5817d465e4249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Vessels" sheetId="7" r:id="Re334253c9a2a4e70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="8" r:id="R6f2cc80169fc4111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales &amp; Delivery Routes" sheetId="9" r:id="R0e5d6e20c6ce4859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announcements" sheetId="10" r:id="R6a36be628caa4e7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="Rffc8e124f6354546"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="12" r:id="Rcaee9e4085c145cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform Classes" sheetId="13" r:id="R38a546632d4445b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Status History" sheetId="14" r:id="Rbbfc6926670445c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defence Companies" sheetId="1" r:id="R039a79f82b5345f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipyards" sheetId="2" r:id="R3215b65011804cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Facilities" sheetId="3" r:id="R3aa34c493bd44411"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yard Capabilities" sheetId="4" r:id="R051f1cf496134d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programmes" sheetId="5" r:id="Ra0628256b7b64bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Participants" sheetId="6" r:id="Ra80ffc739e484174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Vessels" sheetId="7" r:id="R6aad9ebe7ad8484e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="8" r:id="R35eec9ecec7c42d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales &amp; Delivery Routes" sheetId="9" r:id="Rb00936e671b64727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announcements" sheetId="10" r:id="R7588fbd4e1a0449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="R55184f6c617348fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="12" r:id="R0f5445af69034f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform Classes" sheetId="13" r:id="R5ca99c82e553456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Status History" sheetId="14" r:id="R6543ef927235439d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -898,1163 +898,1376 @@
         <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd. (GRSE)</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Strategic shipbuilder / defence PSU</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Defence / government / research / commercial</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>Government of India, Ministry of Defence; listed PSU</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>https://www.grse.in/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="str">
-        <v>Announcement ID</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>Headline</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>Primary Entity ID</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>Programme ID</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>Event Type</v>
-      </c>
-      <c r="G1" s="4" t="str">
-        <v>Linked Entities / Topics</v>
-      </c>
-      <c r="H1" s="4" t="str">
-        <v>Source URL</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="str">
-        <v>ANN_001</v>
-      </c>
-      <c r="B2" s="8" t="str">
-        <v>2024-05-20</v>
-      </c>
-      <c r="C2" s="8" t="str">
-        <v>MAESTRAL formalised and €400m UAE Coast Guard order announced</v>
-      </c>
-      <c r="D2" s="8" t="str">
-        <v>COMP_MAESTRAL</v>
-      </c>
-      <c r="E2" s="8" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="F2" s="8" t="str">
-        <v>JV / contract</v>
-      </c>
-      <c r="G2" s="8" t="str">
-        <v>EDGE; Fincantieri; UAE Coast Guard; P51MR</v>
-      </c>
-      <c r="H2" s="8" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="str">
-        <v>ANN_002</v>
-      </c>
-      <c r="B3" s="8" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C3" s="8" t="str">
-        <v>ADSB launches first Al-Dorra-class 62m vessel for Kuwait</v>
-      </c>
-      <c r="D3" s="8" t="str">
-        <v>COMP_ADSB</v>
-      </c>
-      <c r="E3" s="8" t="str">
-        <v>PROG_ADSB_ALDORRA</v>
-      </c>
-      <c r="F3" s="8" t="str">
-        <v>Launch / export</v>
-      </c>
-      <c r="G3" s="8" t="str">
-        <v>ADSB; EDGE; Kuwait; Abu Dhabi shipyard</v>
-      </c>
-      <c r="H3" s="8" t="str">
-        <v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="str">
-        <v>ANN_003</v>
-      </c>
-      <c r="B4" s="8" t="str">
-        <v>2025-03-08</v>
-      </c>
-      <c r="C4" s="8" t="str">
-        <v>Canada awards River-class destroyer implementation contract</v>
-      </c>
-      <c r="D4" s="8" t="str">
-        <v>COMP_IRVING</v>
-      </c>
-      <c r="E4" s="8" t="str">
-        <v>PROG_RCD</v>
-      </c>
-      <c r="F4" s="8" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="G4" s="8" t="str">
-        <v>Irving; Halifax Shipyard; RCN; Lockheed Martin Canada; BAE Systems</v>
-      </c>
-      <c r="H4" s="8" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/news/2025/03/government-of-canada-announces-contract-award-for-the-construction-of-the-river-class-destroyers-for-the-royal-canadian-navy.html</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="str">
-        <v>ANN_004</v>
-      </c>
-      <c r="B5" s="8" t="str">
-        <v>2026-05-26</v>
-      </c>
-      <c r="C5" s="8" t="str">
-        <v>Seaspan reports one year of polar icebreaker progress</v>
-      </c>
-      <c r="D5" s="8" t="str">
-        <v>COMP_SEASPAN_ULC</v>
-      </c>
-      <c r="E5" s="8" t="str">
-        <v>PROG_SEA_POLAR</v>
-      </c>
-      <c r="F5" s="8" t="str">
-        <v>Construction milestone</v>
-      </c>
-      <c r="G5" s="8" t="str">
-        <v>Vancouver Shipyards; Victoria Shipyards; Ark Road; CCG</v>
-      </c>
-      <c r="H5" s="8" t="str">
-        <v>https://www.seaspan.com/press-release/seaspan-celebrates-one-year-of-progress-on-the-heavy-polar-icebreaker/</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="str">
-        <v>ANN_005</v>
-      </c>
-      <c r="B6" s="8" t="str">
-        <v>2026-01-07</v>
-      </c>
-      <c r="C6" s="8" t="str">
-        <v>Seaspan signs ASC agreements with Bollinger and Rauma</v>
-      </c>
-      <c r="D6" s="8" t="str">
-        <v>COMP_SEASPAN_ULC</v>
-      </c>
-      <c r="E6" s="8" t="str">
-        <v>PROG_US_ASC_BOLL</v>
-      </c>
-      <c r="F6" s="8" t="str">
-        <v>Design / build partnership</v>
-      </c>
-      <c r="G6" s="8" t="str">
-        <v>Seaspan; Bollinger; Rauma; Aker Arctic; USCG</v>
-      </c>
-      <c r="H6" s="8" t="str">
-        <v>https://www.seaspan.com/press-release/seaspan-inks-deal-with-bollinger-rauma-for-u-s-coast-guard-asc-program/</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="str">
-        <v>ANN_006</v>
-      </c>
-      <c r="B7" s="8" t="str">
-        <v>2026-08-24</v>
-      </c>
-      <c r="C7" s="8" t="str">
-        <v>Davie awarded six Program Icebreakers</v>
-      </c>
-      <c r="D7" s="8" t="str">
-        <v>COMP_DAVIE</v>
-      </c>
-      <c r="E7" s="8" t="str">
-        <v>PROG_DAV_PIB</v>
-      </c>
-      <c r="F7" s="8" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <v>Davie; Inocea; Lévis; Canadian Coast Guard</v>
-      </c>
-      <c r="H7" s="8" t="str">
-        <v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="str">
-        <v>ANN_007</v>
-      </c>
-      <c r="B8" s="8" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C8" s="8" t="str">
-        <v>Davie Defense states USCG ASC contract finalized</v>
-      </c>
-      <c r="D8" s="8" t="str">
-        <v>COMP_DAVIE_DEFENSE</v>
-      </c>
-      <c r="E8" s="8" t="str">
-        <v>PROG_US_ASC_DAV</v>
-      </c>
-      <c r="F8" s="8" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="G8" s="8" t="str">
-        <v>Davie Defense; USCG; Galveston / Port Arthur</v>
-      </c>
-      <c r="H8" s="8" t="str">
-        <v>https://www.daviedefense.com/</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="str">
-        <v>ANN_008</v>
-      </c>
-      <c r="B9" s="8" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="C9" s="8" t="str">
-        <v>Damen announces three Stan Patrol 5009s for Dutch Caribbean Coast Guard</v>
-      </c>
-      <c r="D9" s="8" t="str">
-        <v>COMP_DAMEN</v>
-      </c>
-      <c r="E9" s="8" t="str">
-        <v>PROG_DUTCH_CG</v>
-      </c>
-      <c r="F9" s="8" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="G9" s="8" t="str">
-        <v>Damen; Antalya; Netherlands MoD; Dutch Caribbean Coast Guard</v>
-      </c>
-      <c r="H9" s="8" t="str">
-        <v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="str">
-        <v>ANN_009</v>
-      </c>
-      <c r="B10" s="8" t="str">
-        <v>2026-09-08</v>
-      </c>
-      <c r="C10" s="8" t="str">
-        <v>SimFer begins Morebaya port commissioning</v>
-      </c>
-      <c r="D10" s="8" t="str">
-        <v>COMP_SIMFER</v>
-      </c>
-      <c r="E10" s="8" t="str"/>
-      <c r="F10" s="8" t="str">
-        <v>Port / rail commissioning</v>
-      </c>
-      <c r="G10" s="8" t="str">
-        <v>SimFer; Morebaya; rail spur; WCS port; Guinea; Rio Tinto; CIOH</v>
-      </c>
-      <c r="H10" s="8" t="str">
-        <v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="str">
-        <v>ANN_010</v>
-      </c>
-      <c r="B11" s="8" t="str">
-        <v>2026-09-08</v>
-      </c>
-      <c r="C11" s="8" t="str">
-        <v>APM Terminals enters exclusive negotiations over Badagry deepsea port</v>
-      </c>
-      <c r="D11" s="8" t="str">
-        <v>COMP_BADAGRY_PORT_DEV</v>
-      </c>
-      <c r="E11" s="8" t="str"/>
-      <c r="F11" s="8" t="str">
-        <v>Port development</v>
-      </c>
-      <c r="G11" s="8" t="str">
-        <v>APM Terminals; Badagry; Nigeria; Apapa; Onne</v>
-      </c>
-      <c r="H11" s="8" t="str">
-        <v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>ANN_AOPS_01</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2025-08-21</v>
-      </c>
-      <c r="C12" t="str">
-        <v>RCN accepts sixth and final AOPS, HMCS Robert Hampton Gray</v>
-      </c>
-      <c r="D12" t="str">
-        <v>COMP_IRVING</v>
-      </c>
-      <c r="E12" t="str">
-        <v>PROG_AOPS_RCN</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Delivery</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Irving; Halifax Shipyard; RCN; Robert Hampton Gray</v>
-      </c>
-      <c r="H12" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>ANN_AOPS_02</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Canadian Coast Guard launches CCGS Donjek</v>
-      </c>
-      <c r="D13" t="str">
-        <v>COMP_IRVING</v>
-      </c>
-      <c r="E13" t="str">
-        <v>PROG_AOPS_CCG</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Launch</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Irving; Halifax Shipyard; CCG; Donjek; Sermilik</v>
-      </c>
-      <c r="H13" t="str">
-        <v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>ANN_UAE_01</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2021-05-18</v>
-      </c>
-      <c r="C14" t="str">
-        <v>ADSB awarded AED3.5bn contract for four FALAJ 3 vessels</v>
-      </c>
-      <c r="D14" t="str">
-        <v>COMP_ADSB</v>
-      </c>
-      <c r="E14" t="str">
-        <v>PROG_UAE_FALAJ3</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="G14" t="str">
-        <v>ADSB; UAE Navy; UAE Ministry of Defence; FALAJ3</v>
-      </c>
-      <c r="H14" t="str">
-        <v>https://edgegroup.ae/share/pdf/news/173</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>ANN_UAE_02</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2025-01-14</v>
-      </c>
-      <c r="C15" t="str">
-        <v>ADSB launches first FALAJ 3 vessel</v>
-      </c>
-      <c r="D15" t="str">
-        <v>COMP_ADSB</v>
-      </c>
-      <c r="E15" t="str">
-        <v>PROG_UAE_FALAJ3</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Launch</v>
-      </c>
-      <c r="G15" t="str">
-        <v>ADSB; UAE Navy; first FALAJ3</v>
-      </c>
-      <c r="H15" t="str">
-        <v>https://edgegroup.ae/news/adsb-launches-first-vessel-prestigious-falaj-3-programme</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>ANN_UAE_03</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2025-02-19</v>
-      </c>
-      <c r="C16" t="str">
-        <v>ALTAF commissioned as first FALAJ 3 missile boat</v>
-      </c>
-      <c r="D16" t="str">
-        <v>COMP_ADSB</v>
-      </c>
-      <c r="E16" t="str">
-        <v>PROG_UAE_FALAJ3</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Commissioning</v>
-      </c>
-      <c r="G16" t="str">
-        <v>ALTAF; ADSB; EDGE; UAE Navy</v>
-      </c>
-      <c r="H16" t="str">
-        <v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>ANN_UAE_04</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2023-10-21</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Naval Group delivers Bani Yas to UAE Navy</v>
-      </c>
-      <c r="D17" t="str">
-        <v>COMP_NAVAL_GROUP</v>
-      </c>
-      <c r="E17" t="str">
-        <v>PROG_UAE_BANIYAS</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Delivery</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Bani Yas; Lorient; UAE Navy</v>
-      </c>
-      <c r="H17" t="str">
-        <v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>ANN_UAE_05</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2024-06-27</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Naval Group delivers Al Emarat to UAE Navy</v>
-      </c>
-      <c r="D18" t="str">
-        <v>COMP_NAVAL_GROUP</v>
-      </c>
-      <c r="E18" t="str">
-        <v>PROG_UAE_BANIYAS</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Delivery</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Al Emarat; Lorient; UAE Navy</v>
-      </c>
-      <c r="H18" t="str">
-        <v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>ANN_UAE_06</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2017-02-20</v>
-      </c>
-      <c r="C19" t="str">
-        <v>UAE commissions Al Hili, sixth Baynunah-class corvette</v>
-      </c>
-      <c r="D19" t="str">
-        <v>COMP_ADSB</v>
-      </c>
-      <c r="E19" t="str">
-        <v>PROG_UAE_BAYNUNAH</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Commissioning</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Al Hili; ADSB; UAE Navy</v>
-      </c>
-      <c r="H19" t="str">
-        <v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>ANN_UAE_07</v>
-      </c>
-      <c r="B20" t="str">
-        <v>2013-01-08</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Fincantieri delivers Abu Dhabi corvette and Ghantut patrol vessel</v>
-      </c>
-      <c r="D20" t="str">
-        <v>COMP_FINCANTIERI</v>
-      </c>
-      <c r="E20" t="str">
-        <v>PROG_UAE_ABUDHABI</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Delivery</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Abu Dhabi; Ghantut; UAE Navy; Muggiano</v>
-      </c>
-      <c r="H20" t="str">
-        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ANN260911_MI01</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Indian Navy launches advanced Ocean Research Vessel ORV Sagar Manthan</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VESSEL_SAGAR_MANTHAN</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Launch</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Yard 3041; Rishi Bankim Shipyard; Indian Navy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>Announcement ID</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="C1" s="4" t="str">
+        <x:v>Headline</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="str">
+        <x:v>Primary Entity ID</x:v>
+      </x:c>
+      <x:c r="E1" s="4" t="str">
+        <x:v>Programme ID</x:v>
+      </x:c>
+      <x:c r="F1" s="4" t="str">
+        <x:v>Event Type</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="str">
+        <x:v>Linked Entities / Topics</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="8" t="str">
+        <x:v>ANN_001</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>2024-05-20</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>MAESTRAL formalised and €400m UAE Coast Guard order announced</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>COMP_MAESTRAL</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="str">
+        <x:v>JV / contract</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="str">
+        <x:v>EDGE; Fincantieri; UAE Coast Guard; P51MR</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
+        <x:v>ANN_002</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>2026-02-03</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="str">
+        <x:v>ADSB launches first Al-Dorra-class 62m vessel for Kuwait</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="str">
+        <x:v>PROG_ADSB_ALDORRA</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="str">
+        <x:v>Launch / export</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="str">
+        <x:v>ADSB; EDGE; Kuwait; Abu Dhabi shipyard</x:v>
+      </x:c>
+      <x:c r="H3" s="8" t="str">
+        <x:v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="8" t="str">
+        <x:v>ANN_003</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>2025-03-08</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>Canada awards River-class destroyer implementation contract</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str">
+        <x:v>PROG_RCD</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="str">
+        <x:v>Contract</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="str">
+        <x:v>Irving; Halifax Shipyard; RCN; Lockheed Martin Canada; BAE Systems</x:v>
+      </x:c>
+      <x:c r="H4" s="8" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/03/government-of-canada-announces-contract-award-for-the-construction-of-the-river-class-destroyers-for-the-royal-canadian-navy.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>ANN_004</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>2026-05-26</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>Seaspan reports one year of polar icebreaker progress</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>COMP_SEASPAN_ULC</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>PROG_SEA_POLAR</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="str">
+        <x:v>Construction milestone</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
+        <x:v>Vancouver Shipyards; Victoria Shipyards; Ark Road; CCG</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-celebrates-one-year-of-progress-on-the-heavy-polar-icebreaker/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="8" t="str">
+        <x:v>ANN_005</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>2026-01-07</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>Seaspan signs ASC agreements with Bollinger and Rauma</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>COMP_SEASPAN_ULC</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str">
+        <x:v>PROG_US_ASC_BOLL</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="str">
+        <x:v>Design / build partnership</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>Seaspan; Bollinger; Rauma; Aker Arctic; USCG</x:v>
+      </x:c>
+      <x:c r="H6" s="8" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-inks-deal-with-bollinger-rauma-for-u-s-coast-guard-asc-program/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="8" t="str">
+        <x:v>ANN_006</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>Davie awarded six Program Icebreakers</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str">
+        <x:v>PROG_DAV_PIB</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="str">
+        <x:v>Contract</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>Davie; Inocea; Lévis; Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="H7" s="8" t="str">
+        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="8" t="str">
+        <x:v>ANN_007</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>2026-05-13</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str">
+        <x:v>Davie Defense states USCG ASC contract finalized</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>COMP_DAVIE_DEFENSE</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str">
+        <x:v>PROG_US_ASC_DAV</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="str">
+        <x:v>Contract</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>Davie Defense; USCG; Galveston / Port Arthur</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="str">
+        <x:v>https://www.daviedefense.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="8" t="str">
+        <x:v>ANN_008</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="str">
+        <x:v>2026-03-16</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="str">
+        <x:v>Damen announces three Stan Patrol 5009s for Dutch Caribbean Coast Guard</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>COMP_DAMEN</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str">
+        <x:v>PROG_DUTCH_CG</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="str">
+        <x:v>Contract</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
+        <x:v>Damen; Antalya; Netherlands MoD; Dutch Caribbean Coast Guard</x:v>
+      </x:c>
+      <x:c r="H9" s="8" t="str">
+        <x:v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="8" t="str">
+        <x:v>ANN_009</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="str">
+        <x:v>SimFer begins Morebaya port commissioning</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str">
+        <x:v>COMP_SIMFER</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="str"/>
+      <x:c r="F10" s="8" t="str">
+        <x:v>Port / rail commissioning</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
+        <x:v>SimFer; Morebaya; rail spur; WCS port; Guinea; Rio Tinto; CIOH</x:v>
+      </x:c>
+      <x:c r="H10" s="8" t="str">
+        <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="8" t="str">
+        <x:v>ANN_010</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>APM Terminals enters exclusive negotiations over Badagry deepsea port</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>COMP_BADAGRY_PORT_DEV</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str"/>
+      <x:c r="F11" s="8" t="str">
+        <x:v>Port development</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
+        <x:v>APM Terminals; Badagry; Nigeria; Apapa; Onne</x:v>
+      </x:c>
+      <x:c r="H11" s="8" t="str">
+        <x:v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>ANN_AOPS_01</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>2025-08-21</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>RCN accepts sixth and final AOPS, HMCS Robert Hampton Gray</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Irving; Halifax Shipyard; RCN; Robert Hampton Gray</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>ANN_AOPS_02</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2026-04-29</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Canadian Coast Guard launches CCGS Donjek</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>COMP_IRVING</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Launch</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>Irving; Halifax Shipyard; CCG; Donjek; Sermilik</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>ANN_UAE_01</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2021-05-18</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>ADSB awarded AED3.5bn contract for four FALAJ 3 vessels</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Contract</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>ADSB; UAE Navy; UAE Ministry of Defence; FALAJ3</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>https://edgegroup.ae/share/pdf/news/173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>ANN_UAE_02</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>2025-01-14</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>ADSB launches first FALAJ 3 vessel</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Launch</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>ADSB; UAE Navy; first FALAJ3</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>https://edgegroup.ae/news/adsb-launches-first-vessel-prestigious-falaj-3-programme</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>ANN_UAE_03</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2025-02-19</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>ALTAF commissioned as first FALAJ 3 missile boat</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Commissioning</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>ALTAF; ADSB; EDGE; UAE Navy</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>ANN_UAE_04</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2023-10-21</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Naval Group delivers Bani Yas to UAE Navy</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Bani Yas; Lorient; UAE Navy</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>ANN_UAE_05</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>2024-06-27</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Naval Group delivers Al Emarat to UAE Navy</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>COMP_NAVAL_GROUP</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Al Emarat; Lorient; UAE Navy</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>ANN_UAE_06</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>2017-02-20</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>UAE commissions Al Hili, sixth Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>COMP_ADSB</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Commissioning</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Al Hili; ADSB; UAE Navy</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>ANN_UAE_07</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>2013-01-08</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Fincantieri delivers Abu Dhabi corvette and Ghantut patrol vessel</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>COMP_FINCANTIERI</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>PROG_UAE_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Delivery</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Abu Dhabi; Ghantut; UAE Navy; Muggiano</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>ANN260911_MI01</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>NCPOR/MoES launches advanced Ocean Research Vessel ORV Sagar Manthan</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Launch / naming</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Yard 3041; NCPOR; Ministry of Earth Sciences; Deep Ocean Mission; Rishi Bankim Shipyard</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>ANN_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2024-07-16</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>GRSE signs ₹840 crore NCPOR Ocean Research Vessel contract</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Contract</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>NCPOR; MoES; Yard 3041; Deep Ocean Mission</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Signing_of_Contract_for_construction_and_delivery_of_ORV_for_NCPOR.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>ANN_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>2024-11-29</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>GRSE cuts first steel for NCPOR Ocean Research Vessel</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>Construction milestone</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Yard 3041; NCPOR; ORV Sagar Manthan</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>ANN_SAGAR_003</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>2026-04-08</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Keel laid for NCPOR Ocean Research Vessel Yard 3041</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Keel laying</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>Yard 3041; NCPOR; ORV Sagar Manthan</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>ANN_SAGAR_004</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>2024-10-29</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>GRSE signs ₹490.98 crore Acoustic Research Ship contract with NPOL/DRDO</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>PROG_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>Contract</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>NPOL; DRDO; Yard 3058</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>ANN_SAGAR_005</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>2025-04-16</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>GRSE commences construction of NPOL Acoustic Research Ship</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>PROG_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>Construction start</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>NPOL; DRDO; Yard 3058</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>https://www.grse.in/press-releases-2025-26-quarter1/</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="str">
-        <v>Source ID</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>Publisher</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>Supports</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>URL</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>Checked As Of</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="str">
-        <v>SRC127_001</v>
-      </c>
-      <c r="B2" s="8" t="str">
-        <v>EDGE Group</v>
-      </c>
-      <c r="C2" s="8" t="str">
-        <v>MAESTRAL JV / UAE Coast Guard order</v>
-      </c>
-      <c r="D2" s="8" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-      <c r="E2" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="str">
-        <v>SRC127_002</v>
-      </c>
-      <c r="B3" s="8" t="str">
-        <v>EDGE Group</v>
-      </c>
-      <c r="C3" s="8" t="str">
-        <v>ADSB / Al-Dorra launch</v>
-      </c>
-      <c r="D3" s="8" t="str">
-        <v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</v>
-      </c>
-      <c r="E3" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="str">
-        <v>SRC127_003</v>
-      </c>
-      <c r="B4" s="8" t="str">
-        <v>Government of Canada</v>
-      </c>
-      <c r="C4" s="8" t="str">
-        <v>River-class Destroyer</v>
-      </c>
-      <c r="D4" s="8" t="str">
-        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/river-class-destroyer.html</v>
-      </c>
-      <c r="E4" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="str">
-        <v>SRC127_004</v>
-      </c>
-      <c r="B5" s="8" t="str">
-        <v>Government of Canada</v>
-      </c>
-      <c r="C5" s="8" t="str">
-        <v>AOPS</v>
-      </c>
-      <c r="D5" s="8" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/corporate/reports-publications/departmental-plans/departmental-plan-2026-27/status-report-transformational-major-capital-projects.html</v>
-      </c>
-      <c r="E5" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="str">
-        <v>SRC127_005</v>
-      </c>
-      <c r="B6" s="8" t="str">
-        <v>Seaspan</v>
-      </c>
-      <c r="C6" s="8" t="str">
-        <v>Shipyards / roles</v>
-      </c>
-      <c r="D6" s="8" t="str">
-        <v>https://www.seaspan.com/seaspan-shipyards/</v>
-      </c>
-      <c r="E6" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="str">
-        <v>SRC127_006</v>
-      </c>
-      <c r="B7" s="8" t="str">
-        <v>Seaspan</v>
-      </c>
-      <c r="C7" s="8" t="str">
-        <v>ASC partnership</v>
-      </c>
-      <c r="D7" s="8" t="str">
-        <v>https://www.seaspan.com/press-release/seaspan-inks-deal-with-bollinger-rauma-for-u-s-coast-guard-asc-program/</v>
-      </c>
-      <c r="E7" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="str">
-        <v>SRC127_007</v>
-      </c>
-      <c r="B8" s="8" t="str">
-        <v>Davie</v>
-      </c>
-      <c r="C8" s="8" t="str">
-        <v>Six Program Icebreakers</v>
-      </c>
-      <c r="D8" s="8" t="str">
-        <v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</v>
-      </c>
-      <c r="E8" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="str">
-        <v>SRC127_008</v>
-      </c>
-      <c r="B9" s="8" t="str">
-        <v>Davie Defense</v>
-      </c>
-      <c r="C9" s="8" t="str">
-        <v>US facilities / ASC announcements</v>
-      </c>
-      <c r="D9" s="8" t="str">
-        <v>https://www.daviedefense.com/</v>
-      </c>
-      <c r="E9" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="str">
-        <v>SRC127_009</v>
-      </c>
-      <c r="B10" s="8" t="str">
-        <v>Bollinger</v>
-      </c>
-      <c r="C10" s="8" t="str">
-        <v>Yard network / Houma / Gulfport</v>
-      </c>
-      <c r="D10" s="8" t="str">
-        <v>https://www.bollingershipyards.com/locations/</v>
-      </c>
-      <c r="E10" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="str">
-        <v>SRC127_010</v>
-      </c>
-      <c r="B11" s="8" t="str">
-        <v>RMC</v>
-      </c>
-      <c r="C11" s="8" t="str">
-        <v>Rauma capabilities</v>
-      </c>
-      <c r="D11" s="8" t="str">
-        <v>https://rmcfinland.fi/capabilities/</v>
-      </c>
-      <c r="E11" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="str">
-        <v>SRC127_011</v>
-      </c>
-      <c r="B12" s="8" t="str">
-        <v>Damen</v>
-      </c>
-      <c r="C12" s="8" t="str">
-        <v>Dutch Caribbean Coast Guard / Antalya</v>
-      </c>
-      <c r="D12" s="8" t="str">
-        <v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</v>
-      </c>
-      <c r="E12" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="str">
-        <v>SRC127_012</v>
-      </c>
-      <c r="B13" s="8" t="str">
-        <v>Fincantieri</v>
-      </c>
-      <c r="C13" s="8" t="str">
-        <v>UAE Navy Muggiano deliveries</v>
-      </c>
-      <c r="D13" s="8" t="str">
-        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
-      </c>
-      <c r="E13" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="str">
-        <v>SRC127_013</v>
-      </c>
-      <c r="B14" s="8" t="str">
-        <v>RMK Marine</v>
-      </c>
-      <c r="C14" s="8" t="str">
-        <v>Dual-use profile</v>
-      </c>
-      <c r="D14" s="8" t="str">
-        <v>https://www.rmkmarine.com.tr/Default.aspx</v>
-      </c>
-      <c r="E14" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="str">
-        <v>SRC127_014</v>
-      </c>
-      <c r="B15" s="8" t="str">
-        <v>Sefine</v>
-      </c>
-      <c r="C15" s="8" t="str">
-        <v>Commercial / government / repair profile</v>
-      </c>
-      <c r="D15" s="8" t="str">
-        <v>https://www.sefine.com.tr/</v>
-      </c>
-      <c r="E15" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="str">
-        <v>SRC127_015</v>
-      </c>
-      <c r="B16" s="8" t="str">
-        <v>SimFer</v>
-      </c>
-      <c r="C16" s="8" t="str">
-        <v>Morebaya commissioning</v>
-      </c>
-      <c r="D16" s="8" t="str">
-        <v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</v>
-      </c>
-      <c r="E16" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="str">
-        <v>SRC127_016</v>
-      </c>
-      <c r="B17" s="8" t="str">
-        <v>Splash247</v>
-      </c>
-      <c r="C17" s="8" t="str">
-        <v>Badagry negotiations</v>
-      </c>
-      <c r="D17" s="8" t="str">
-        <v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</v>
-      </c>
-      <c r="E17" s="8" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>SRC131_001</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Government of Canada</v>
-      </c>
-      <c r="C18" t="str">
-        <v>RCN AOPS fleet / six deliveries</v>
-      </c>
-      <c r="D18" t="str">
-        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-navy.html</v>
-      </c>
-      <c r="E18" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>SRC131_002</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Government of Canada</v>
-      </c>
-      <c r="C19" t="str">
-        <v>AOPS project updates / delivery timeline</v>
-      </c>
-      <c r="D19" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
-      </c>
-      <c r="E19" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>SRC131_003</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Canadian Coast Guard</v>
-      </c>
-      <c r="C20" t="str">
-        <v>CCGS Donjek launch / CCG AOPS status</v>
-      </c>
-      <c r="D20" t="str">
-        <v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</v>
-      </c>
-      <c r="E20" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>SRC131_004</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Government of Canada</v>
-      </c>
-      <c r="C21" t="str">
-        <v>CCG AOPS programme budget / delivery</v>
-      </c>
-      <c r="D21" t="str">
-        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</v>
-      </c>
-      <c r="E21" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>SRC131_005</v>
-      </c>
-      <c r="B22" t="str">
-        <v>EDGE / ADSB</v>
-      </c>
-      <c r="C22" t="str">
-        <v>FALAJ3 AED3.5bn / four-vessel contract</v>
-      </c>
-      <c r="D22" t="str">
-        <v>https://edgegroup.ae/share/pdf/news/173</v>
-      </c>
-      <c r="E22" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>SRC131_006</v>
-      </c>
-      <c r="B23" t="str">
-        <v>EDGE / ADSB</v>
-      </c>
-      <c r="C23" t="str">
-        <v>ALTAF commissioning / first-of-class</v>
-      </c>
-      <c r="D23" t="str">
-        <v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</v>
-      </c>
-      <c r="E23" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>SRC131_007</v>
-      </c>
-      <c r="B24" t="str">
-        <v>EDGE / ADSB</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Baynunah programme / six corvettes</v>
-      </c>
-      <c r="D24" t="str">
-        <v>https://edgegroup.ae/adsb</v>
-      </c>
-      <c r="E24" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>SRC131_008</v>
-      </c>
-      <c r="B25" t="str">
-        <v>WAM</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Al Hili sixth Baynunah commissioned</v>
-      </c>
-      <c r="D25" t="str">
-        <v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</v>
-      </c>
-      <c r="E25" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>SRC131_009</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Fincantieri</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Abu Dhabi / Falaj 2 UAE deliveries</v>
-      </c>
-      <c r="D26" t="str">
-        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
-      </c>
-      <c r="E26" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>SRC131_010</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Naval Group</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Bani Yas delivery</v>
-      </c>
-      <c r="D27" t="str">
-        <v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</v>
-      </c>
-      <c r="E27" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>SRC131_011</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Naval Group</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Al Emarat delivery</v>
-      </c>
-      <c r="D28" t="str">
-        <v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</v>
-      </c>
-      <c r="E28" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>SRC131_012</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Fincantieri</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Qarnen launch / Falaj 2 programme</v>
-      </c>
-      <c r="D29" t="str">
-        <v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</v>
-      </c>
-      <c r="E29" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>SRC131_013</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Public fleet reference</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Baynunah class vessel names / pennants cross-check</v>
-      </c>
-      <c r="D30" t="str">
-        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
-      </c>
-      <c r="E30" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>SRC131_014</v>
-      </c>
-      <c r="B31" t="str">
-        <v>EDGE / MAESTRAL</v>
-      </c>
-      <c r="C31" t="str">
-        <v>UAE Coast Guard ten P51MR order</v>
-      </c>
-      <c r="D31" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-      <c r="E31" t="str">
-        <v>2026-09-09</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SRC260911_MI01</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Marine Insight</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Admiral Essen attack report in Novorossiysk</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SRC260911_MI15</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Marine Insight</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ORV Sagar Manthan launch at Rishi Bankim Shipyard</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="str">
+        <x:v>Publisher</x:v>
+      </x:c>
+      <x:c r="C1" s="4" t="str">
+        <x:v>Supports</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="str">
+        <x:v>URL</x:v>
+      </x:c>
+      <x:c r="E1" s="4" t="str">
+        <x:v>Checked As Of</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="8" t="str">
+        <x:v>SRC127_001</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>EDGE Group</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>MAESTRAL JV / UAE Coast Guard order</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
+        <x:v>SRC127_002</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>EDGE Group</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="str">
+        <x:v>ADSB / Al-Dorra launch</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="str">
+        <x:v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="8" t="str">
+        <x:v>SRC127_003</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>River-class Destroyer</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/river-class-destroyer.html</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>SRC127_004</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>AOPS</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/corporate/reports-publications/departmental-plans/departmental-plan-2026-27/status-report-transformational-major-capital-projects.html</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="8" t="str">
+        <x:v>SRC127_005</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>Seaspan</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>Shipyards / roles</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>https://www.seaspan.com/seaspan-shipyards/</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="8" t="str">
+        <x:v>SRC127_006</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>Seaspan</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>ASC partnership</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-inks-deal-with-bollinger-rauma-for-u-s-coast-guard-asc-program/</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="8" t="str">
+        <x:v>SRC127_007</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>Davie</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str">
+        <x:v>Six Program Icebreakers</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="8" t="str">
+        <x:v>SRC127_008</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="str">
+        <x:v>Davie Defense</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="str">
+        <x:v>US facilities / ASC announcements</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>https://www.daviedefense.com/</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="8" t="str">
+        <x:v>SRC127_009</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="str">
+        <x:v>Bollinger</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="str">
+        <x:v>Yard network / Houma / Gulfport</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str">
+        <x:v>https://www.bollingershipyards.com/locations/</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="8" t="str">
+        <x:v>SRC127_010</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>RMC</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>Rauma capabilities</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>https://rmcfinland.fi/capabilities/</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="8" t="str">
+        <x:v>SRC127_011</x:v>
+      </x:c>
+      <x:c r="B12" s="8" t="str">
+        <x:v>Damen</x:v>
+      </x:c>
+      <x:c r="C12" s="8" t="str">
+        <x:v>Dutch Caribbean Coast Guard / Antalya</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="str">
+        <x:v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="8" t="str">
+        <x:v>SRC127_012</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="str">
+        <x:v>Fincantieri</x:v>
+      </x:c>
+      <x:c r="C13" s="8" t="str">
+        <x:v>UAE Navy Muggiano deliveries</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="8" t="str">
+        <x:v>SRC127_013</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>RMK Marine</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>Dual-use profile</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>https://www.rmkmarine.com.tr/Default.aspx</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="8" t="str">
+        <x:v>SRC127_014</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>Sefine</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>Commercial / government / repair profile</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>https://www.sefine.com.tr/</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="8" t="str">
+        <x:v>SRC127_015</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="str">
+        <x:v>SimFer</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="str">
+        <x:v>Morebaya commissioning</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>https://simfer-sa.com/en/media-centre/press-releases/simfer-starts-staged-commissioning-of-key-port-infrastructure-at-morebaya/</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="8" t="str">
+        <x:v>SRC127_016</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="str">
+        <x:v>Badagry negotiations</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="str">
+        <x:v>https://splash247.com/maersk-port-arm-lines-up-badagry-as-next-nigerian-gateway/</x:v>
+      </x:c>
+      <x:c r="E17" s="8" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>SRC131_001</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>RCN AOPS fleet / six deliveries</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-navy.html</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>SRC131_002</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>AOPS project updates / delivery timeline</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>SRC131_003</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>CCGS Donjek launch / CCG AOPS status</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>SRC131_004</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Government of Canada</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>CCG AOPS programme budget / delivery</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>SRC131_005</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>EDGE / ADSB</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>FALAJ3 AED3.5bn / four-vessel contract</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>https://edgegroup.ae/share/pdf/news/173</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>SRC131_006</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>EDGE / ADSB</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>ALTAF commissioning / first-of-class</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>SRC131_007</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>EDGE / ADSB</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Baynunah programme / six corvettes</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>https://edgegroup.ae/adsb</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>SRC131_008</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>WAM</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Al Hili sixth Baynunah commissioned</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>SRC131_009</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Fincantieri</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Abu Dhabi / Falaj 2 UAE deliveries</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>SRC131_010</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Naval Group</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Bani Yas delivery</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>SRC131_011</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Naval Group</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Al Emarat delivery</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>SRC131_012</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Fincantieri</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Qarnen launch / Falaj 2 programme</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>SRC131_013</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Public fleet reference</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Baynunah class vessel names / pennants cross-check</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>SRC131_014</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>EDGE / MAESTRAL</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>UAE Coast Guard ten P51MR order</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SRC260911_MI01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Marine Insight</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Admiral Essen attack report in Novorossiysk</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-11</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>SRC260911_MI15</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Press Information Bureau / Government of India</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>ORV Sagar Manthan launch; correct customer/operator NCPOR/MoES</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>SRC_SAGAR_DEF_01</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>GRSE</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>NCPOR ORV contract and technical specifications</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Signing_of_Contract_for_construction_and_delivery_of_ORV_for_NCPOR.pdf</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>SRC_SAGAR_DEF_02</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>NCPOR</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>ORV Sagar Kanya official vessel history</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>https://ncpor.res.in/pages/view/260/167-orv-sagar-kanya</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>SRC_SAGAR_DEF_03</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>GRSE</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>NPOL Acoustic Research Ship contract and specifications</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>SRC_SAGAR_DEF_04</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>GRSE</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>ARS construction commencement</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>https://www.grse.in/press-releases-2025-26-quarter1/</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3485,6 +3698,35 @@
         <x:v>https://www.reuters.com/world/asia-pacific/fire-cargo-vessel-china-shipyard-causes-major-casualties-state-media-reports-2026-09-10/</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>YARD_GRSE_RISHI_BANKIM</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>GRSE Rishi Bankim Shipyard / Kolkata build complex</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Kolkata, West Bengal</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Strategic naval / research vessel shipyard</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>ORV Sagar Manthan Yard 3041; Acoustic Research Ship Yard 3058</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5080,6 +5322,76 @@
         <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>NCPOR Ocean Research Vessel / ORV Sagar Manthan</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Civil government research</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>NCPOR / Ministry of Earth Sciences</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Ocean Research Vessel / Yard 3041</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>₹840 crore (~US$100.50m contract-date normalized)</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>Launched / outfitting; delivery 2028</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>India → global ocean research / Southern Ocean capable</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>PROG_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>NPOL Acoustic Research Ship</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Defence R&amp;D</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>NPOL / DRDO</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Acoustic Research Ship / Yard 3058</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>₹490.98 crore (~US$58.40m contract-date normalized)</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5571,1262 +5883,1399 @@
         <x:v>UAE Coast Guard</x:v>
       </x:c>
     </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Prime contractor / builder</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>GRSE Yard 3041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>GOV_NCPOR</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Customer / future operator</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>NCPOR under Ministry of Earth Sciences</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>GOV_MOES_INDIA</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Programme ministry</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>Deep Ocean Mission / civilian science</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>PROG_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Prime contractor / builder</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>GRSE Yard 3058</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>PROG_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>GOV_NPOL</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Customer / future operator</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>NPOL under DRDO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>PROG_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>GOV_DRDO_INDIA</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>Parent R&amp;D organisation</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Defence R&amp;D</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="str">
-        <v>Vessel ID</v>
-      </c>
-      <c r="B1" s="4" t="str">
-        <v>Vessel</v>
-      </c>
-      <c r="C1" s="4" t="str">
-        <v>Programme ID</v>
-      </c>
-      <c r="D1" s="4" t="str">
-        <v>Class / Type</v>
-      </c>
-      <c r="E1" s="4" t="str">
-        <v>Customer / Operator</v>
-      </c>
-      <c r="F1" s="4" t="str">
-        <v>Build Yard ID</v>
-      </c>
-      <c r="G1" s="4" t="str">
-        <v>Status</v>
-      </c>
-      <c r="H1" s="4" t="str">
-        <v>Build / Delivery Route</v>
-      </c>
-      <c r="I1" s="4" t="str">
-        <v>Source URL</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="str">
-        <v>VES_DEF_001</v>
-      </c>
-      <c r="B2" s="8" t="str">
-        <v>HMCS Fraser</v>
-      </c>
-      <c r="C2" s="8" t="str">
-        <v>PROG_RCD</v>
-      </c>
-      <c r="D2" s="8" t="str">
-        <v>River-class Destroyer</v>
-      </c>
-      <c r="E2" s="8" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F2" s="8" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G2" s="8" t="str">
-        <v>Full-rate production</v>
-      </c>
-      <c r="H2" s="8" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="I2" s="8" t="str">
-        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/river-class-destroyer.html</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="str">
-        <v>VES_DEF_002</v>
-      </c>
-      <c r="B3" s="8" t="str">
-        <v>Joint Support Ship 1</v>
-      </c>
-      <c r="C3" s="8" t="str">
-        <v>PROG_SEA_JSS</v>
-      </c>
-      <c r="D3" s="8" t="str">
-        <v>Joint Support Ship</v>
-      </c>
-      <c r="E3" s="8" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F3" s="8" t="str">
-        <v>YARD_SEA_VAN</v>
-      </c>
-      <c r="G3" s="8" t="str">
-        <v>Under construction</v>
-      </c>
-      <c r="H3" s="8" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="I3" s="8" t="str">
-        <v>https://www.seaspan.com/seaspan-shipyards/shipbuilding/joint-support-ships/</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="str">
-        <v>VES_DEF_003</v>
-      </c>
-      <c r="B4" s="8" t="str">
-        <v>Joint Support Ship 2</v>
-      </c>
-      <c r="C4" s="8" t="str">
-        <v>PROG_SEA_JSS</v>
-      </c>
-      <c r="D4" s="8" t="str">
-        <v>Joint Support Ship</v>
-      </c>
-      <c r="E4" s="8" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F4" s="8" t="str">
-        <v>YARD_SEA_VAN</v>
-      </c>
-      <c r="G4" s="8" t="str">
-        <v>Under construction</v>
-      </c>
-      <c r="H4" s="8" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="I4" s="8" t="str">
-        <v>https://www.seaspan.com/seaspan-shipyards/shipbuilding/joint-support-ships/</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="str">
-        <v>VES_DEF_004</v>
-      </c>
-      <c r="B5" s="8" t="str">
-        <v>Seaspan Heavy Polar Icebreaker</v>
-      </c>
-      <c r="C5" s="8" t="str">
-        <v>PROG_SEA_POLAR</v>
-      </c>
-      <c r="D5" s="8" t="str">
-        <v>Heavy polar icebreaker</v>
-      </c>
-      <c r="E5" s="8" t="str">
-        <v>Canadian Coast Guard</v>
-      </c>
-      <c r="F5" s="8" t="str">
-        <v>YARD_SEA_VAN</v>
-      </c>
-      <c r="G5" s="8" t="str">
-        <v>Under construction</v>
-      </c>
-      <c r="H5" s="8" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="I5" s="8" t="str">
-        <v>https://www.seaspan.com/press-release/seaspan-celebrates-one-year-of-progress-on-the-heavy-polar-icebreaker/</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="str">
-        <v>VES_DEF_005</v>
-      </c>
-      <c r="B6" s="8" t="str">
-        <v>Polar Max</v>
-      </c>
-      <c r="C6" s="8" t="str">
-        <v>PROG_DAV_POLARMAX</v>
-      </c>
-      <c r="D6" s="8" t="str">
-        <v>Heavy polar icebreaker</v>
-      </c>
-      <c r="E6" s="8" t="str">
-        <v>Canadian Coast Guard</v>
-      </c>
-      <c r="F6" s="8" t="str">
-        <v>YARD_DAVIE_LEVIS</v>
-      </c>
-      <c r="G6" s="8" t="str">
-        <v>Under construction</v>
-      </c>
-      <c r="H6" s="8" t="str">
-        <v>Finland + Canada</v>
-      </c>
-      <c r="I6" s="8" t="str">
-        <v>https://www.davie.ca/en/news/20260331-davie-begins-construction-of-polarmax-en/</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="str">
-        <v>VES_DEF_006</v>
-      </c>
-      <c r="B7" s="8" t="str">
-        <v>Abu Dhabi</v>
-      </c>
-      <c r="C7" s="8" t="str">
-        <v>PROG_UAE_ABUDHABI</v>
-      </c>
-      <c r="D7" s="8" t="str">
-        <v>Abu Dhabi-class corvette</v>
-      </c>
-      <c r="E7" s="8" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F7" s="8" t="str">
-        <v>YARD_FIN_MUGGIANO</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <v>Delivered 2013</v>
-      </c>
-      <c r="H7" s="8" t="str">
-        <v>Italy → UAE</v>
-      </c>
-      <c r="I7" s="8" t="str">
-        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="str">
-        <v>VES_DEF_007</v>
-      </c>
-      <c r="B8" s="8" t="str">
-        <v>Ghantut</v>
-      </c>
-      <c r="C8" s="8" t="str">
-        <v>PROG_UAE_ABUDHABI</v>
-      </c>
-      <c r="D8" s="8" t="str">
-        <v>Falaj 2 patrol vessel</v>
-      </c>
-      <c r="E8" s="8" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F8" s="8" t="str">
-        <v>YARD_FIN_MUGGIANO</v>
-      </c>
-      <c r="G8" s="8" t="str">
-        <v>Delivered 2013</v>
-      </c>
-      <c r="H8" s="8" t="str">
-        <v>Italy → UAE</v>
-      </c>
-      <c r="I8" s="8" t="str">
-        <v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="str">
-        <v>VES_UAE_P51_01</v>
-      </c>
-      <c r="B9" s="8" t="str">
-        <v>P51MR OPV 01 — name pending</v>
-      </c>
-      <c r="C9" s="8" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D9" s="8" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E9" s="8" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H9" s="8" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I9" s="8" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="str">
-        <v>VES_DEF_009</v>
-      </c>
-      <c r="B10" s="8" t="str">
-        <v>Al-Dorra class - first vessel</v>
-      </c>
-      <c r="C10" s="8" t="str">
-        <v>PROG_ADSB_ALDORRA</v>
-      </c>
-      <c r="D10" s="8" t="str">
-        <v>62 m vessel</v>
-      </c>
-      <c r="E10" s="8" t="str">
-        <v>Kuwait Naval Forces</v>
-      </c>
-      <c r="F10" s="8" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G10" s="8" t="str">
-        <v>Launched Feb 2026</v>
-      </c>
-      <c r="H10" s="8" t="str">
-        <v>UAE → Kuwait</v>
-      </c>
-      <c r="I10" s="8" t="str">
-        <v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="str">
-        <v>VES_DEF_010</v>
-      </c>
-      <c r="B11" s="8" t="str">
-        <v>Stan Patrol 5009 - sample hull</v>
-      </c>
-      <c r="C11" s="8" t="str">
-        <v>PROG_DUTCH_CG</v>
-      </c>
-      <c r="D11" s="8" t="str">
-        <v>Stan Patrol 5009</v>
-      </c>
-      <c r="E11" s="8" t="str">
-        <v>Dutch Caribbean Coast Guard</v>
-      </c>
-      <c r="F11" s="8" t="str">
-        <v>YARD_DAMEN_ANTALYA</v>
-      </c>
-      <c r="G11" s="8" t="str">
-        <v>Contracted</v>
-      </c>
-      <c r="H11" s="8" t="str">
-        <v>Turkey → Caribbean</v>
-      </c>
-      <c r="I11" s="8" t="str">
-        <v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>VES_AOPS_01</v>
-      </c>
-      <c r="B12" t="str">
-        <v>HMCS Harry DeWolf</v>
-      </c>
-      <c r="C12" t="str">
-        <v>PROG_AOPS_RCN</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Harry DeWolf-class AOPV</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F12" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Delivered 2020 / operational</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Halifax → RCN</v>
-      </c>
-      <c r="I12" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>VES_AOPS_02</v>
-      </c>
-      <c r="B13" t="str">
-        <v>HMCS Margaret Brooke</v>
-      </c>
-      <c r="C13" t="str">
-        <v>PROG_AOPS_RCN</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Harry DeWolf-class AOPV</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F13" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Delivered 2021 / operational</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Halifax → RCN</v>
-      </c>
-      <c r="I13" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>VES_AOPS_03</v>
-      </c>
-      <c r="B14" t="str">
-        <v>HMCS Max Bernays</v>
-      </c>
-      <c r="C14" t="str">
-        <v>PROG_AOPS_RCN</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Harry DeWolf-class AOPV</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F14" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Delivered 2022 / operational</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Halifax → RCN</v>
-      </c>
-      <c r="I14" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>VES_AOPS_04</v>
-      </c>
-      <c r="B15" t="str">
-        <v>HMCS William Hall</v>
-      </c>
-      <c r="C15" t="str">
-        <v>PROG_AOPS_RCN</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Harry DeWolf-class AOPV</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F15" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Delivered 2023 / commissioned 2024</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Halifax → RCN</v>
-      </c>
-      <c r="I15" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>VES_AOPS_05</v>
-      </c>
-      <c r="B16" t="str">
-        <v>HMCS Frédérick Rolette</v>
-      </c>
-      <c r="C16" t="str">
-        <v>PROG_AOPS_RCN</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Harry DeWolf-class AOPV</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F16" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Delivered 2024 / commissioned 2025</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Halifax → RCN</v>
-      </c>
-      <c r="I16" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/news/2025/06/his-majestys-canadian-ship-frederick-rolette-commissioned-into-service.html</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>VES_AOPS_06</v>
-      </c>
-      <c r="B17" t="str">
-        <v>HMCS Robert Hampton Gray</v>
-      </c>
-      <c r="C17" t="str">
-        <v>PROG_AOPS_RCN</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Harry DeWolf-class AOPV</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Royal Canadian Navy</v>
-      </c>
-      <c r="F17" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Delivered 21 Aug 2025; commissioning expected 2026</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Halifax → RCN / Esquimalt</v>
-      </c>
-      <c r="I17" t="str">
-        <v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>VES_AOPS_07</v>
-      </c>
-      <c r="B18" t="str">
-        <v>CCGS Donjek</v>
-      </c>
-      <c r="C18" t="str">
-        <v>PROG_AOPS_CCG</v>
-      </c>
-      <c r="D18" t="str">
-        <v>AOPS Coast Guard variant</v>
-      </c>
-      <c r="E18" t="str">
-        <v>Canadian Coast Guard</v>
-      </c>
-      <c r="F18" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Launched 29 Apr 2026; delivery expected late 2026</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Halifax → CCG</v>
-      </c>
-      <c r="I18" t="str">
-        <v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>VES_AOPS_08</v>
-      </c>
-      <c r="B19" t="str">
-        <v>CCGS Sermilik</v>
-      </c>
-      <c r="C19" t="str">
-        <v>PROG_AOPS_CCG</v>
-      </c>
-      <c r="D19" t="str">
-        <v>AOPS Coast Guard variant</v>
-      </c>
-      <c r="E19" t="str">
-        <v>Canadian Coast Guard</v>
-      </c>
-      <c r="F19" t="str">
-        <v>YARD_IRV_HALIFAX</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Under construction; delivery expected 2027</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Halifax → CCG</v>
-      </c>
-      <c r="I19" t="str">
-        <v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>VES_UAE_F3_01</v>
-      </c>
-      <c r="B20" t="str">
-        <v>ALTAF</v>
-      </c>
-      <c r="C20" t="str">
-        <v>PROG_UAE_FALAJ3</v>
-      </c>
-      <c r="D20" t="str">
-        <v>FALAJ 3 62 m missile boat</v>
-      </c>
-      <c r="E20" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F20" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Commissioned 19 Feb 2025</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I20" t="str">
-        <v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>VES_UAE_F3_02</v>
-      </c>
-      <c r="B21" t="str">
-        <v>FALAJ 3 Unit 2 — name pending</v>
-      </c>
-      <c r="C21" t="str">
-        <v>PROG_UAE_FALAJ3</v>
-      </c>
-      <c r="D21" t="str">
-        <v>FALAJ 3 62 m missile boat</v>
-      </c>
-      <c r="E21" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F21" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Programme vessel / name not confirmed</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I21" t="str">
-        <v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>VES_UAE_F3_03</v>
-      </c>
-      <c r="B22" t="str">
-        <v>FALAJ 3 Unit 3 — name pending</v>
-      </c>
-      <c r="C22" t="str">
-        <v>PROG_UAE_FALAJ3</v>
-      </c>
-      <c r="D22" t="str">
-        <v>FALAJ 3 62 m missile boat</v>
-      </c>
-      <c r="E22" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F22" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Programme vessel / name not confirmed</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I22" t="str">
-        <v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>VES_UAE_F3_04</v>
-      </c>
-      <c r="B23" t="str">
-        <v>FALAJ 3 Unit 4 — name pending</v>
-      </c>
-      <c r="C23" t="str">
-        <v>PROG_UAE_FALAJ3</v>
-      </c>
-      <c r="D23" t="str">
-        <v>FALAJ 3 62 m missile boat</v>
-      </c>
-      <c r="E23" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F23" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Programme vessel / name not confirmed</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I23" t="str">
-        <v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>VES_UAE_BAY_01</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Baynunah (P171)</v>
-      </c>
-      <c r="C24" t="str">
-        <v>PROG_UAE_BAYNUNAH</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Baynunah-class corvette</v>
-      </c>
-      <c r="E24" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F24" t="str">
-        <v>YARD_CMN_CHERBOURG</v>
-      </c>
-      <c r="G24" t="str">
-        <v>In service</v>
-      </c>
-      <c r="H24" t="str">
-        <v>France → UAE</v>
-      </c>
-      <c r="I24" t="str">
-        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>VES_UAE_BAY_02</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Al Hesen (P172)</v>
-      </c>
-      <c r="C25" t="str">
-        <v>PROG_UAE_BAYNUNAH</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Baynunah-class corvette</v>
-      </c>
-      <c r="E25" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F25" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G25" t="str">
-        <v>In service</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I25" t="str">
-        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>VES_UAE_BAY_03</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Al Dhafra (P173)</v>
-      </c>
-      <c r="C26" t="str">
-        <v>PROG_UAE_BAYNUNAH</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Baynunah-class corvette</v>
-      </c>
-      <c r="E26" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F26" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G26" t="str">
-        <v>In service</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I26" t="str">
-        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>VES_UAE_BAY_04</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Mezyad (P174)</v>
-      </c>
-      <c r="C27" t="str">
-        <v>PROG_UAE_BAYNUNAH</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Baynunah-class corvette</v>
-      </c>
-      <c r="E27" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F27" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G27" t="str">
-        <v>In service</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I27" t="str">
-        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>VES_UAE_BAY_05</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Al Jahili (P175)</v>
-      </c>
-      <c r="C28" t="str">
-        <v>PROG_UAE_BAYNUNAH</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Baynunah-class corvette</v>
-      </c>
-      <c r="E28" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F28" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G28" t="str">
-        <v>In service</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I28" t="str">
-        <v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>VES_UAE_BAY_06</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Al Hili (P176)</v>
-      </c>
-      <c r="C29" t="str">
-        <v>PROG_UAE_BAYNUNAH</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Baynunah-class corvette</v>
-      </c>
-      <c r="E29" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F29" t="str">
-        <v>YARD_ADSB_ABUDHABI</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Commissioned 20 Feb 2017 / in service</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Abu Dhabi → UAE Navy</v>
-      </c>
-      <c r="I29" t="str">
-        <v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>VES_UAE_GOW_01</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Bani Yas</v>
-      </c>
-      <c r="C30" t="str">
-        <v>PROG_UAE_BANIYAS</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Gowind multi-mission corvette</v>
-      </c>
-      <c r="E30" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F30" t="str">
-        <v>YARD_NAVAL_LORIENT</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Delivered 21 Oct 2023</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Lorient → UAE</v>
-      </c>
-      <c r="I30" t="str">
-        <v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>VES_UAE_GOW_02</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Al Emarat</v>
-      </c>
-      <c r="C31" t="str">
-        <v>PROG_UAE_BANIYAS</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Gowind multi-mission corvette</v>
-      </c>
-      <c r="E31" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F31" t="str">
-        <v>YARD_NAVAL_LORIENT</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Delivered 27 Jun 2024</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Lorient → UAE</v>
-      </c>
-      <c r="I31" t="str">
-        <v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>VES_UAE_F2_02</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Qarnen</v>
-      </c>
-      <c r="C32" t="str">
-        <v>PROG_UAE_ABUDHABI</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Falaj 2 patrol vessel</v>
-      </c>
-      <c r="E32" t="str">
-        <v>UAE Navy</v>
-      </c>
-      <c r="F32" t="str">
-        <v>YARD_FIN_MUGGIANO</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Delivered / operational</v>
-      </c>
-      <c r="H32" t="str">
-        <v>Italy → UAE</v>
-      </c>
-      <c r="I32" t="str">
-        <v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>VES_UAE_P51_02</v>
-      </c>
-      <c r="B33" t="str">
-        <v>P51MR OPV 02 — name pending</v>
-      </c>
-      <c r="C33" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D33" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E33" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F33"/>
-      <c r="G33" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H33" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I33" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>VES_UAE_P51_03</v>
-      </c>
-      <c r="B34" t="str">
-        <v>P51MR OPV 03 — name pending</v>
-      </c>
-      <c r="C34" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D34" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E34" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F34"/>
-      <c r="G34" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H34" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I34" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>VES_UAE_P51_04</v>
-      </c>
-      <c r="B35" t="str">
-        <v>P51MR OPV 04 — name pending</v>
-      </c>
-      <c r="C35" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D35" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E35" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F35"/>
-      <c r="G35" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H35" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I35" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>VES_UAE_P51_05</v>
-      </c>
-      <c r="B36" t="str">
-        <v>P51MR OPV 05 — name pending</v>
-      </c>
-      <c r="C36" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D36" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E36" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F36"/>
-      <c r="G36" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H36" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I36" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>VES_UAE_P51_06</v>
-      </c>
-      <c r="B37" t="str">
-        <v>P51MR OPV 06 — name pending</v>
-      </c>
-      <c r="C37" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D37" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E37" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F37"/>
-      <c r="G37" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H37" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I37" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>VES_UAE_P51_07</v>
-      </c>
-      <c r="B38" t="str">
-        <v>P51MR OPV 07 — name pending</v>
-      </c>
-      <c r="C38" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D38" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E38" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F38"/>
-      <c r="G38" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H38" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I38" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>VES_UAE_P51_08</v>
-      </c>
-      <c r="B39" t="str">
-        <v>P51MR OPV 08 — name pending</v>
-      </c>
-      <c r="C39" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D39" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E39" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F39"/>
-      <c r="G39" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H39" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I39" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>VES_UAE_P51_09</v>
-      </c>
-      <c r="B40" t="str">
-        <v>P51MR OPV 09 — name pending</v>
-      </c>
-      <c r="C40" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D40" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E40" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F40"/>
-      <c r="G40" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H40" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I40" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>VES_UAE_P51_10</v>
-      </c>
-      <c r="B41" t="str">
-        <v>P51MR OPV 10 — name pending</v>
-      </c>
-      <c r="C41" t="str">
-        <v>PROG_UAE_P51MR</v>
-      </c>
-      <c r="D41" t="str">
-        <v>51 m OPV</v>
-      </c>
-      <c r="E41" t="str">
-        <v>UAE Coast Guard</v>
-      </c>
-      <c r="F41"/>
-      <c r="G41" t="str">
-        <v>Contracted / name not confirmed</v>
-      </c>
-      <c r="H41" t="str">
-        <v>UAE / Italy</v>
-      </c>
-      <c r="I41" t="str">
-        <v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>DEF_VES_ADMIRAL_ESSEN</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Admiral Essen</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Missile carrier / naval vessel</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Russian Black Sea Fleet</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Reported attacked</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Novorossiysk / Black Sea</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>VESSEL_SAGAR_MANTHAN</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ORV Sagar Manthan</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Ocean Research Vessel (Yard 3041)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Indian Navy</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Rishi Bankim Shipyard / India</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>Vessel ID</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="C1" s="4" t="str">
+        <x:v>Programme ID</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="str">
+        <x:v>Class / Type</x:v>
+      </x:c>
+      <x:c r="E1" s="4" t="str">
+        <x:v>Customer / Operator</x:v>
+      </x:c>
+      <x:c r="F1" s="4" t="str">
+        <x:v>Build Yard ID</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="str">
+        <x:v>Build / Delivery Route</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="8" t="str">
+        <x:v>VES_DEF_001</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>HMCS Fraser</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>PROG_RCD</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>River-class Destroyer</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="str">
+        <x:v>Full-rate production</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="I2" s="8" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/river-class-destroyer.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
+        <x:v>VES_DEF_002</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="str">
+        <x:v>Joint Support Ship 1</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="str">
+        <x:v>PROG_SEA_JSS</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="str">
+        <x:v>Joint Support Ship</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="str">
+        <x:v>YARD_SEA_VAN</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="H3" s="8" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="I3" s="8" t="str">
+        <x:v>https://www.seaspan.com/seaspan-shipyards/shipbuilding/joint-support-ships/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="8" t="str">
+        <x:v>VES_DEF_003</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
+        <x:v>Joint Support Ship 2</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>PROG_SEA_JSS</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>Joint Support Ship</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="str">
+        <x:v>YARD_SEA_VAN</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="H4" s="8" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="I4" s="8" t="str">
+        <x:v>https://www.seaspan.com/seaspan-shipyards/shipbuilding/joint-support-ships/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="8" t="str">
+        <x:v>VES_DEF_004</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="str">
+        <x:v>Seaspan Heavy Polar Icebreaker</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="str">
+        <x:v>PROG_SEA_POLAR</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str">
+        <x:v>Heavy polar icebreaker</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="str">
+        <x:v>YARD_SEA_VAN</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="H5" s="8" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-celebrates-one-year-of-progress-on-the-heavy-polar-icebreaker/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="8" t="str">
+        <x:v>VES_DEF_005</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="str">
+        <x:v>Polar Max</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="str">
+        <x:v>PROG_DAV_POLARMAX</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
+        <x:v>Heavy polar icebreaker</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="str">
+        <x:v>YARD_DAVIE_LEVIS</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="H6" s="8" t="str">
+        <x:v>Finland + Canada</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="str">
+        <x:v>https://www.davie.ca/en/news/20260331-davie-begins-construction-of-polarmax-en/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="8" t="str">
+        <x:v>VES_DEF_006</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="str">
+        <x:v>Abu Dhabi</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="str">
+        <x:v>PROG_UAE_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
+        <x:v>Abu Dhabi-class corvette</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="str">
+        <x:v>YARD_FIN_MUGGIANO</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>Delivered 2013</x:v>
+      </x:c>
+      <x:c r="H7" s="8" t="str">
+        <x:v>Italy → UAE</x:v>
+      </x:c>
+      <x:c r="I7" s="8" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="8" t="str">
+        <x:v>VES_DEF_007</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>Ghantut</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str">
+        <x:v>PROG_UAE_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="str">
+        <x:v>Falaj 2 patrol vessel</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="str">
+        <x:v>YARD_FIN_MUGGIANO</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>Delivered 2013</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="str">
+        <x:v>Italy → UAE</x:v>
+      </x:c>
+      <x:c r="I8" s="8" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2013/muggiano-double-delivery-for-the-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="8" t="str">
+        <x:v>VES_UAE_P51_01</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="str">
+        <x:v>P51MR OPV 01 — name pending</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F9" s="8"/>
+      <x:c r="G9" s="8" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H9" s="8" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I9" s="8" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="8" t="str">
+        <x:v>VES_DEF_009</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="str">
+        <x:v>Al-Dorra class - first vessel</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="str">
+        <x:v>PROG_ADSB_ALDORRA</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str">
+        <x:v>62 m vessel</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="str">
+        <x:v>Kuwait Naval Forces</x:v>
+      </x:c>
+      <x:c r="F10" s="8" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
+        <x:v>Launched Feb 2026</x:v>
+      </x:c>
+      <x:c r="H10" s="8" t="str">
+        <x:v>UAE → Kuwait</x:v>
+      </x:c>
+      <x:c r="I10" s="8" t="str">
+        <x:v>https://edgegroup.ae/news/adsb-celebrates-30-years-uae-shipbuilding-excellence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="8" t="str">
+        <x:v>VES_DEF_010</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="str">
+        <x:v>Stan Patrol 5009 - sample hull</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="str">
+        <x:v>PROG_DUTCH_CG</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>Stan Patrol 5009</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="str">
+        <x:v>Dutch Caribbean Coast Guard</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="str">
+        <x:v>YARD_DAMEN_ANTALYA</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
+        <x:v>Contracted</x:v>
+      </x:c>
+      <x:c r="H11" s="8" t="str">
+        <x:v>Turkey → Caribbean</x:v>
+      </x:c>
+      <x:c r="I11" s="8" t="str">
+        <x:v>https://www.damen.com/insights-center/news/damen-spa-5009-to-strengthen-dutch-caribbean-coast-guard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>VES_AOPS_01</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>HMCS Harry DeWolf</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Delivered 2020 / operational</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>VES_AOPS_02</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>HMCS Margaret Brooke</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>Delivered 2021 / operational</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>VES_AOPS_03</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>HMCS Max Bernays</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Delivered 2022 / operational</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>VES_AOPS_04</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>HMCS William Hall</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Delivered 2023 / commissioned 2024</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/services/procurement/arctic-offshore-patrol-ships.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>VES_AOPS_05</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>HMCS Frédérick Rolette</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Delivered 2024 / commissioned 2025</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Halifax → RCN</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/06/his-majestys-canadian-ship-frederick-rolette-commissioned-into-service.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>VES_AOPS_06</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>HMCS Robert Hampton Gray</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>PROG_AOPS_RCN</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Harry DeWolf-class AOPV</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Royal Canadian Navy</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Delivered 21 Aug 2025; commissioning expected 2026</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Halifax → RCN / Esquimalt</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>https://www.canada.ca/en/department-national-defence/news/2025/08/royal-canadian-navy-accepts-the-sixth-arctic-and-offshore-patrol-vessel.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>VES_AOPS_07</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>CCGS Donjek</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>AOPS Coast Guard variant</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Launched 29 Apr 2026; delivery expected late 2026</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Halifax → CCG</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>https://www.canada.ca/en/canadian-coast-guard/news/2026/04/canadian-coast-guard-launches-its-first-of-two-arctic-and-offshore-patrol-ships-ccgs-donjek.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>VES_AOPS_08</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>CCGS Sermilik</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>PROG_AOPS_CCG</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>AOPS Coast Guard variant</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Canadian Coast Guard</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>YARD_IRV_HALIFAX</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Under construction; delivery expected 2027</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Halifax → CCG</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>https://www.canada.ca/en/public-services-procurement/services/acquisitions/defence-marine/national-shipbuilding-strategy/projects/large-vessels/arctic-patrol-coast-guard.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>VES_UAE_F3_01</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>ALTAF</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>FALAJ 3 62 m missile boat</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Commissioned 19 Feb 2025</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>https://edgegroup.ae/news/hh-sheikh-hazza-bin-zayed-al-nahyan-staff-major-general-sheikh-ahmed-bin-tahnoun-al-nahyan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>VES_UAE_F3_02</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>FALAJ 3 Unit 2 — name pending</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>FALAJ 3 62 m missile boat</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Programme vessel / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>VES_UAE_F3_03</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>FALAJ 3 Unit 3 — name pending</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>FALAJ 3 62 m missile boat</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Programme vessel / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>VES_UAE_F3_04</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>FALAJ 3 Unit 4 — name pending</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>PROG_UAE_FALAJ3</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>FALAJ 3 62 m missile boat</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Programme vessel / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>https://edgegroup.ae/news/edge-groups-abu-dhabi-ship-building-pjsc-commences-production-falaj-class-vessels-uae-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>VES_UAE_BAY_01</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>Baynunah (P171)</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>YARD_CMN_CHERBOURG</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>France → UAE</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>VES_UAE_BAY_02</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Al Hesen (P172)</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>VES_UAE_BAY_03</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Al Dhafra (P173)</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>VES_UAE_BAY_04</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Mezyad (P174)</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>VES_UAE_BAY_05</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Al Jahili (P175)</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>In service</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>https://en.wikipedia.org/wiki/Baynunah-class_corvette</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>VES_UAE_BAY_06</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Al Hili (P176)</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>PROG_UAE_BAYNUNAH</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Baynunah-class corvette</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>YARD_ADSB_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Commissioned 20 Feb 2017 / in service</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Abu Dhabi → UAE Navy</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>https://www.wam.ae/en/article/hszr53nn-commissions-uae-made-baynunah-class-corvette-hili</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>VES_UAE_GOW_01</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Bani Yas</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Gowind multi-mission corvette</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>YARD_NAVAL_LORIENT</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Delivered 21 Oct 2023</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Lorient → UAE</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>VES_UAE_GOW_02</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Al Emarat</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>PROG_UAE_BANIYAS</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>Gowind multi-mission corvette</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>YARD_NAVAL_LORIENT</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Delivered 27 Jun 2024</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Lorient → UAE</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>https://www.naval-group.com/en/naval-group-delivers-second-gowindr-corvette-al-emarat-united-arab-emirates</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>VES_UAE_F2_02</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Qarnen</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>PROG_UAE_ABUDHABI</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Falaj 2 patrol vessel</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>UAE Navy</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>YARD_FIN_MUGGIANO</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Delivered / operational</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Italy → UAE</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>https://www.fincantieri.com/en/newsroom/press-releases/2012/second-patrol-vessel-for-the-eau-navy-launched-the-qarnen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>VES_UAE_P51_02</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>P51MR OPV 02 — name pending</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F33"/>
+      <x:c r="G33" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>VES_UAE_P51_03</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>P51MR OPV 03 — name pending</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F34"/>
+      <x:c r="G34" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>VES_UAE_P51_04</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>P51MR OPV 04 — name pending</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F35"/>
+      <x:c r="G35" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>VES_UAE_P51_05</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>P51MR OPV 05 — name pending</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F36"/>
+      <x:c r="G36" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>VES_UAE_P51_06</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>P51MR OPV 06 — name pending</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F37"/>
+      <x:c r="G37" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>VES_UAE_P51_07</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>P51MR OPV 07 — name pending</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F38"/>
+      <x:c r="G38" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>VES_UAE_P51_08</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>P51MR OPV 08 — name pending</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F39"/>
+      <x:c r="G39" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>VES_UAE_P51_09</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>P51MR OPV 09 — name pending</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F40"/>
+      <x:c r="G40" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>VES_UAE_P51_10</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>P51MR OPV 10 — name pending</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>PROG_UAE_P51MR</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>51 m OPV</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>UAE Coast Guard</x:v>
+      </x:c>
+      <x:c r="F41"/>
+      <x:c r="G41" t="str">
+        <x:v>Contracted / name not confirmed</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>UAE / Italy</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>https://edgegroup.ae/news/edge-group-and-fincantieri-formalise-shipbuilding-joint-venture-maestral-and-announce-400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DEF_VES_ADMIRAL_ESSEN</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Admiral Essen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Missile carrier / naval vessel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Russian Black Sea Fleet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Reported attacked</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H42" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Novorossiysk / Black Sea</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>ORV Sagar Manthan</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Ocean Research Vessel / Yard 3041</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>NCPOR / Ministry of Earth Sciences</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>YARD_GRSE_RISHI_BANKIM</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>Launched / outfitting</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>VESSEL_SAGAR_KANYA</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>ORV Sagar Kanya</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Legacy multidisciplinary ocean research vessel</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>NCPOR / Ministry of Earth Sciences</x:v>
+      </x:c>
+      <x:c r="F44"/>
+      <x:c r="G44" t="str">
+        <x:v>Operating / gradual replacement planned</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Germany → India</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>https://ncpor.res.in/pages/view/260/167-orv-sagar-kanya</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>VESSEL_ARS_3058</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Acoustic Research Ship — Yard 3058 (name pending)</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>PROG_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Acoustic Research Ship</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>NPOL / DRDO</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>YARD_GRSE_RISHI_BANKIM</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7221,6 +7670,70 @@
       </x:c>
       <x:c r="J12" t="str">
         <x:v>https://www.naval-group.com/en/delivery-first-gowindr-corvette-united-arab-emirates-navy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>CON_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>2024-07-16</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>PROG_IND_ORV_NCPOR</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>NCPOR / Ministry of Earth Sciences</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>₹840 crore (~US$100.50m @ ₹83.58/USD)</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>1 Ocean Research Vessel / Yard 3041</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>Government shipbuilding contract</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>Launched 9 Sep 2026; delivery scheduled 2028</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Signing_of_Contract_for_construction_and_delivery_of_ORV_for_NCPOR.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>CON_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>2024-10-29</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>PROG_IND_ARS_NPOL</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>NPOL / DRDO</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>₹490.98 crore (~US$58.40m @ ₹84.06594/USD)</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>1 Acoustic Research Ship / Yard 3058</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Government defence-R&amp;D shipbuilding contract</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>Under construction</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
